--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C1C176-E1DD-4925-B633-CC954F56CA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EC0899-CF6A-5D48-B850-CAE5C38F363B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
     <sheet name="_CN_" sheetId="14" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="16" r:id="rId4"/>
-    <sheet name="_US_" sheetId="15" r:id="rId5"/>
+    <sheet name="Data" sheetId="17" r:id="rId3"/>
+    <sheet name="R" sheetId="12" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
@@ -27,11 +27,24 @@
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328482352282765" hidden="1">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="141">
   <si>
     <t>Name</t>
   </si>
@@ -78,18 +91,9 @@
     <t>成本收入比</t>
   </si>
   <si>
-    <t>Source</t>
-  </si>
-  <si>
     <t>Capital Ratio</t>
   </si>
   <si>
-    <t>Regulatory minimum</t>
-  </si>
-  <si>
-    <t>Cost of Equity</t>
-  </si>
-  <si>
     <t>Terminal Growth (g₂)</t>
   </si>
   <si>
@@ -145,9 +149,6 @@
   </si>
   <si>
     <t>Report Currency</t>
-  </si>
-  <si>
-    <t>Value = Sustainable Earnings × (1 / Required Return)</t>
   </si>
   <si>
     <t>Latest price + currency sign</t>
@@ -315,12 +316,173 @@
   </si>
   <si>
     <t>核心一级资本充足率</t>
+  </si>
+  <si>
+    <t>Fair P/TBV ≈ (ROTCE – g) ÷ (k – g)</t>
+  </si>
+  <si>
+    <t>TBV is Tangible Common Equity.</t>
+  </si>
+  <si>
+    <t>Tangible Common Equity per Share</t>
+  </si>
+  <si>
+    <t>Common Equity per share</t>
+  </si>
+  <si>
+    <t>ROTCE = Core Net income ÷ Tangible common equity (goodwill &amp; intangibles stripped out).</t>
+  </si>
+  <si>
+    <t>Core net income is predictable, high-quality earnings from core operations (e.g., deposits and lending) rather than fluctuating trading activities,</t>
+  </si>
+  <si>
+    <t>ROTCE</t>
+  </si>
+  <si>
+    <t>Total Assets/Total Equity</t>
+  </si>
+  <si>
+    <t>DuPont for ROTCE</t>
+  </si>
+  <si>
+    <t>ROTCE = Net Profit Margin × Asset Turnover × Tangible Equity Multiplier</t>
+  </si>
+  <si>
+    <t>Asset Turnover = Total Revenue / Total Assets</t>
+  </si>
+  <si>
+    <t>Tangible Equity Multiplier = Total Assets / Tangible Common Equity</t>
+  </si>
+  <si>
+    <t>Tangible Equity Multiplier</t>
+  </si>
+  <si>
+    <t>Net Profit Margin = Core Net Income attributable to common shareholders / Total Revenue</t>
+  </si>
+  <si>
+    <t>Core Net Income attributable to common shareholders / Total Revenue</t>
+  </si>
+  <si>
+    <t>Core Net income attributable to common shareholders ÷ Tangible common equity</t>
+  </si>
+  <si>
+    <t>(ROTCE – g) ÷ (k – g)</t>
+  </si>
+  <si>
+    <t>Fair TBV Multiple</t>
+  </si>
+  <si>
+    <t>TBV * Fair TBV Multiple</t>
+  </si>
+  <si>
+    <t>最新财报的截止日期</t>
+  </si>
+  <si>
+    <t>财年结束日期</t>
+  </si>
+  <si>
+    <t>财务报告使用的货币</t>
+  </si>
+  <si>
+    <t>最新股价</t>
+  </si>
+  <si>
+    <t>交易货币</t>
+  </si>
+  <si>
+    <t>Company Info.</t>
+  </si>
+  <si>
+    <t>Profitability &amp; Efficiency</t>
+  </si>
+  <si>
+    <t>Per Share Metrics</t>
+  </si>
+  <si>
+    <t>Last FY EPS</t>
+  </si>
+  <si>
+    <t>Last FY Core EPS</t>
+  </si>
+  <si>
+    <t>上一个财年EPS</t>
+  </si>
+  <si>
+    <t>上一个财年核心EPS</t>
+  </si>
+  <si>
+    <t>每股有形净资产</t>
+  </si>
+  <si>
+    <t>Core Net Income Margin</t>
+  </si>
+  <si>
+    <t>核心净利率</t>
+  </si>
+  <si>
+    <t>有形权益乘数</t>
+  </si>
+  <si>
+    <t>有形普通股回报率</t>
+  </si>
+  <si>
+    <t>Valuation</t>
+  </si>
+  <si>
+    <t>隐含公允市净率</t>
+  </si>
+  <si>
+    <t>隐含公允股价</t>
+  </si>
+  <si>
+    <t>股息率</t>
+  </si>
+  <si>
+    <t>Dividend Yield</t>
+  </si>
+  <si>
+    <t>Cost of Equity (k)</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>Inflation rate as proxy for long term Growth</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Financial Year End
+(MM/DD)</t>
+  </si>
+  <si>
+    <t>End Date of Last Statement
+(YYYY/MM/DD)</t>
+  </si>
+  <si>
+    <t>12/31</t>
+  </si>
+  <si>
+    <t>Lastest Price</t>
+  </si>
+  <si>
+    <t>Fair Price 
+in Trading Currency</t>
+  </si>
+  <si>
+    <t>Market</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="167" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -350,7 +512,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,8 +525,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -387,6 +573,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -395,16 +605,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -421,10 +628,50 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -450,9 +697,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -490,7 +737,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -596,7 +843,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -738,7 +985,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -746,87 +993,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D2ED91-59EB-437C-A4C2-C114238F9C2A}">
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="20.73046875" customWidth="1"/>
-    <col min="5" max="5" width="23.06640625" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="D4" s="3">
+        <v>7.2499999999999995E-2</v>
+      </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B5" s="1"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="D5" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>38</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -836,485 +1105,1333 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6E8AA2-48F2-4368-B9E3-BA821DC1A767}">
-  <dimension ref="B2:W12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:W11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="23" width="18.59765625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="21" width="18.6640625" customWidth="1"/>
+    <col min="22" max="23" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:23" ht="80" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="W3" s="15"/>
+    </row>
+    <row r="4" spans="2:23" ht="48" x14ac:dyDescent="0.2">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-    </row>
-    <row r="3" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-    </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="L4" s="10" t="s">
+      <c r="R5" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="O4" s="9" t="s">
+      <c r="S5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.26550000000000001</v>
+      </c>
+      <c r="I6" s="19">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K6" s="22">
+        <v>12.49</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.44519999999999998</v>
+      </c>
+      <c r="M6" s="22">
+        <v>11.7</v>
+      </c>
+      <c r="N6" s="22">
+        <v>11.7</v>
+      </c>
+      <c r="O6" s="22">
+        <v>0.99</v>
+      </c>
+      <c r="P6" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0.308</v>
+      </c>
+      <c r="R6" s="20">
+        <f>Q6/O6</f>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="S6" s="22">
+        <v>7.43</v>
+      </c>
+      <c r="T6" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U6" s="19">
+        <f>Q6/S6</f>
+        <v>4.1453566621803502E-2</v>
+      </c>
+      <c r="V6" s="16">
+        <v>1.26</v>
+      </c>
+      <c r="W6" s="22">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0.25530000000000003</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.1032</v>
+      </c>
+      <c r="J7" s="21">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="K7" s="22">
+        <v>12.86</v>
+      </c>
+      <c r="L7" s="19">
+        <v>0.4612</v>
+      </c>
+      <c r="M7" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="N7" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="O7" s="22">
+        <v>1.3</v>
+      </c>
+      <c r="P7" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="R7" s="20">
+        <f t="shared" ref="R7:R11" si="0">Q7/O7</f>
+        <v>0.2976923076923077</v>
+      </c>
+      <c r="S7" s="22">
+        <v>8.91</v>
+      </c>
+      <c r="T7" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U7" s="19">
+        <f>Q7/S7</f>
+        <v>4.3434343434343436E-2</v>
+      </c>
+      <c r="V7" s="16">
+        <v>1.46</v>
+      </c>
+      <c r="W7" s="22">
+        <v>19.71</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0.29139999999999999</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.1047</v>
+      </c>
+      <c r="J8" s="21">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="K8" s="22">
+        <v>16.38</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="M8" s="22">
+        <v>8.59</v>
+      </c>
+      <c r="N8" s="22">
+        <v>8.59</v>
+      </c>
+      <c r="O8" s="22">
+        <v>0.78</v>
+      </c>
+      <c r="P8" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="R8" s="20">
+        <f t="shared" si="0"/>
+        <v>0.3051282051282051</v>
+      </c>
+      <c r="S8" s="22">
+        <v>6.96</v>
+      </c>
+      <c r="T8" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U8" s="19">
+        <f>Q8/S8</f>
+        <v>3.4195402298850576E-2</v>
+      </c>
+      <c r="V8" s="16">
+        <v>1.49</v>
+      </c>
+      <c r="W8" s="22">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G9" s="19">
+        <v>1.26E-2</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0.27</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.09</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K9" s="22">
+        <v>12.5</v>
+      </c>
+      <c r="L9" s="19">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="M9" s="22">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="N9" s="22">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="O9" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="P9" s="22">
+        <v>0.72</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="R9" s="20">
+        <f t="shared" si="0"/>
+        <v>0.30533333333333335</v>
+      </c>
+      <c r="S9" s="22">
+        <v>5.38</v>
+      </c>
+      <c r="T9" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="19">
+        <f>Q9/S9</f>
+        <v>4.2565055762081784E-2</v>
+      </c>
+      <c r="V9" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="W9" s="22">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-    </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="19">
+        <v>8.7400000000000005E-2</v>
+      </c>
+      <c r="J10" s="21">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="K10" s="22">
+        <v>12.64</v>
+      </c>
+      <c r="L10" s="19">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="M10" s="22">
+        <v>36.89</v>
+      </c>
+      <c r="N10" s="22">
+        <v>36.89</v>
+      </c>
+      <c r="O10" s="22">
+        <v>3.21</v>
+      </c>
+      <c r="P10" s="22">
+        <v>3.21</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>1.06</v>
+      </c>
+      <c r="R10" s="20">
+        <f t="shared" si="0"/>
+        <v>0.33021806853582558</v>
+      </c>
+      <c r="S10" s="22">
+        <v>20.09</v>
+      </c>
+      <c r="T10" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="19">
+        <f>Q10/S10</f>
+        <v>5.2762568442010951E-2</v>
+      </c>
+      <c r="V10" s="22">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W10" s="22">
+        <v>42.35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-    </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-    </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-    </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.45">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
+      <c r="D11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G11" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="H11" s="19">
+        <v>0.32</v>
+      </c>
+      <c r="I11" s="19">
+        <v>7.9600000000000004E-2</v>
+      </c>
+      <c r="J11" s="21">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="K11" s="22">
+        <v>16.3</v>
+      </c>
+      <c r="L11" s="19">
+        <v>0.252</v>
+      </c>
+      <c r="M11" s="22">
+        <v>8.44</v>
+      </c>
+      <c r="N11" s="22">
+        <v>8.44</v>
+      </c>
+      <c r="O11" s="22">
+        <v>0.76</v>
+      </c>
+      <c r="P11" s="22">
+        <v>0.76</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>0.24</v>
+      </c>
+      <c r="R11" s="20">
+        <f t="shared" si="0"/>
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="S11" s="22">
+        <v>5.17</v>
+      </c>
+      <c r="T11" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U11" s="19">
+        <f>Q11/S11</f>
+        <v>4.6421663442940041E-2</v>
+      </c>
+      <c r="V11" s="22">
+        <v>0.99</v>
+      </c>
+      <c r="W11" s="22">
+        <v>8.36</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="S3:U3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3340EE-867B-1444-82F3-2AF6ED01C016}">
+  <dimension ref="B2:W11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="21" width="18.6640625" customWidth="1"/>
+    <col min="22" max="23" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23" ht="80" x14ac:dyDescent="0.2">
+      <c r="B2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="W3" s="15"/>
+    </row>
+    <row r="4" spans="2:23" ht="48" x14ac:dyDescent="0.2">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.26550000000000001</v>
+      </c>
+      <c r="I6" s="19">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K6" s="22">
+        <v>12.49</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0.44519999999999998</v>
+      </c>
+      <c r="M6" s="22">
+        <v>11.7</v>
+      </c>
+      <c r="N6" s="22">
+        <v>11.7</v>
+      </c>
+      <c r="O6" s="22">
+        <v>0.99</v>
+      </c>
+      <c r="P6" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0.308</v>
+      </c>
+      <c r="R6" s="20">
+        <f>Q6/O6</f>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="S6" s="22">
+        <v>7.43</v>
+      </c>
+      <c r="T6" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U6" s="19">
+        <f>Q6/S6</f>
+        <v>4.1453566621803502E-2</v>
+      </c>
+      <c r="V6" s="16">
+        <v>1.26</v>
+      </c>
+      <c r="W6" s="22">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0.25530000000000003</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.1032</v>
+      </c>
+      <c r="J7" s="21">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="K7" s="22">
+        <v>12.86</v>
+      </c>
+      <c r="L7" s="19">
+        <v>0.4612</v>
+      </c>
+      <c r="M7" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="N7" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="O7" s="22">
+        <v>1.3</v>
+      </c>
+      <c r="P7" s="22">
+        <v>1.29</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="R7" s="20">
+        <f t="shared" ref="R7:R9" si="0">Q7/O7</f>
+        <v>0.2976923076923077</v>
+      </c>
+      <c r="S7" s="22">
+        <v>8.91</v>
+      </c>
+      <c r="T7" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U7" s="19">
+        <f>Q7/S7</f>
+        <v>4.3434343434343436E-2</v>
+      </c>
+      <c r="V7" s="16">
+        <v>1.46</v>
+      </c>
+      <c r="W7" s="22">
+        <v>19.71</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0.29139999999999999</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.1047</v>
+      </c>
+      <c r="J8" s="21">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="K8" s="22">
+        <v>16.38</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="M8" s="22">
+        <v>8.59</v>
+      </c>
+      <c r="N8" s="22">
+        <v>8.59</v>
+      </c>
+      <c r="O8" s="22">
+        <v>0.78</v>
+      </c>
+      <c r="P8" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="R8" s="20">
+        <f t="shared" si="0"/>
+        <v>0.3051282051282051</v>
+      </c>
+      <c r="S8" s="22">
+        <v>6.96</v>
+      </c>
+      <c r="T8" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U8" s="19">
+        <f>Q8/S8</f>
+        <v>3.4195402298850576E-2</v>
+      </c>
+      <c r="V8" s="16">
+        <v>1.49</v>
+      </c>
+      <c r="W8" s="22">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G9" s="19">
+        <v>1.26E-2</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0.27</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.09</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1.6E-2</v>
+      </c>
+      <c r="K9" s="22">
+        <v>12.5</v>
+      </c>
+      <c r="L9" s="19">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="M9" s="22">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="N9" s="22">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="O9" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="P9" s="22">
+        <v>0.72</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="R9" s="20">
+        <f t="shared" si="0"/>
+        <v>0.30533333333333335</v>
+      </c>
+      <c r="S9" s="22">
+        <v>5.38</v>
+      </c>
+      <c r="T9" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="19">
+        <f>Q9/S9</f>
+        <v>4.2565055762081784E-2</v>
+      </c>
+      <c r="V9" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="W9" s="22">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="22"/>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="18">
+        <v>45930</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="V3:W3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3942D8-FD59-4EBD-B3EE-552DD1A594AB}">
   <dimension ref="B2:L21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="32.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="22.59765625" customWidth="1"/>
-    <col min="5" max="12" width="18.59765625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="12" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
@@ -1337,10 +2454,10 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
@@ -1352,15 +2469,15 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1371,15 +2488,15 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1390,15 +2507,15 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1409,15 +2526,15 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1428,15 +2545,15 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1447,15 +2564,15 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -1466,15 +2583,15 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1485,9 +2602,9 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>2</v>
@@ -1504,15 +2621,15 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1523,15 +2640,15 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1542,12 +2659,12 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>12</v>
@@ -1561,12 +2678,12 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>13</v>
@@ -1580,12 +2697,12 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -1599,10 +2716,10 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="1"/>
@@ -1614,10 +2731,10 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="1"/>
@@ -1629,10 +2746,10 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="1"/>
@@ -1644,10 +2761,10 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="1"/>
@@ -1665,54 +2782,54 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D576F13-239D-4B57-808C-A408C5C0333E}">
   <dimension ref="B2:J20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="4" width="15.59765625" customWidth="1"/>
-    <col min="5" max="10" width="18.59765625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="10" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>51</v>
+      <c r="D2" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>52</v>
+      <c r="D3" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
@@ -1733,15 +2850,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>5</v>
@@ -1762,15 +2879,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>53</v>
+        <v>74</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1779,15 +2896,15 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1796,15 +2913,15 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="8" t="s">
+    <row r="7" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>71</v>
+      <c r="C7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1813,15 +2930,15 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>73</v>
+    <row r="8" spans="2:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="B8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1830,15 +2947,15 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:10" ht="48" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>5</v>
@@ -1859,15 +2976,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="48" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>56</v>
+        <v>75</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -1876,15 +2993,15 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>80</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1893,15 +3010,15 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1910,15 +3027,15 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1927,15 +3044,15 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1944,15 +3061,15 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1961,15 +3078,15 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1978,14 +3095,14 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E17" s="1"/>
@@ -1995,14 +3112,14 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="1"/>
@@ -2012,14 +3129,14 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" ht="48" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="1"/>
@@ -2029,14 +3146,14 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="1"/>
@@ -2049,112 +3166,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43E465B-07D1-4F4A-99AA-E08A45441664}">
-  <dimension ref="B2:Q3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="2" spans="2:17" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="2:17" ht="57" x14ac:dyDescent="0.45">
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,18 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8944044B-277E-4DEB-A9DD-3E1EC9CBF60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7770292-F970-4AA4-8488-3B55C8DAB788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
-    <sheet name="_CN_" sheetId="14" r:id="rId2"/>
+    <sheet name="Model" sheetId="14" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
-    <definedName name="g">Assumptions!$D$4</definedName>
-    <definedName name="k">Assumptions!$D$3</definedName>
+    <definedName name="Base_Cost_of_Equity">Assumptions!$C$9</definedName>
+    <definedName name="Benchmark_yield">Assumptions!$C$8</definedName>
+    <definedName name="Entry_yield">Assumptions!$C$7</definedName>
+    <definedName name="g">Assumptions!$C$4</definedName>
+    <definedName name="Holding_Period">Assumptions!$C$5</definedName>
+    <definedName name="k">Assumptions!$C$3</definedName>
+    <definedName name="Target_return">Assumptions!$C$6</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328481945590045" hidden="1">#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328482352282765" hidden="1">#REF!</definedName>
   </definedNames>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="125">
   <si>
     <t>Name</t>
   </si>
@@ -70,9 +75,6 @@
   </si>
   <si>
     <t>Core Philosophy</t>
-  </si>
-  <si>
-    <t>Calculation</t>
   </si>
   <si>
     <t>From last FY report</t>
@@ -235,18 +237,9 @@
     <t>Company Info.</t>
   </si>
   <si>
-    <t>Profitability &amp; Efficiency</t>
-  </si>
-  <si>
     <t>Per Share Metrics</t>
   </si>
   <si>
-    <t>Last FY EPS</t>
-  </si>
-  <si>
-    <t>Last FY Core EPS</t>
-  </si>
-  <si>
     <t>上一个财年EPS</t>
   </si>
   <si>
@@ -281,9 +274,6 @@
   </si>
   <si>
     <t>Dividend Yield</t>
-  </si>
-  <si>
-    <t>Cost of Equity (k)</t>
   </si>
   <si>
     <t>Inflation rate as proxy for long term Growth</t>
@@ -303,9 +293,6 @@
     <t>12/31</t>
   </si>
   <si>
-    <t>Lastest Price</t>
-  </si>
-  <si>
     <t>Fair Price 
 in Trading Currency</t>
   </si>
@@ -320,18 +307,126 @@
   </si>
   <si>
     <t>Long-term Growth (g)</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>@ Target Return</t>
+  </si>
+  <si>
+    <t>@Entry yield</t>
+  </si>
+  <si>
+    <t>@Benchmark yield</t>
+  </si>
+  <si>
+    <t>@Base equity cost</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Bank Cost of Equity (k)</t>
+  </si>
+  <si>
+    <t>目标价</t>
+  </si>
+  <si>
+    <t>买入价</t>
+  </si>
+  <si>
+    <t>卖出价</t>
+  </si>
+  <si>
+    <t>退出价</t>
+  </si>
+  <si>
+    <t>Lastest Market Price</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Last FY Core shareholders' EPS</t>
+  </si>
+  <si>
+    <t>Last FY 
+shareholders' EPS</t>
+  </si>
+  <si>
+    <t>有形净资产</t>
+  </si>
+  <si>
+    <t>核心净利润</t>
+  </si>
+  <si>
+    <t>Last FY Core shareholders' Net Income</t>
+  </si>
+  <si>
+    <t>收入</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>总资产</t>
+  </si>
+  <si>
+    <t>Tangible Common Equity (TBV)</t>
+  </si>
+  <si>
+    <t>CET1</t>
+  </si>
+  <si>
+    <t>普通股一级资本比率</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Profibilities and Efficiency</t>
+  </si>
+  <si>
+    <t>Share Outstanding</t>
+  </si>
+  <si>
+    <t>股数</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot;yrs&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,8 +468,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,18 +494,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,8 +509,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -459,6 +587,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -467,7 +608,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -477,16 +618,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -496,21 +628,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -525,16 +642,114 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -860,821 +1075,1062 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D2ED91-59EB-437C-A4C2-C114238F9C2A}">
-  <dimension ref="B2:E21"/>
+  <dimension ref="B2:D24"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="36.33203125" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" customWidth="1"/>
+    <col min="4" max="4" width="71.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D2" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="24">
+        <v>99</v>
+      </c>
+      <c r="C3" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="15">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="14">
+        <v>0.29465259038036606</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0.20075184365903009</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0.1174</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="14">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="24">
-        <v>0.02</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>56</v>
+      <c r="B19" s="20" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6E8AA2-48F2-4368-B9E3-BA821DC1A767}">
-  <dimension ref="B2:Y11"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:AG12"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="18" width="18.6640625" customWidth="1"/>
-    <col min="19" max="25" width="18.796875" customWidth="1"/>
+    <col min="2" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="11" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="18.6640625" customWidth="1" collapsed="1"/>
+    <col min="13" max="18" width="18.6640625" customWidth="1"/>
+    <col min="19" max="24" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="18.796875" customWidth="1" collapsed="1"/>
+    <col min="26" max="33" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:33" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="T2" s="2"/>
+      <c r="U2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+    </row>
+    <row r="3" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB3" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC3" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD3" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE3" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+    </row>
+    <row r="4" spans="2:33" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="B4" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="M4" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="T4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="V4" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="W4" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z4" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB4" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC4" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD4" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE4" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B5" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="D5" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="M5" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="P5" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="X5" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-    </row>
-    <row r="3" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-    </row>
-    <row r="4" spans="2:25" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B5" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="Y5" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA5" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB5" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC5" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE5" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="AF5" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG5" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M5" s="5" t="s">
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="T5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="9">
+        <v>45930</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0.26550000000000001</v>
+      </c>
+      <c r="O6" s="45">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="P6" s="46">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Q6" s="47">
+        <v>12.49</v>
+      </c>
+      <c r="R6" s="45">
+        <v>0.44519999999999998</v>
+      </c>
+      <c r="S6" s="47">
+        <v>11.7</v>
+      </c>
+      <c r="T6" s="47">
+        <v>11.7</v>
+      </c>
+      <c r="U6" s="47">
+        <v>0.99</v>
+      </c>
+      <c r="V6" s="47">
+        <v>0.94</v>
+      </c>
+      <c r="W6" s="48">
+        <v>0.308</v>
+      </c>
+      <c r="X6" s="6">
+        <f>W6/U6</f>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="Y6" s="7">
+        <f>(O6-g)/(k-g)</f>
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="Z6" s="7">
+        <f>T6*Y6</f>
+        <v>10.67625</v>
+      </c>
+      <c r="AA6" s="7">
+        <f>PV(Target_return,Holding_Period,-W6,-Z6)</f>
+        <v>5.4835251610179547</v>
+      </c>
+      <c r="AB6" s="7">
+        <f>PV(Entry_yield,Holding_Period,-W6,-Z6)</f>
+        <v>6.8148202193689871</v>
+      </c>
+      <c r="AC6" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-W6,-Z6)</f>
+        <v>8.3953949087133903</v>
+      </c>
+      <c r="AD6" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-W6,-Z6)</f>
+        <v>9.4588096710841096</v>
+      </c>
+      <c r="AE6" s="13">
+        <v>7.43</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG6" s="5">
+        <f>W6/AE6</f>
+        <v>4.1453566621803502E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="C7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="17">
+      <c r="E7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="9">
         <v>45930</v>
       </c>
-      <c r="G6" s="20">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="H6" s="20">
-        <v>0.26550000000000001</v>
-      </c>
-      <c r="I6" s="20">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="J6" s="21">
-        <v>1.6E-2</v>
-      </c>
-      <c r="K6" s="22">
-        <v>12.49</v>
-      </c>
-      <c r="L6" s="20">
-        <v>0.44519999999999998</v>
-      </c>
-      <c r="M6" s="22">
-        <v>11.7</v>
-      </c>
-      <c r="N6" s="22">
-        <v>11.7</v>
-      </c>
-      <c r="O6" s="22">
-        <v>0.99</v>
-      </c>
-      <c r="P6" s="22">
-        <v>0.94</v>
-      </c>
-      <c r="Q6" s="19">
-        <v>0.308</v>
-      </c>
-      <c r="R6" s="9">
-        <f>Q6/O6</f>
-        <v>0.31111111111111112</v>
-      </c>
-      <c r="S6" s="10">
-        <f>(I6-g)/(k-g)</f>
-        <v>1.3904761904761906</v>
-      </c>
-      <c r="T6" s="10">
-        <f>N6*S6</f>
-        <v>16.26857142857143</v>
-      </c>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10">
-        <v>7.43</v>
-      </c>
-      <c r="X6" s="10" t="s">
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="N7" s="12">
+        <v>0.25530000000000003</v>
+      </c>
+      <c r="O7" s="45">
+        <v>0.1032</v>
+      </c>
+      <c r="P7" s="46">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="Q7" s="47">
+        <v>12.86</v>
+      </c>
+      <c r="R7" s="45">
+        <v>0.4612</v>
+      </c>
+      <c r="S7" s="47">
+        <v>13.5</v>
+      </c>
+      <c r="T7" s="47">
+        <v>13.5</v>
+      </c>
+      <c r="U7" s="47">
+        <v>1.3</v>
+      </c>
+      <c r="V7" s="47">
+        <v>1.29</v>
+      </c>
+      <c r="W7" s="48">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" ref="X7:X11" si="0">W7/U7</f>
+        <v>0.2976923076923077</v>
+      </c>
+      <c r="Y7" s="7">
+        <f>(O7-g)/(k-g)</f>
+        <v>1.04</v>
+      </c>
+      <c r="Z7" s="7">
+        <f>T7*Y7</f>
+        <v>14.040000000000001</v>
+      </c>
+      <c r="AA7" s="7">
+        <f>PV(Target_return,Holding_Period,-W7,-Z7)</f>
+        <v>7.1781986429039275</v>
+      </c>
+      <c r="AB7" s="7">
+        <f>PV(Entry_yield,Holding_Period,-W7,-Z7)</f>
+        <v>8.9239968200119097</v>
+      </c>
+      <c r="AC7" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-W7,-Z7)</f>
+        <v>10.996993327666086</v>
+      </c>
+      <c r="AD7" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-W7,-Z7)</f>
+        <v>12.391852469176545</v>
+      </c>
+      <c r="AE7" s="13">
+        <v>8.91</v>
+      </c>
+      <c r="AF7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Y6" s="8">
-        <f>Q6/W6</f>
-        <v>4.1453566621803502E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B7" s="18" t="s">
+      <c r="AG7" s="5">
+        <f>W7/AE7</f>
+        <v>4.3434343434343436E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="17">
+      <c r="E8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="9">
         <v>45930</v>
       </c>
-      <c r="G7" s="20">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="H7" s="20">
-        <v>0.25530000000000003</v>
-      </c>
-      <c r="I7" s="20">
-        <v>0.1032</v>
-      </c>
-      <c r="J7" s="21">
-        <v>1.7399999999999999E-2</v>
-      </c>
-      <c r="K7" s="22">
-        <v>12.86</v>
-      </c>
-      <c r="L7" s="20">
-        <v>0.4612</v>
-      </c>
-      <c r="M7" s="22">
-        <v>13.5</v>
-      </c>
-      <c r="N7" s="22">
-        <v>13.5</v>
-      </c>
-      <c r="O7" s="22">
-        <v>1.3</v>
-      </c>
-      <c r="P7" s="22">
-        <v>1.29</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>0.38700000000000001</v>
-      </c>
-      <c r="R7" s="9">
-        <f t="shared" ref="R7:R11" si="0">Q7/O7</f>
-        <v>0.2976923076923077</v>
-      </c>
-      <c r="S7" s="10">
-        <f>(I7-g)/(k-g)</f>
-        <v>1.584761904761905</v>
-      </c>
-      <c r="T7" s="10">
-        <f t="shared" ref="T7:T11" si="1">N7*S7</f>
-        <v>21.394285714285719</v>
-      </c>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10">
-        <v>8.91</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="8">
-        <f>Q7/W7</f>
-        <v>4.3434343434343436E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B8" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="17">
-        <v>45930</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="H8" s="20">
+      <c r="N8" s="12">
         <v>0.29139999999999999</v>
       </c>
-      <c r="I8" s="20">
+      <c r="O8" s="45">
         <v>0.1047</v>
       </c>
-      <c r="J8" s="21">
+      <c r="P8" s="46">
         <v>1.5900000000000001E-2</v>
       </c>
-      <c r="K8" s="22">
+      <c r="Q8" s="47">
         <v>16.38</v>
       </c>
-      <c r="L8" s="20">
+      <c r="R8" s="45">
         <v>0.40100000000000002</v>
       </c>
-      <c r="M8" s="22">
+      <c r="S8" s="47">
         <v>8.59</v>
       </c>
-      <c r="N8" s="22">
+      <c r="T8" s="47">
         <v>8.59</v>
       </c>
-      <c r="O8" s="22">
+      <c r="U8" s="47">
         <v>0.78</v>
       </c>
-      <c r="P8" s="22">
+      <c r="V8" s="47">
         <v>0.7</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="W8" s="48">
         <v>0.23799999999999999</v>
       </c>
-      <c r="R8" s="9">
+      <c r="X8" s="6">
         <f t="shared" si="0"/>
         <v>0.3051282051282051</v>
       </c>
-      <c r="S8" s="10">
-        <f>(I8-g)/(k-g)</f>
-        <v>1.6133333333333335</v>
-      </c>
-      <c r="T8" s="10">
-        <f t="shared" si="1"/>
-        <v>13.858533333333334</v>
-      </c>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10">
+      <c r="Y8" s="7">
+        <f>(O8-g)/(k-g)</f>
+        <v>1.0587499999999999</v>
+      </c>
+      <c r="Z8" s="7">
+        <f>T8*Y8</f>
+        <v>9.0946624999999983</v>
+      </c>
+      <c r="AA8" s="7">
+        <f>PV(Target_return,Holding_Period,-W8,-Z8)</f>
+        <v>4.6265933847916285</v>
+      </c>
+      <c r="AB8" s="7">
+        <f>PV(Entry_yield,Holding_Period,-W8,-Z8)</f>
+        <v>5.7539875964897522</v>
+      </c>
+      <c r="AC8" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-W8,-Z8)</f>
+        <v>7.0928934118103841</v>
+      </c>
+      <c r="AD8" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-W8,-Z8)</f>
+        <v>7.9939041555159687</v>
+      </c>
+      <c r="AE8" s="13">
         <v>6.96</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="AF8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="8">
-        <f>Q8/W8</f>
+      <c r="AG8" s="5">
+        <f>W8/AE8</f>
         <v>3.4195402298850576E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="18" t="s">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="17">
+      <c r="E9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="9">
         <v>45930</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12">
         <v>1.26E-2</v>
       </c>
-      <c r="H9" s="20">
+      <c r="N9" s="12">
         <v>0.27</v>
       </c>
-      <c r="I9" s="20">
+      <c r="O9" s="45">
         <v>0.09</v>
       </c>
-      <c r="J9" s="21">
+      <c r="P9" s="46">
         <v>1.6E-2</v>
       </c>
-      <c r="K9" s="22">
+      <c r="Q9" s="47">
         <v>12.5</v>
       </c>
-      <c r="L9" s="20">
+      <c r="R9" s="45">
         <v>0.38500000000000001</v>
       </c>
-      <c r="M9" s="22">
+      <c r="S9" s="47">
         <v>9.1199999999999992</v>
       </c>
-      <c r="N9" s="22">
+      <c r="T9" s="47">
         <v>9.1199999999999992</v>
       </c>
-      <c r="O9" s="22">
+      <c r="U9" s="47">
         <v>0.75</v>
       </c>
-      <c r="P9" s="22">
+      <c r="V9" s="47">
         <v>0.72</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="W9" s="48">
         <v>0.22900000000000001</v>
       </c>
-      <c r="R9" s="9">
+      <c r="X9" s="6">
         <f t="shared" si="0"/>
         <v>0.30533333333333335</v>
       </c>
-      <c r="S9" s="10">
-        <f>(I9-g)/(k-g)</f>
-        <v>1.3333333333333335</v>
-      </c>
-      <c r="T9" s="10">
-        <f t="shared" si="1"/>
-        <v>12.16</v>
-      </c>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10">
+      <c r="Y9" s="7">
+        <f>(O9-g)/(k-g)</f>
+        <v>0.87499999999999989</v>
+      </c>
+      <c r="Z9" s="7">
+        <f>T9*Y9</f>
+        <v>7.9799999999999986</v>
+      </c>
+      <c r="AA9" s="7">
+        <f>PV(Target_return,Holding_Period,-W9,-Z9)</f>
+        <v>4.0964553657679277</v>
+      </c>
+      <c r="AB9" s="7">
+        <f>PV(Entry_yield,Holding_Period,-W9,-Z9)</f>
+        <v>5.0912031855130682</v>
+      </c>
+      <c r="AC9" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-W9,-Z9)</f>
+        <v>6.2722340520980744</v>
+      </c>
+      <c r="AD9" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-W9,-Z9)</f>
+        <v>7.0668442393416715</v>
+      </c>
+      <c r="AE9" s="13">
         <v>5.38</v>
       </c>
-      <c r="X9" s="10" t="s">
+      <c r="AF9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="8">
-        <f>Q9/W9</f>
+      <c r="AG9" s="5">
+        <f>W9/AE9</f>
         <v>4.2565055762081784E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="18" t="s">
+    <row r="10" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="17">
+      <c r="E10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="9">
         <v>45930</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H10" s="20">
+      <c r="N10" s="12">
         <v>0.3</v>
       </c>
-      <c r="I10" s="20">
+      <c r="O10" s="45">
         <v>8.7400000000000005E-2</v>
       </c>
-      <c r="J10" s="21">
+      <c r="P10" s="46">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="K10" s="22">
+      <c r="Q10" s="47">
         <v>12.64</v>
       </c>
-      <c r="L10" s="20">
+      <c r="R10" s="45">
         <v>0.47599999999999998</v>
       </c>
-      <c r="M10" s="22">
+      <c r="S10" s="47">
         <v>36.89</v>
       </c>
-      <c r="N10" s="22">
+      <c r="T10" s="47">
         <v>36.89</v>
       </c>
-      <c r="O10" s="22">
+      <c r="U10" s="47">
         <v>3.21</v>
       </c>
-      <c r="P10" s="22">
+      <c r="V10" s="47">
         <v>3.21</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="W10" s="49">
         <v>1.06</v>
       </c>
-      <c r="R10" s="9">
+      <c r="X10" s="6">
         <f t="shared" si="0"/>
         <v>0.33021806853582558</v>
       </c>
-      <c r="S10" s="10">
-        <f>(I10-g)/(k-g)</f>
-        <v>1.283809523809524</v>
-      </c>
-      <c r="T10" s="10">
-        <f t="shared" si="1"/>
-        <v>47.359733333333338</v>
-      </c>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10">
+      <c r="Y10" s="7">
+        <f>(O10-g)/(k-g)</f>
+        <v>0.84250000000000003</v>
+      </c>
+      <c r="Z10" s="7">
+        <f>T10*Y10</f>
+        <v>31.079825000000003</v>
+      </c>
+      <c r="AA10" s="7">
+        <f>PV(Target_return,Holding_Period,-W10,-Z10)</f>
+        <v>16.262142670676731</v>
+      </c>
+      <c r="AB10" s="7">
+        <f>PV(Entry_yield,Holding_Period,-W10,-Z10)</f>
+        <v>20.182489671469853</v>
+      </c>
+      <c r="AC10" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-W10,-Z10)</f>
+        <v>24.834146895326256</v>
+      </c>
+      <c r="AD10" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-W10,-Z10)</f>
+        <v>27.962510785925137</v>
+      </c>
+      <c r="AE10" s="13">
         <v>20.09</v>
       </c>
-      <c r="X10" s="10" t="s">
+      <c r="AF10" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Y10" s="8">
-        <f>Q10/W10</f>
+      <c r="AG10" s="5">
+        <f>W10/AE10</f>
         <v>5.2762568442010951E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B11" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="18" t="s">
+    <row r="11" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="17">
+      <c r="E11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="9">
         <v>45930</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="H11" s="20">
+      <c r="N11" s="12">
         <v>0.32</v>
       </c>
-      <c r="I11" s="20">
+      <c r="O11" s="45">
         <v>7.9600000000000004E-2</v>
       </c>
-      <c r="J11" s="21">
+      <c r="P11" s="46">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="K11" s="22">
+      <c r="Q11" s="47">
         <v>16.3</v>
       </c>
-      <c r="L11" s="20">
+      <c r="R11" s="45">
         <v>0.252</v>
       </c>
-      <c r="M11" s="22">
+      <c r="S11" s="47">
         <v>8.44</v>
       </c>
-      <c r="N11" s="22">
+      <c r="T11" s="47">
         <v>8.44</v>
       </c>
-      <c r="O11" s="22">
+      <c r="U11" s="47">
         <v>0.76</v>
       </c>
-      <c r="P11" s="22">
+      <c r="V11" s="47">
         <v>0.76</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="W11" s="49">
         <v>0.24</v>
       </c>
-      <c r="R11" s="9">
+      <c r="X11" s="6">
         <f t="shared" si="0"/>
         <v>0.31578947368421051</v>
       </c>
-      <c r="S11" s="10">
-        <f>(I11-g)/(k-g)</f>
-        <v>1.1352380952380954</v>
-      </c>
-      <c r="T11" s="10">
-        <f t="shared" si="1"/>
-        <v>9.5814095238095245</v>
-      </c>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10">
+      <c r="Y11" s="7">
+        <f>(O11-g)/(k-g)</f>
+        <v>0.745</v>
+      </c>
+      <c r="Z11" s="7">
+        <f>T11*Y11</f>
+        <v>6.2877999999999998</v>
+      </c>
+      <c r="AA11" s="7">
+        <f>PV(Target_return,Holding_Period,-W11,-Z11)</f>
+        <v>3.3367680649023743</v>
+      </c>
+      <c r="AB11" s="7">
+        <f>PV(Entry_yield,Holding_Period,-W11,-Z11)</f>
+        <v>4.136903185611728</v>
+      </c>
+      <c r="AC11" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-W11,-Z11)</f>
+        <v>5.0858707494237514</v>
+      </c>
+      <c r="AD11" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-W11,-Z11)</f>
+        <v>5.7238783153986832</v>
+      </c>
+      <c r="AE11" s="13">
         <v>5.17</v>
       </c>
-      <c r="X11" s="10" t="s">
+      <c r="AF11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Y11" s="8">
-        <f>Q11/W11</f>
+      <c r="AG11" s="5">
+        <f>W11/AE11</f>
         <v>4.6421663442940041E-2</v>
       </c>
     </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="X12" s="19"/>
+      <c r="AA12" s="18"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="18"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:L3"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="W3:Y3"/>
+  <dataConsolidate/>
+  <mergeCells count="6">
+    <mergeCell ref="S3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="L3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7770292-F970-4AA4-8488-3B55C8DAB788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FF9D08-A2B1-44E9-AA16-CAAAB78307D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,8 @@
     <definedName name="Benchmark_yield">Assumptions!$C$8</definedName>
     <definedName name="Entry_yield">Assumptions!$C$7</definedName>
     <definedName name="g">Assumptions!$C$4</definedName>
+    <definedName name="HKDCNY">Assumptions!$C$13</definedName>
+    <definedName name="HKDUSD">Assumptions!$C$12</definedName>
     <definedName name="Holding_Period">Assumptions!$C$5</definedName>
     <definedName name="k">Assumptions!$C$3</definedName>
     <definedName name="Target_return">Assumptions!$C$6</definedName>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="132">
   <si>
     <t>Name</t>
   </si>
@@ -110,9 +112,6 @@
     <t>公司名称</t>
   </si>
   <si>
-    <t>每股净资产</t>
-  </si>
-  <si>
     <t>HK:1398 / SH:601398</t>
   </si>
   <si>
@@ -132,9 +131,6 @@
   </si>
   <si>
     <t>Trading Currency</t>
-  </si>
-  <si>
-    <t>listed in China</t>
   </si>
   <si>
     <t>YYYY-MM-DD</t>
@@ -150,9 +146,6 @@
 per share</t>
   </si>
   <si>
-    <t>From last Financial year</t>
-  </si>
-  <si>
     <t>派息率</t>
   </si>
   <si>
@@ -171,9 +164,6 @@
     <t>Tangible Common Equity per Share</t>
   </si>
   <si>
-    <t>Common Equity per share</t>
-  </si>
-  <si>
     <t>ROTCE = Core Net income ÷ Tangible common equity (goodwill &amp; intangibles stripped out).</t>
   </si>
   <si>
@@ -183,9 +173,6 @@
     <t>ROTCE</t>
   </si>
   <si>
-    <t>Total Assets/Total Equity</t>
-  </si>
-  <si>
     <t>DuPont for ROTCE</t>
   </si>
   <si>
@@ -237,12 +224,6 @@
     <t>Company Info.</t>
   </si>
   <si>
-    <t>Per Share Metrics</t>
-  </si>
-  <si>
-    <t>上一个财年EPS</t>
-  </si>
-  <si>
     <t>上一个财年核心EPS</t>
   </si>
   <si>
@@ -262,9 +243,6 @@
   </si>
   <si>
     <t>Valuation</t>
-  </si>
-  <si>
-    <t>隐含公允市净率</t>
   </si>
   <si>
     <t>隐含公允股价</t>
@@ -369,34 +347,18 @@
     <t>Last FY Core shareholders' EPS</t>
   </si>
   <si>
-    <t>Last FY 
-shareholders' EPS</t>
-  </si>
-  <si>
     <t>有形净资产</t>
   </si>
   <si>
     <t>核心净利润</t>
   </si>
   <si>
-    <t>Last FY Core shareholders' Net Income</t>
-  </si>
-  <si>
     <t>收入</t>
   </si>
   <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>Total Assets</t>
-  </si>
-  <si>
     <t>总资产</t>
   </si>
   <si>
-    <t>Tangible Common Equity (TBV)</t>
-  </si>
-  <si>
     <t>CET1</t>
   </si>
   <si>
@@ -409,18 +371,80 @@
     <t>Profibilities and Efficiency</t>
   </si>
   <si>
-    <t>Share Outstanding</t>
-  </si>
-  <si>
     <t>股数</t>
+  </si>
+  <si>
+    <t>HSBC</t>
+  </si>
+  <si>
+    <t>HK:0005</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Total Assets
+(in Millions)</t>
+  </si>
+  <si>
+    <t>Tangible Common Equity (TBV)
+(in Millions)</t>
+  </si>
+  <si>
+    <t>Revenue
+(in Millions)</t>
+  </si>
+  <si>
+    <t>Last FY Core shareholders' Net Income (in Millions)</t>
+  </si>
+  <si>
+    <t>From End Date of Last Statement</t>
+  </si>
+  <si>
+    <t>From the Last Annual Report</t>
+  </si>
+  <si>
+    <t>Listing Symbol</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>Latest Share Outstanding</t>
+  </si>
+  <si>
+    <t>Total Assets/TBV</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Forex</t>
+  </si>
+  <si>
+    <t>HKDUSD</t>
+  </si>
+  <si>
+    <t>HKDCNY</t>
+  </si>
+  <si>
+    <t>Forex Pair</t>
+  </si>
+  <si>
+    <t>Forex Rate</t>
+  </si>
+  <si>
+    <t>公允市净率倍数</t>
+  </si>
+  <si>
+    <t>From last Financial year (in trading currency)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
@@ -651,8 +675,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -681,8 +703,38 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -690,66 +742,38 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1075,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D2ED91-59EB-437C-A4C2-C114238F9C2A}">
-  <dimension ref="B2:D24"/>
+  <dimension ref="B2:D30"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -1092,12 +1116,12 @@
         <v>2</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C3" s="14">
         <v>0.1</v>
@@ -1106,18 +1130,18 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C4" s="14">
         <v>0.02</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C5" s="15">
         <v>3</v>
@@ -1126,7 +1150,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C6" s="14">
         <v>0.29465259038036606</v>
@@ -1135,7 +1159,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C7" s="14">
         <v>0.20075184365903009</v>
@@ -1144,7 +1168,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C8" s="14">
         <v>0.1174</v>
@@ -1153,61 +1177,100 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C9" s="14">
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="D9" s="1"/>
     </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="52">
+        <v>7.8</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="52">
+        <v>0.89</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="1"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" s="1"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B19" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B25" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1218,22 +1281,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6E8AA2-48F2-4368-B9E3-BA821DC1A767}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:AG12"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="11" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1" collapsed="1"/>
-    <col min="13" max="18" width="18.6640625" customWidth="1"/>
-    <col min="19" max="24" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="18.796875" customWidth="1" collapsed="1"/>
-    <col min="26" max="33" width="18.796875" customWidth="1"/>
+    <col min="5" max="12" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="14" max="19" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="18.6640625" customWidth="1" collapsed="1"/>
+    <col min="21" max="22" width="18.6640625" customWidth="1"/>
+    <col min="23" max="30" width="18.796875" customWidth="1"/>
+    <col min="31" max="32" width="18.796875" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:33" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -1242,318 +1310,320 @@
         <v>17</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="P2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="R2" s="2" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="U2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
       <c r="AA2" s="16"/>
       <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
     </row>
     <row r="3" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB3" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC3" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="41"/>
+    </row>
+    <row r="4" spans="2:33" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="B4" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="V4" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC4" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF4" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG4" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B5" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="R5" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="33" t="s">
+      <c r="S5" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="V5" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="W5" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="X5" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y5" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z5" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AB3" s="33" t="s">
+      <c r="AB5" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AC3" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD3" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE3" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-    </row>
-    <row r="4" spans="2:33" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="J4" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="S4" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="U4" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="V4" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="W4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="X4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y4" s="25" t="s">
+      <c r="AC5" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA4" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB4" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC4" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD4" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE4" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF4" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.45">
-      <c r="B5" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="L5" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="O5" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="P5" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="S5" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="28" t="s">
+      <c r="AD5" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE5" s="22"/>
+      <c r="AF5" s="22"/>
+      <c r="AG5" s="22" t="s">
         <v>70</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="W5" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="X5" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y5" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z5" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA5" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB5" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC5" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD5" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE5" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF5" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG5" s="24" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B6" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>4</v>
@@ -1562,92 +1632,112 @@
         <v>3</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F6" s="9">
-        <v>45930</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+        <v>45838</v>
+      </c>
+      <c r="G6" s="49">
+        <v>48821746</v>
+      </c>
+      <c r="H6" s="49">
+        <v>3969841</v>
+      </c>
+      <c r="I6" s="49">
+        <v>820000</v>
+      </c>
+      <c r="J6" s="49">
+        <v>366900</v>
+      </c>
+      <c r="K6" s="49">
+        <v>356406000000</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0.308</v>
+      </c>
       <c r="M6" s="12">
-        <v>1.2800000000000001E-2</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="N6" s="12">
-        <v>0.26550000000000001</v>
-      </c>
-      <c r="O6" s="45">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="P6" s="46">
-        <v>1.6E-2</v>
-      </c>
-      <c r="Q6" s="47">
-        <v>12.49</v>
-      </c>
-      <c r="R6" s="45">
-        <v>0.44519999999999998</v>
-      </c>
-      <c r="S6" s="47">
-        <v>11.7</v>
-      </c>
-      <c r="T6" s="47">
-        <v>11.7</v>
-      </c>
-      <c r="U6" s="47">
-        <v>0.99</v>
-      </c>
-      <c r="V6" s="47">
-        <v>0.94</v>
-      </c>
-      <c r="W6" s="48">
-        <v>0.308</v>
-      </c>
-      <c r="X6" s="6">
-        <f>W6/U6</f>
-        <v>0.31111111111111112</v>
+        <v>1.55E-2</v>
+      </c>
+      <c r="O6" s="12">
+        <v>0.25269999999999998</v>
+      </c>
+      <c r="P6" s="36">
+        <f t="shared" ref="P6:P8" si="0">J6/H6</f>
+        <v>9.2421837549665084E-2</v>
+      </c>
+      <c r="Q6" s="37">
+        <f>I6/G6</f>
+        <v>1.679579423480676E-2</v>
+      </c>
+      <c r="R6" s="38">
+        <f>G6/H6</f>
+        <v>12.298161563649527</v>
+      </c>
+      <c r="S6" s="36">
+        <f>J6/I6</f>
+        <v>0.44743902439024391</v>
+      </c>
+      <c r="T6" s="38">
+        <f t="shared" ref="T6:T11" si="1">H6/(K6/1000000)*$AF6</f>
+        <v>11.138535827118512</v>
+      </c>
+      <c r="U6" s="38">
+        <f t="shared" ref="U6:U11" si="2">J6/(K6/1000000)*$AF6</f>
+        <v>1.0294439487550715</v>
+      </c>
+      <c r="V6" s="6">
+        <f>L6/U6</f>
+        <v>0.29919064595257561</v>
+      </c>
+      <c r="W6" s="7">
+        <f>(P6-g)/(k-g)</f>
+        <v>0.90527296937081347</v>
+      </c>
+      <c r="X6" s="7">
+        <f>T6*W6</f>
+        <v>10.083415402658765</v>
       </c>
       <c r="Y6" s="7">
-        <f>(O6-g)/(k-g)</f>
-        <v>0.91249999999999998</v>
+        <f>PV(Target_return,Holding_Period,-L6,-X6)</f>
+        <v>5.2103294940404279</v>
       </c>
       <c r="Z6" s="7">
-        <f>T6*Y6</f>
-        <v>10.67625</v>
+        <f>PV(Entry_yield,Holding_Period,-L6,-X6)</f>
+        <v>6.4723886829985986</v>
       </c>
       <c r="AA6" s="7">
-        <f>PV(Target_return,Holding_Period,-W6,-Z6)</f>
-        <v>5.4835251610179547</v>
+        <f>PV(Benchmark_yield,Holding_Period,-L6,-X6)</f>
+        <v>7.9704745497303149</v>
       </c>
       <c r="AB6" s="7">
-        <f>PV(Entry_yield,Holding_Period,-W6,-Z6)</f>
-        <v>6.8148202193689871</v>
-      </c>
-      <c r="AC6" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-W6,-Z6)</f>
-        <v>8.3953949087133903</v>
-      </c>
-      <c r="AD6" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-W6,-Z6)</f>
-        <v>9.4588096710841096</v>
-      </c>
-      <c r="AE6" s="13">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L6,-X6)</f>
+        <v>8.9782562888960111</v>
+      </c>
+      <c r="AC6" s="13">
         <v>7.43</v>
       </c>
-      <c r="AF6" s="7" t="s">
+      <c r="AD6" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="AE6" s="7" t="str">
+        <f>AD6&amp;D6</f>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AF6" s="7">
+        <f>IFERROR(VLOOKUP(AE6,Assumptions!B$12:C$13,2),1)</f>
+        <v>1</v>
+      </c>
       <c r="AG6" s="5">
-        <f>W6/AE6</f>
+        <f>L6/AC6</f>
         <v>4.1453566621803502E-2</v>
       </c>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B7" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>5</v>
@@ -1656,92 +1746,112 @@
         <v>3</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F7" s="9">
-        <v>45930</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+        <v>45838</v>
+      </c>
+      <c r="G7" s="49">
+        <v>40571149</v>
+      </c>
+      <c r="H7" s="49">
+        <v>3322127</v>
+      </c>
+      <c r="I7" s="49">
+        <v>728570</v>
+      </c>
+      <c r="J7" s="49">
+        <v>335577</v>
+      </c>
+      <c r="K7" s="49">
+        <v>250011000000</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0.38700000000000001</v>
+      </c>
       <c r="M7" s="12">
-        <v>1.3599999999999999E-2</v>
+        <v>0.14480000000000001</v>
       </c>
       <c r="N7" s="12">
-        <v>0.25530000000000003</v>
-      </c>
-      <c r="O7" s="45">
-        <v>0.1032</v>
-      </c>
-      <c r="P7" s="46">
-        <v>1.7399999999999999E-2</v>
-      </c>
-      <c r="Q7" s="47">
-        <v>12.86</v>
-      </c>
-      <c r="R7" s="45">
-        <v>0.4612</v>
-      </c>
-      <c r="S7" s="47">
-        <v>13.5</v>
-      </c>
-      <c r="T7" s="47">
-        <v>13.5</v>
-      </c>
-      <c r="U7" s="47">
-        <v>1.3</v>
-      </c>
-      <c r="V7" s="47">
-        <v>1.29</v>
-      </c>
-      <c r="W7" s="48">
-        <v>0.38700000000000001</v>
-      </c>
-      <c r="X7" s="6">
-        <f t="shared" ref="X7:X11" si="0">W7/U7</f>
-        <v>0.2976923076923077</v>
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="O7" s="12">
+        <v>0.29580000000000001</v>
+      </c>
+      <c r="P7" s="36">
+        <f t="shared" si="0"/>
+        <v>0.10101269457790145</v>
+      </c>
+      <c r="Q7" s="37">
+        <f t="shared" ref="Q7:Q12" si="3">I7/G7</f>
+        <v>1.7957835012264504E-2</v>
+      </c>
+      <c r="R7" s="38">
+        <f t="shared" ref="R7:R12" si="4">G7/H7</f>
+        <v>12.212401572847757</v>
+      </c>
+      <c r="S7" s="36">
+        <f t="shared" ref="S7:S12" si="5">J7/I7</f>
+        <v>0.4605967854838931</v>
+      </c>
+      <c r="T7" s="38">
+        <f t="shared" si="1"/>
+        <v>13.28792333137342</v>
+      </c>
+      <c r="U7" s="38">
+        <f t="shared" si="2"/>
+        <v>1.3422489410465939</v>
+      </c>
+      <c r="V7" s="6">
+        <f>L7/U7</f>
+        <v>0.28832207511241836</v>
+      </c>
+      <c r="W7" s="7">
+        <f>(P7-g)/(k-g)</f>
+        <v>1.012658682223768</v>
+      </c>
+      <c r="X7" s="7">
+        <f>T7*W7</f>
+        <v>13.45613093023907</v>
       </c>
       <c r="Y7" s="7">
-        <f>(O7-g)/(k-g)</f>
-        <v>1.04</v>
+        <f>PV(Target_return,Holding_Period,-L7,-X7)</f>
+        <v>6.9091345554564931</v>
       </c>
       <c r="Z7" s="7">
-        <f>T7*Y7</f>
-        <v>14.040000000000001</v>
+        <f>PV(Entry_yield,Holding_Period,-L7,-X7)</f>
+        <v>8.5867439277312272</v>
       </c>
       <c r="AA7" s="7">
-        <f>PV(Target_return,Holding_Period,-W7,-Z7)</f>
-        <v>7.1781986429039275</v>
+        <f>PV(Benchmark_yield,Holding_Period,-L7,-X7)</f>
+        <v>10.578499103755053</v>
       </c>
       <c r="AB7" s="7">
-        <f>PV(Entry_yield,Holding_Period,-W7,-Z7)</f>
-        <v>8.9239968200119097</v>
-      </c>
-      <c r="AC7" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-W7,-Z7)</f>
-        <v>10.996993327666086</v>
-      </c>
-      <c r="AD7" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-W7,-Z7)</f>
-        <v>12.391852469176545</v>
-      </c>
-      <c r="AE7" s="13">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L7,-X7)</f>
+        <v>11.918566568712924</v>
+      </c>
+      <c r="AC7" s="13">
         <v>8.91</v>
       </c>
-      <c r="AF7" s="7" t="s">
+      <c r="AD7" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="AE7" s="7" t="str">
+        <f t="shared" ref="AE7:AE12" si="6">AD7&amp;D7</f>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AF7" s="7">
+        <f>IFERROR(VLOOKUP(AE7,Assumptions!B$12:C$13,2),1)</f>
+        <v>1</v>
+      </c>
       <c r="AG7" s="5">
-        <f>W7/AE7</f>
+        <f>L7/AC7</f>
         <v>4.3434343434343436E-2</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>6</v>
@@ -1750,92 +1860,112 @@
         <v>3</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F8" s="9">
-        <v>45930</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+        <v>45838</v>
+      </c>
+      <c r="G8" s="49">
+        <v>43238135</v>
+      </c>
+      <c r="H8" s="49">
+        <v>3090808</v>
+      </c>
+      <c r="I8" s="49">
+        <v>711416</v>
+      </c>
+      <c r="J8" s="49">
+        <v>282671</v>
+      </c>
+      <c r="K8" s="49">
+        <v>349983000000</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0.23799999999999999</v>
+      </c>
       <c r="M8" s="12">
-        <v>1.2999999999999999E-2</v>
+        <v>0.1163</v>
       </c>
       <c r="N8" s="12">
-        <v>0.29139999999999999</v>
-      </c>
-      <c r="O8" s="45">
-        <v>0.1047</v>
-      </c>
-      <c r="P8" s="46">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="Q8" s="47">
-        <v>16.38</v>
-      </c>
-      <c r="R8" s="45">
-        <v>0.40100000000000002</v>
-      </c>
-      <c r="S8" s="47">
-        <v>8.59</v>
-      </c>
-      <c r="T8" s="47">
-        <v>8.59</v>
-      </c>
-      <c r="U8" s="47">
-        <v>0.78</v>
-      </c>
-      <c r="V8" s="47">
-        <v>0.7</v>
-      </c>
-      <c r="W8" s="48">
-        <v>0.23799999999999999</v>
-      </c>
-      <c r="X8" s="6">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="P8" s="36">
         <f t="shared" si="0"/>
-        <v>0.3051282051282051</v>
+        <v>9.1455373481626814E-2</v>
+      </c>
+      <c r="Q8" s="37">
+        <f t="shared" si="3"/>
+        <v>1.6453438613853257E-2</v>
+      </c>
+      <c r="R8" s="38">
+        <f t="shared" si="4"/>
+        <v>13.989265913638116</v>
+      </c>
+      <c r="S8" s="36">
+        <f t="shared" si="5"/>
+        <v>0.39733573605316719</v>
+      </c>
+      <c r="T8" s="38">
+        <f t="shared" si="1"/>
+        <v>8.831308949291822</v>
+      </c>
+      <c r="U8" s="38">
+        <f t="shared" si="2"/>
+        <v>0.80767065828911688</v>
+      </c>
+      <c r="V8" s="6">
+        <f>L8/U8</f>
+        <v>0.2946745651304874</v>
+      </c>
+      <c r="W8" s="7">
+        <f>(P8-g)/(k-g)</f>
+        <v>0.89319216852033512</v>
+      </c>
+      <c r="X8" s="7">
+        <f>T8*W8</f>
+        <v>7.8880559912910044</v>
       </c>
       <c r="Y8" s="7">
-        <f>(O8-g)/(k-g)</f>
-        <v>1.0587499999999999</v>
+        <f>PV(Target_return,Holding_Period,-L8,-X8)</f>
+        <v>4.0705535190271149</v>
       </c>
       <c r="Z8" s="7">
-        <f>T8*Y8</f>
-        <v>9.0946624999999983</v>
+        <f>PV(Entry_yield,Holding_Period,-L8,-X8)</f>
+        <v>5.0570307683545934</v>
       </c>
       <c r="AA8" s="7">
-        <f>PV(Target_return,Holding_Period,-W8,-Z8)</f>
-        <v>4.6265933847916285</v>
+        <f>PV(Benchmark_yield,Holding_Period,-L8,-X8)</f>
+        <v>6.2280456564139071</v>
       </c>
       <c r="AB8" s="7">
-        <f>PV(Entry_yield,Holding_Period,-W8,-Z8)</f>
-        <v>5.7539875964897522</v>
-      </c>
-      <c r="AC8" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-W8,-Z8)</f>
-        <v>7.0928934118103841</v>
-      </c>
-      <c r="AD8" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-W8,-Z8)</f>
-        <v>7.9939041555159687</v>
-      </c>
-      <c r="AE8" s="13">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L8,-X8)</f>
+        <v>7.0158255458485144</v>
+      </c>
+      <c r="AC8" s="13">
         <v>6.96</v>
       </c>
-      <c r="AF8" s="7" t="s">
+      <c r="AD8" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="AE8" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AF8" s="7">
+        <f>IFERROR(VLOOKUP(AE8,Assumptions!B$12:C$13,2),1)</f>
+        <v>1</v>
+      </c>
       <c r="AG8" s="5">
-        <f>W8/AE8</f>
+        <f>L8/AC8</f>
         <v>3.4195402298850576E-2</v>
       </c>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B9" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>7</v>
@@ -1844,92 +1974,112 @@
         <v>3</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F9" s="9">
-        <v>45930</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+        <v>45838</v>
+      </c>
+      <c r="G9" s="49">
+        <v>35061299</v>
+      </c>
+      <c r="H9" s="49">
+        <v>2816231</v>
+      </c>
+      <c r="I9" s="49">
+        <v>632771</v>
+      </c>
+      <c r="J9" s="49">
+        <v>252700</v>
+      </c>
+      <c r="K9" s="49">
+        <v>294388000000</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0.22900000000000001</v>
+      </c>
       <c r="M9" s="12">
-        <v>1.26E-2</v>
+        <v>0.122</v>
       </c>
       <c r="N9" s="12">
-        <v>0.27</v>
-      </c>
-      <c r="O9" s="45">
-        <v>0.09</v>
-      </c>
-      <c r="P9" s="46">
-        <v>1.6E-2</v>
-      </c>
-      <c r="Q9" s="47">
-        <v>12.5</v>
-      </c>
-      <c r="R9" s="45">
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="S9" s="47">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="T9" s="47">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="U9" s="47">
-        <v>0.75</v>
-      </c>
-      <c r="V9" s="47">
-        <v>0.72</v>
-      </c>
-      <c r="W9" s="48">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="X9" s="6">
-        <f t="shared" si="0"/>
-        <v>0.30533333333333335</v>
+        <v>1.4E-2</v>
+      </c>
+      <c r="O9" s="12">
+        <v>0.28770000000000001</v>
+      </c>
+      <c r="P9" s="36">
+        <f>J9/H9</f>
+        <v>8.9729855256901872E-2</v>
+      </c>
+      <c r="Q9" s="37">
+        <f t="shared" si="3"/>
+        <v>1.8047562926861323E-2</v>
+      </c>
+      <c r="R9" s="38">
+        <f t="shared" si="4"/>
+        <v>12.449724117091247</v>
+      </c>
+      <c r="S9" s="36">
+        <f t="shared" si="5"/>
+        <v>0.39935458483400788</v>
+      </c>
+      <c r="T9" s="38">
+        <f t="shared" si="1"/>
+        <v>9.5663919724988791</v>
+      </c>
+      <c r="U9" s="38">
+        <f t="shared" si="2"/>
+        <v>0.85839096702311235</v>
+      </c>
+      <c r="V9" s="6">
+        <f>L9/U9</f>
+        <v>0.26677820340324498</v>
+      </c>
+      <c r="W9" s="7">
+        <f>(P9-g)/(k-g)</f>
+        <v>0.87162319071127337</v>
+      </c>
+      <c r="X9" s="7">
+        <f>T9*W9</f>
+        <v>8.3382890946641854</v>
       </c>
       <c r="Y9" s="7">
-        <f>(O9-g)/(k-g)</f>
-        <v>0.87499999999999989</v>
+        <f>PV(Target_return,Holding_Period,-L9,-X9)</f>
+        <v>4.2615655476408243</v>
       </c>
       <c r="Z9" s="7">
-        <f>T9*Y9</f>
-        <v>7.9799999999999986</v>
+        <f>PV(Entry_yield,Holding_Period,-L9,-X9)</f>
+        <v>5.2981571752107932</v>
       </c>
       <c r="AA9" s="7">
-        <f>PV(Target_return,Holding_Period,-W9,-Z9)</f>
-        <v>4.0964553657679277</v>
+        <f>PV(Benchmark_yield,Holding_Period,-L9,-X9)</f>
+        <v>6.5290414844024953</v>
       </c>
       <c r="AB9" s="7">
-        <f>PV(Entry_yield,Holding_Period,-W9,-Z9)</f>
-        <v>5.0912031855130682</v>
-      </c>
-      <c r="AC9" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-W9,-Z9)</f>
-        <v>6.2722340520980744</v>
-      </c>
-      <c r="AD9" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-W9,-Z9)</f>
-        <v>7.0668442393416715</v>
-      </c>
-      <c r="AE9" s="13">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L9,-X9)</f>
+        <v>7.3572743812635029</v>
+      </c>
+      <c r="AC9" s="13">
         <v>5.38</v>
       </c>
-      <c r="AF9" s="7" t="s">
+      <c r="AD9" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="AE9" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AF9" s="7">
+        <f>IFERROR(VLOOKUP(AE9,Assumptions!B$12:C$13,2),1)</f>
+        <v>1</v>
+      </c>
       <c r="AG9" s="5">
-        <f>W9/AE9</f>
+        <f>L9/AC9</f>
         <v>4.2565055762081784E-2</v>
       </c>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>8</v>
@@ -1938,92 +2088,112 @@
         <v>3</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F10" s="9">
-        <v>45930</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
+        <v>45838</v>
+      </c>
+      <c r="G10" s="49">
+        <v>10510731</v>
+      </c>
+      <c r="H10" s="49">
+        <v>766132</v>
+      </c>
+      <c r="I10" s="49">
+        <v>212226</v>
+      </c>
+      <c r="J10" s="49">
+        <v>77205</v>
+      </c>
+      <c r="K10" s="49">
+        <v>20774000000</v>
+      </c>
+      <c r="L10" s="50">
+        <v>1.06</v>
+      </c>
       <c r="M10" s="12">
-        <v>1.7000000000000001E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="N10" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="O10" s="45">
-        <v>8.7400000000000005E-2</v>
-      </c>
-      <c r="P10" s="46">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="Q10" s="47">
-        <v>12.64</v>
-      </c>
-      <c r="R10" s="45">
+        <v>1.72E-2</v>
+      </c>
+      <c r="O10" s="12">
         <v>0.47599999999999998</v>
       </c>
-      <c r="S10" s="47">
-        <v>36.89</v>
-      </c>
-      <c r="T10" s="47">
-        <v>36.89</v>
-      </c>
-      <c r="U10" s="47">
-        <v>3.21</v>
-      </c>
-      <c r="V10" s="47">
-        <v>3.21</v>
-      </c>
-      <c r="W10" s="49">
-        <v>1.06</v>
-      </c>
-      <c r="X10" s="6">
-        <f t="shared" si="0"/>
-        <v>0.33021806853582558</v>
+      <c r="P10" s="36">
+        <f t="shared" ref="P10:P12" si="7">J10/H10</f>
+        <v>0.10077245174460799</v>
+      </c>
+      <c r="Q10" s="37">
+        <f t="shared" si="3"/>
+        <v>2.0191364425557079E-2</v>
+      </c>
+      <c r="R10" s="38">
+        <f t="shared" si="4"/>
+        <v>13.719216792928634</v>
+      </c>
+      <c r="S10" s="36">
+        <f t="shared" si="5"/>
+        <v>0.36378671793276979</v>
+      </c>
+      <c r="T10" s="38">
+        <f t="shared" si="1"/>
+        <v>36.879368441320885</v>
+      </c>
+      <c r="U10" s="38">
+        <f t="shared" si="2"/>
+        <v>3.716424376624627</v>
+      </c>
+      <c r="V10" s="6">
+        <f>L10/U10</f>
+        <v>0.28522038728061655</v>
+      </c>
+      <c r="W10" s="7">
+        <f>(P10-g)/(k-g)</f>
+        <v>1.0096556468075997</v>
+      </c>
+      <c r="X10" s="7">
+        <f>T10*W10</f>
+        <v>37.235462597477614</v>
       </c>
       <c r="Y10" s="7">
-        <f>(O10-g)/(k-g)</f>
-        <v>0.84250000000000003</v>
+        <f>PV(Target_return,Holding_Period,-L10,-X10)</f>
+        <v>19.098842024353051</v>
       </c>
       <c r="Z10" s="7">
-        <f>T10*Y10</f>
-        <v>31.079825000000003</v>
+        <f>PV(Entry_yield,Holding_Period,-L10,-X10)</f>
+        <v>23.738092615861252</v>
       </c>
       <c r="AA10" s="7">
-        <f>PV(Target_return,Holding_Period,-W10,-Z10)</f>
-        <v>16.262142670676731</v>
+        <f>PV(Benchmark_yield,Holding_Period,-L10,-X10)</f>
+        <v>29.246264118951007</v>
       </c>
       <c r="AB10" s="7">
-        <f>PV(Entry_yield,Holding_Period,-W10,-Z10)</f>
-        <v>20.182489671469853</v>
-      </c>
-      <c r="AC10" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-W10,-Z10)</f>
-        <v>24.834146895326256</v>
-      </c>
-      <c r="AD10" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-W10,-Z10)</f>
-        <v>27.962510785925137</v>
-      </c>
-      <c r="AE10" s="13">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L10,-X10)</f>
+        <v>32.952287833787608</v>
+      </c>
+      <c r="AC10" s="13">
         <v>20.09</v>
       </c>
-      <c r="AF10" s="7" t="s">
+      <c r="AD10" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="AE10" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AF10" s="7">
+        <f>IFERROR(VLOOKUP(AE10,Assumptions!B$12:C$13,2),1)</f>
+        <v>1</v>
+      </c>
       <c r="AG10" s="5">
-        <f>W10/AE10</f>
+        <f>L10/AC10</f>
         <v>5.2762568442010951E-2</v>
       </c>
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B11" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -2032,107 +2202,235 @@
         <v>3</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F11" s="9">
-        <v>45930</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
+        <v>45838</v>
+      </c>
+      <c r="G11" s="49">
+        <v>17084910</v>
+      </c>
+      <c r="H11" s="49">
+        <v>1023006</v>
+      </c>
+      <c r="I11" s="49">
+        <v>349133</v>
+      </c>
+      <c r="J11" s="49">
+        <v>86479</v>
+      </c>
+      <c r="K11" s="49">
+        <v>99161000000</v>
+      </c>
+      <c r="L11" s="50">
+        <v>0.24</v>
+      </c>
       <c r="M11" s="12">
-        <v>1.4E-2</v>
+        <v>9.4799999999999995E-2</v>
       </c>
       <c r="N11" s="12">
-        <v>0.32</v>
-      </c>
-      <c r="O11" s="45">
-        <v>7.9600000000000004E-2</v>
-      </c>
-      <c r="P11" s="46">
-        <v>1.9400000000000001E-2</v>
-      </c>
-      <c r="Q11" s="47">
-        <v>16.3</v>
-      </c>
-      <c r="R11" s="45">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="O11" s="12">
         <v>0.252</v>
       </c>
-      <c r="S11" s="47">
-        <v>8.44</v>
-      </c>
-      <c r="T11" s="47">
-        <v>8.44</v>
-      </c>
-      <c r="U11" s="47">
-        <v>0.76</v>
-      </c>
-      <c r="V11" s="47">
-        <v>0.76</v>
-      </c>
-      <c r="W11" s="49">
-        <v>0.24</v>
-      </c>
-      <c r="X11" s="6">
-        <f t="shared" si="0"/>
-        <v>0.31578947368421051</v>
+      <c r="P11" s="36">
+        <f t="shared" si="7"/>
+        <v>8.4534206055487462E-2</v>
+      </c>
+      <c r="Q11" s="37">
+        <f t="shared" si="3"/>
+        <v>2.0435167642088838E-2</v>
+      </c>
+      <c r="R11" s="38">
+        <f t="shared" si="4"/>
+        <v>16.7006938375728</v>
+      </c>
+      <c r="S11" s="36">
+        <f t="shared" si="5"/>
+        <v>0.24769643660152435</v>
+      </c>
+      <c r="T11" s="38">
+        <f t="shared" si="1"/>
+        <v>10.316616411694113</v>
+      </c>
+      <c r="U11" s="38">
+        <f t="shared" si="2"/>
+        <v>0.87210697754157385</v>
+      </c>
+      <c r="V11" s="6">
+        <f>L11/U11</f>
+        <v>0.27519559661883231</v>
+      </c>
+      <c r="W11" s="7">
+        <f>(P11-g)/(k-g)</f>
+        <v>0.80667757569359322</v>
+      </c>
+      <c r="X11" s="7">
+        <f>T11*W11</f>
+        <v>8.3221831163461442</v>
       </c>
       <c r="Y11" s="7">
-        <f>(O11-g)/(k-g)</f>
-        <v>0.745</v>
+        <f>PV(Target_return,Holding_Period,-L11,-X11)</f>
+        <v>4.2742718051540534</v>
       </c>
       <c r="Z11" s="7">
-        <f>T11*Y11</f>
-        <v>6.2877999999999998</v>
+        <f>PV(Entry_yield,Holding_Period,-L11,-X11)</f>
+        <v>5.3119981264614875</v>
       </c>
       <c r="AA11" s="7">
-        <f>PV(Target_return,Holding_Period,-W11,-Z11)</f>
-        <v>3.3367680649023743</v>
+        <f>PV(Benchmark_yield,Holding_Period,-L11,-X11)</f>
+        <v>6.5440359914386921</v>
       </c>
       <c r="AB11" s="7">
-        <f>PV(Entry_yield,Holding_Period,-W11,-Z11)</f>
-        <v>4.136903185611728</v>
-      </c>
-      <c r="AC11" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-W11,-Z11)</f>
-        <v>5.0858707494237514</v>
-      </c>
-      <c r="AD11" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-W11,-Z11)</f>
-        <v>5.7238783153986832</v>
-      </c>
-      <c r="AE11" s="13">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L11,-X11)</f>
+        <v>7.3729549577050042</v>
+      </c>
+      <c r="AC11" s="13">
         <v>5.17</v>
       </c>
-      <c r="AF11" s="7" t="s">
+      <c r="AD11" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="AE11" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AF11" s="7">
+        <f>IFERROR(VLOOKUP(AE11,Assumptions!B$12:C$13,2),1)</f>
+        <v>1</v>
+      </c>
       <c r="AG11" s="5">
-        <f>W11/AE11</f>
+        <f>L11/AC11</f>
         <v>4.6421663442940041E-2</v>
       </c>
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.45">
-      <c r="X12" s="19"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="18"/>
-      <c r="AD12" s="18"/>
+      <c r="B12" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="9">
+        <v>45838</v>
+      </c>
+      <c r="G12" s="49">
+        <v>3017048</v>
+      </c>
+      <c r="H12" s="49">
+        <v>154295</v>
+      </c>
+      <c r="I12" s="49">
+        <v>51910</v>
+      </c>
+      <c r="J12" s="49">
+        <v>23730</v>
+      </c>
+      <c r="K12" s="49">
+        <v>17918000000</v>
+      </c>
+      <c r="L12" s="50">
+        <f>0.780688+0.779073+0.777313+2.791007</f>
+        <v>5.1280809999999999</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="N12" s="12">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="O12" s="12">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="P12" s="36">
+        <f t="shared" si="7"/>
+        <v>0.15379629929680158</v>
+      </c>
+      <c r="Q12" s="37">
+        <f t="shared" si="3"/>
+        <v>1.7205559871768694E-2</v>
+      </c>
+      <c r="R12" s="38">
+        <f t="shared" si="4"/>
+        <v>19.553763893839722</v>
+      </c>
+      <c r="S12" s="36">
+        <f t="shared" si="5"/>
+        <v>0.45713735311115394</v>
+      </c>
+      <c r="T12" s="38">
+        <f>H12/(K12/1000000)*$AF12</f>
+        <v>67.167150351601748</v>
+      </c>
+      <c r="U12" s="38">
+        <f>J12/(K12/1000000)*$AF12</f>
+        <v>10.330059158388213</v>
+      </c>
+      <c r="V12" s="6">
+        <f>L12/U12</f>
+        <v>0.49642319771575522</v>
+      </c>
+      <c r="W12" s="7">
+        <f>(P12-g)/(k-g)</f>
+        <v>1.6724537412100198</v>
+      </c>
+      <c r="X12" s="7">
+        <f>T12*W12</f>
+        <v>112.33395189195224</v>
+      </c>
+      <c r="Y12" s="7">
+        <f>PV(Target_return,Holding_Period,-L12,-X12)</f>
+        <v>61.150425207160808</v>
+      </c>
+      <c r="Z12" s="7">
+        <f>PV(Entry_yield,Holding_Period,-L12,-X12)</f>
+        <v>75.675539859823033</v>
+      </c>
+      <c r="AA12" s="7">
+        <f>PV(Benchmark_yield,Holding_Period,-L12,-X12)</f>
+        <v>92.888551757648202</v>
+      </c>
+      <c r="AB12" s="7">
+        <f>PV(Base_Cost_of_Equity,Holding_Period,-L12,-X12)</f>
+        <v>104.45468726004771</v>
+      </c>
+      <c r="AC12" s="13">
+        <v>130</v>
+      </c>
+      <c r="AD12" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE12" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HKDUSD</v>
+      </c>
+      <c r="AF12" s="7">
+        <f>IFERROR(VLOOKUP(AE12,Assumptions!B$12:C$13,2),1)</f>
+        <v>7.8</v>
+      </c>
+      <c r="AG12" s="5">
+        <f>L12/AC12</f>
+        <v>3.9446776923076923E-2</v>
+      </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="6">
-    <mergeCell ref="S3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="AC3:AG3"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="E3:K3"/>
-    <mergeCell ref="L3:R3"/>
+    <mergeCell ref="M3:S3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FF9D08-A2B1-44E9-AA16-CAAAB78307D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B520FD-FC66-45AE-B87B-A38F97C09CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -736,6 +736,14 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -766,14 +774,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1199,7 +1199,7 @@
       <c r="B12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="42">
         <v>7.8</v>
       </c>
       <c r="D12" s="1"/>
@@ -1208,19 +1208,19 @@
       <c r="B13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="42">
         <v>0.89</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
-      <c r="C14" s="51"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
-      <c r="C15" s="51"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="1"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.45">
@@ -1289,11 +1289,10 @@
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="12" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="14" max="19" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="18.6640625" customWidth="1" collapsed="1"/>
-    <col min="21" max="22" width="18.6640625" customWidth="1"/>
+    <col min="5" max="12" width="18.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="18.6640625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="14" max="19" width="18.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="22" width="18.6640625" customWidth="1"/>
     <col min="23" max="30" width="18.796875" customWidth="1"/>
     <col min="31" max="32" width="18.796875" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="18.796875" customWidth="1"/>
@@ -1378,37 +1377,37 @@
       <c r="AG2" s="2"/>
     </row>
     <row r="3" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
       <c r="L3" s="31"/>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="40" t="s">
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="X3" s="40"/>
+      <c r="X3" s="44"/>
       <c r="Y3" s="28" t="s">
         <v>86</v>
       </c>
@@ -1421,13 +1420,13 @@
       <c r="AB3" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="AC3" s="41" t="s">
+      <c r="AC3" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
     </row>
     <row r="4" spans="2:33" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="34" t="s">
@@ -1637,19 +1636,19 @@
       <c r="F6" s="9">
         <v>45838</v>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="39">
         <v>48821746</v>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="39">
         <v>3969841</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="39">
         <v>820000</v>
       </c>
-      <c r="J6" s="49">
+      <c r="J6" s="39">
         <v>366900</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="39">
         <v>356406000000</v>
       </c>
       <c r="L6" s="11">
@@ -1689,31 +1688,31 @@
         <v>1.0294439487550715</v>
       </c>
       <c r="V6" s="6">
-        <f>L6/U6</f>
+        <f t="shared" ref="V6:V12" si="3">L6/U6</f>
         <v>0.29919064595257561</v>
       </c>
       <c r="W6" s="7">
-        <f>(P6-g)/(k-g)</f>
+        <f t="shared" ref="W6:W12" si="4">(P6-g)/(k-g)</f>
         <v>0.90527296937081347</v>
       </c>
       <c r="X6" s="7">
-        <f>T6*W6</f>
+        <f t="shared" ref="X6:X12" si="5">T6*W6</f>
         <v>10.083415402658765</v>
       </c>
       <c r="Y6" s="7">
-        <f>PV(Target_return,Holding_Period,-L6,-X6)</f>
+        <f t="shared" ref="Y6:Y12" si="6">PV(Target_return,Holding_Period,-L6,-X6)</f>
         <v>5.2103294940404279</v>
       </c>
       <c r="Z6" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L6,-X6)</f>
+        <f t="shared" ref="Z6:Z12" si="7">PV(Entry_yield,Holding_Period,-L6,-X6)</f>
         <v>6.4723886829985986</v>
       </c>
       <c r="AA6" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L6,-X6)</f>
+        <f t="shared" ref="AA6:AA12" si="8">PV(Benchmark_yield,Holding_Period,-L6,-X6)</f>
         <v>7.9704745497303149</v>
       </c>
       <c r="AB6" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L6,-X6)</f>
+        <f t="shared" ref="AB6:AB12" si="9">PV(Base_Cost_of_Equity,Holding_Period,-L6,-X6)</f>
         <v>8.9782562888960111</v>
       </c>
       <c r="AC6" s="13">
@@ -1731,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="AG6" s="5">
-        <f>L6/AC6</f>
+        <f t="shared" ref="AG6:AG12" si="10">L6/AC6</f>
         <v>4.1453566621803502E-2</v>
       </c>
     </row>
@@ -1751,19 +1750,19 @@
       <c r="F7" s="9">
         <v>45838</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="39">
         <v>40571149</v>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="39">
         <v>3322127</v>
       </c>
-      <c r="I7" s="49">
+      <c r="I7" s="39">
         <v>728570</v>
       </c>
-      <c r="J7" s="49">
+      <c r="J7" s="39">
         <v>335577</v>
       </c>
-      <c r="K7" s="49">
+      <c r="K7" s="39">
         <v>250011000000</v>
       </c>
       <c r="L7" s="11">
@@ -1783,15 +1782,15 @@
         <v>0.10101269457790145</v>
       </c>
       <c r="Q7" s="37">
-        <f t="shared" ref="Q7:Q12" si="3">I7/G7</f>
+        <f t="shared" ref="Q7:Q12" si="11">I7/G7</f>
         <v>1.7957835012264504E-2</v>
       </c>
       <c r="R7" s="38">
-        <f t="shared" ref="R7:R12" si="4">G7/H7</f>
+        <f t="shared" ref="R7:R12" si="12">G7/H7</f>
         <v>12.212401572847757</v>
       </c>
       <c r="S7" s="36">
-        <f t="shared" ref="S7:S12" si="5">J7/I7</f>
+        <f t="shared" ref="S7:S12" si="13">J7/I7</f>
         <v>0.4605967854838931</v>
       </c>
       <c r="T7" s="38">
@@ -1803,31 +1802,31 @@
         <v>1.3422489410465939</v>
       </c>
       <c r="V7" s="6">
-        <f>L7/U7</f>
+        <f t="shared" si="3"/>
         <v>0.28832207511241836</v>
       </c>
       <c r="W7" s="7">
-        <f>(P7-g)/(k-g)</f>
+        <f t="shared" si="4"/>
         <v>1.012658682223768</v>
       </c>
       <c r="X7" s="7">
-        <f>T7*W7</f>
+        <f t="shared" si="5"/>
         <v>13.45613093023907</v>
       </c>
       <c r="Y7" s="7">
-        <f>PV(Target_return,Holding_Period,-L7,-X7)</f>
+        <f t="shared" si="6"/>
         <v>6.9091345554564931</v>
       </c>
       <c r="Z7" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L7,-X7)</f>
+        <f t="shared" si="7"/>
         <v>8.5867439277312272</v>
       </c>
       <c r="AA7" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L7,-X7)</f>
+        <f t="shared" si="8"/>
         <v>10.578499103755053</v>
       </c>
       <c r="AB7" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L7,-X7)</f>
+        <f t="shared" si="9"/>
         <v>11.918566568712924</v>
       </c>
       <c r="AC7" s="13">
@@ -1837,7 +1836,7 @@
         <v>3</v>
       </c>
       <c r="AE7" s="7" t="str">
-        <f t="shared" ref="AE7:AE12" si="6">AD7&amp;D7</f>
+        <f t="shared" ref="AE7:AE12" si="14">AD7&amp;D7</f>
         <v>CNYCNY</v>
       </c>
       <c r="AF7" s="7">
@@ -1845,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="AG7" s="5">
-        <f>L7/AC7</f>
+        <f t="shared" si="10"/>
         <v>4.3434343434343436E-2</v>
       </c>
     </row>
@@ -1865,19 +1864,19 @@
       <c r="F8" s="9">
         <v>45838</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="39">
         <v>43238135</v>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="39">
         <v>3090808</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="39">
         <v>711416</v>
       </c>
-      <c r="J8" s="49">
+      <c r="J8" s="39">
         <v>282671</v>
       </c>
-      <c r="K8" s="49">
+      <c r="K8" s="39">
         <v>349983000000</v>
       </c>
       <c r="L8" s="11">
@@ -1897,15 +1896,15 @@
         <v>9.1455373481626814E-2</v>
       </c>
       <c r="Q8" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1.6453438613853257E-2</v>
       </c>
       <c r="R8" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>13.989265913638116</v>
       </c>
       <c r="S8" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>0.39733573605316719</v>
       </c>
       <c r="T8" s="38">
@@ -1917,31 +1916,31 @@
         <v>0.80767065828911688</v>
       </c>
       <c r="V8" s="6">
-        <f>L8/U8</f>
+        <f t="shared" si="3"/>
         <v>0.2946745651304874</v>
       </c>
       <c r="W8" s="7">
-        <f>(P8-g)/(k-g)</f>
+        <f t="shared" si="4"/>
         <v>0.89319216852033512</v>
       </c>
       <c r="X8" s="7">
-        <f>T8*W8</f>
+        <f t="shared" si="5"/>
         <v>7.8880559912910044</v>
       </c>
       <c r="Y8" s="7">
-        <f>PV(Target_return,Holding_Period,-L8,-X8)</f>
+        <f t="shared" si="6"/>
         <v>4.0705535190271149</v>
       </c>
       <c r="Z8" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L8,-X8)</f>
+        <f t="shared" si="7"/>
         <v>5.0570307683545934</v>
       </c>
       <c r="AA8" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L8,-X8)</f>
+        <f t="shared" si="8"/>
         <v>6.2280456564139071</v>
       </c>
       <c r="AB8" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L8,-X8)</f>
+        <f t="shared" si="9"/>
         <v>7.0158255458485144</v>
       </c>
       <c r="AC8" s="13">
@@ -1951,7 +1950,7 @@
         <v>3</v>
       </c>
       <c r="AE8" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AF8" s="7">
@@ -1959,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="AG8" s="5">
-        <f>L8/AC8</f>
+        <f t="shared" si="10"/>
         <v>3.4195402298850576E-2</v>
       </c>
     </row>
@@ -1979,19 +1978,19 @@
       <c r="F9" s="9">
         <v>45838</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="39">
         <v>35061299</v>
       </c>
-      <c r="H9" s="49">
+      <c r="H9" s="39">
         <v>2816231</v>
       </c>
-      <c r="I9" s="49">
+      <c r="I9" s="39">
         <v>632771</v>
       </c>
-      <c r="J9" s="49">
+      <c r="J9" s="39">
         <v>252700</v>
       </c>
-      <c r="K9" s="49">
+      <c r="K9" s="39">
         <v>294388000000</v>
       </c>
       <c r="L9" s="11">
@@ -2011,15 +2010,15 @@
         <v>8.9729855256901872E-2</v>
       </c>
       <c r="Q9" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1.8047562926861323E-2</v>
       </c>
       <c r="R9" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>12.449724117091247</v>
       </c>
       <c r="S9" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>0.39935458483400788</v>
       </c>
       <c r="T9" s="38">
@@ -2031,31 +2030,31 @@
         <v>0.85839096702311235</v>
       </c>
       <c r="V9" s="6">
-        <f>L9/U9</f>
+        <f t="shared" si="3"/>
         <v>0.26677820340324498</v>
       </c>
       <c r="W9" s="7">
-        <f>(P9-g)/(k-g)</f>
+        <f t="shared" si="4"/>
         <v>0.87162319071127337</v>
       </c>
       <c r="X9" s="7">
-        <f>T9*W9</f>
+        <f t="shared" si="5"/>
         <v>8.3382890946641854</v>
       </c>
       <c r="Y9" s="7">
-        <f>PV(Target_return,Holding_Period,-L9,-X9)</f>
+        <f t="shared" si="6"/>
         <v>4.2615655476408243</v>
       </c>
       <c r="Z9" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L9,-X9)</f>
+        <f t="shared" si="7"/>
         <v>5.2981571752107932</v>
       </c>
       <c r="AA9" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L9,-X9)</f>
+        <f t="shared" si="8"/>
         <v>6.5290414844024953</v>
       </c>
       <c r="AB9" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L9,-X9)</f>
+        <f t="shared" si="9"/>
         <v>7.3572743812635029</v>
       </c>
       <c r="AC9" s="13">
@@ -2065,7 +2064,7 @@
         <v>3</v>
       </c>
       <c r="AE9" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AF9" s="7">
@@ -2073,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="AG9" s="5">
-        <f>L9/AC9</f>
+        <f t="shared" si="10"/>
         <v>4.2565055762081784E-2</v>
       </c>
     </row>
@@ -2093,22 +2092,22 @@
       <c r="F10" s="9">
         <v>45838</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="39">
         <v>10510731</v>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="39">
         <v>766132</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="39">
         <v>212226</v>
       </c>
-      <c r="J10" s="49">
+      <c r="J10" s="39">
         <v>77205</v>
       </c>
-      <c r="K10" s="49">
+      <c r="K10" s="39">
         <v>20774000000</v>
       </c>
-      <c r="L10" s="50">
+      <c r="L10" s="40">
         <v>1.06</v>
       </c>
       <c r="M10" s="12">
@@ -2121,19 +2120,19 @@
         <v>0.47599999999999998</v>
       </c>
       <c r="P10" s="36">
-        <f t="shared" ref="P10:P12" si="7">J10/H10</f>
+        <f t="shared" ref="P10:P12" si="15">J10/H10</f>
         <v>0.10077245174460799</v>
       </c>
       <c r="Q10" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2.0191364425557079E-2</v>
       </c>
       <c r="R10" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>13.719216792928634</v>
       </c>
       <c r="S10" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>0.36378671793276979</v>
       </c>
       <c r="T10" s="38">
@@ -2145,31 +2144,31 @@
         <v>3.716424376624627</v>
       </c>
       <c r="V10" s="6">
-        <f>L10/U10</f>
+        <f t="shared" si="3"/>
         <v>0.28522038728061655</v>
       </c>
       <c r="W10" s="7">
-        <f>(P10-g)/(k-g)</f>
+        <f t="shared" si="4"/>
         <v>1.0096556468075997</v>
       </c>
       <c r="X10" s="7">
-        <f>T10*W10</f>
+        <f t="shared" si="5"/>
         <v>37.235462597477614</v>
       </c>
       <c r="Y10" s="7">
-        <f>PV(Target_return,Holding_Period,-L10,-X10)</f>
+        <f t="shared" si="6"/>
         <v>19.098842024353051</v>
       </c>
       <c r="Z10" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L10,-X10)</f>
+        <f t="shared" si="7"/>
         <v>23.738092615861252</v>
       </c>
       <c r="AA10" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L10,-X10)</f>
+        <f t="shared" si="8"/>
         <v>29.246264118951007</v>
       </c>
       <c r="AB10" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L10,-X10)</f>
+        <f t="shared" si="9"/>
         <v>32.952287833787608</v>
       </c>
       <c r="AC10" s="13">
@@ -2179,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="AE10" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AF10" s="7">
@@ -2187,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="AG10" s="5">
-        <f>L10/AC10</f>
+        <f t="shared" si="10"/>
         <v>5.2762568442010951E-2</v>
       </c>
     </row>
@@ -2207,22 +2206,22 @@
       <c r="F11" s="9">
         <v>45838</v>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="39">
         <v>17084910</v>
       </c>
-      <c r="H11" s="49">
+      <c r="H11" s="39">
         <v>1023006</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="39">
         <v>349133</v>
       </c>
-      <c r="J11" s="49">
+      <c r="J11" s="39">
         <v>86479</v>
       </c>
-      <c r="K11" s="49">
+      <c r="K11" s="39">
         <v>99161000000</v>
       </c>
-      <c r="L11" s="50">
+      <c r="L11" s="40">
         <v>0.24</v>
       </c>
       <c r="M11" s="12">
@@ -2235,19 +2234,19 @@
         <v>0.252</v>
       </c>
       <c r="P11" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>8.4534206055487462E-2</v>
       </c>
       <c r="Q11" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2.0435167642088838E-2</v>
       </c>
       <c r="R11" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>16.7006938375728</v>
       </c>
       <c r="S11" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>0.24769643660152435</v>
       </c>
       <c r="T11" s="38">
@@ -2259,31 +2258,31 @@
         <v>0.87210697754157385</v>
       </c>
       <c r="V11" s="6">
-        <f>L11/U11</f>
+        <f t="shared" si="3"/>
         <v>0.27519559661883231</v>
       </c>
       <c r="W11" s="7">
-        <f>(P11-g)/(k-g)</f>
+        <f t="shared" si="4"/>
         <v>0.80667757569359322</v>
       </c>
       <c r="X11" s="7">
-        <f>T11*W11</f>
+        <f t="shared" si="5"/>
         <v>8.3221831163461442</v>
       </c>
       <c r="Y11" s="7">
-        <f>PV(Target_return,Holding_Period,-L11,-X11)</f>
+        <f t="shared" si="6"/>
         <v>4.2742718051540534</v>
       </c>
       <c r="Z11" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L11,-X11)</f>
+        <f t="shared" si="7"/>
         <v>5.3119981264614875</v>
       </c>
       <c r="AA11" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L11,-X11)</f>
+        <f t="shared" si="8"/>
         <v>6.5440359914386921</v>
       </c>
       <c r="AB11" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L11,-X11)</f>
+        <f t="shared" si="9"/>
         <v>7.3729549577050042</v>
       </c>
       <c r="AC11" s="13">
@@ -2293,7 +2292,7 @@
         <v>3</v>
       </c>
       <c r="AE11" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AF11" s="7">
@@ -2301,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="AG11" s="5">
-        <f>L11/AC11</f>
+        <f t="shared" si="10"/>
         <v>4.6421663442940041E-2</v>
       </c>
     </row>
@@ -2321,22 +2320,22 @@
       <c r="F12" s="9">
         <v>45838</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="39">
         <v>3017048</v>
       </c>
-      <c r="H12" s="49">
+      <c r="H12" s="39">
         <v>154295</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="39">
         <v>51910</v>
       </c>
-      <c r="J12" s="49">
+      <c r="J12" s="39">
         <v>23730</v>
       </c>
-      <c r="K12" s="49">
+      <c r="K12" s="39">
         <v>17918000000</v>
       </c>
-      <c r="L12" s="50">
+      <c r="L12" s="40">
         <f>0.780688+0.779073+0.777313+2.791007</f>
         <v>5.1280809999999999</v>
       </c>
@@ -2350,19 +2349,19 @@
         <v>0.52300000000000002</v>
       </c>
       <c r="P12" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>0.15379629929680158</v>
       </c>
       <c r="Q12" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1.7205559871768694E-2</v>
       </c>
       <c r="R12" s="38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>19.553763893839722</v>
       </c>
       <c r="S12" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>0.45713735311115394</v>
       </c>
       <c r="T12" s="38">
@@ -2374,31 +2373,31 @@
         <v>10.330059158388213</v>
       </c>
       <c r="V12" s="6">
-        <f>L12/U12</f>
+        <f t="shared" si="3"/>
         <v>0.49642319771575522</v>
       </c>
       <c r="W12" s="7">
-        <f>(P12-g)/(k-g)</f>
+        <f t="shared" si="4"/>
         <v>1.6724537412100198</v>
       </c>
       <c r="X12" s="7">
-        <f>T12*W12</f>
+        <f t="shared" si="5"/>
         <v>112.33395189195224</v>
       </c>
       <c r="Y12" s="7">
-        <f>PV(Target_return,Holding_Period,-L12,-X12)</f>
+        <f t="shared" si="6"/>
         <v>61.150425207160808</v>
       </c>
       <c r="Z12" s="7">
-        <f>PV(Entry_yield,Holding_Period,-L12,-X12)</f>
+        <f t="shared" si="7"/>
         <v>75.675539859823033</v>
       </c>
       <c r="AA12" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-L12,-X12)</f>
+        <f t="shared" si="8"/>
         <v>92.888551757648202</v>
       </c>
       <c r="AB12" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-L12,-X12)</f>
+        <f t="shared" si="9"/>
         <v>104.45468726004771</v>
       </c>
       <c r="AC12" s="13">
@@ -2408,7 +2407,7 @@
         <v>124</v>
       </c>
       <c r="AE12" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>HKDUSD</v>
       </c>
       <c r="AF12" s="7">
@@ -2416,7 +2415,7 @@
         <v>7.8</v>
       </c>
       <c r="AG12" s="5">
-        <f>L12/AC12</f>
+        <f t="shared" si="10"/>
         <v>3.9446776923076923E-2</v>
       </c>
     </row>
@@ -2431,6 +2430,6 @@
     <mergeCell ref="M3:S3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="25" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B520FD-FC66-45AE-B87B-A38F97C09CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBBEFEA-0893-4EF0-969B-5F46CE4327DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1289,10 +1289,11 @@
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="12" width="18.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="18.6640625" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="14" max="19" width="18.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="22" width="18.6640625" customWidth="1"/>
+    <col min="5" max="12" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="14" max="19" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="18.6640625" customWidth="1" collapsed="1"/>
+    <col min="21" max="22" width="18.6640625" customWidth="1"/>
     <col min="23" max="30" width="18.796875" customWidth="1"/>
     <col min="31" max="32" width="18.796875" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="18.796875" customWidth="1"/>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08AFF37-8D61-428D-A983-8C1EE74FBCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FB43D6-FE21-4CA7-B17D-038AFBC06517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="1770" windowWidth="14520" windowHeight="7860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -841,36 +841,6 @@
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -878,15 +848,6 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,6 +863,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1349,7 +1349,7 @@
       <c r="B14" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="41">
         <v>1000000</v>
       </c>
       <c r="D14" s="1"/>
@@ -1535,45 +1535,45 @@
       <c r="AW2" s="2"/>
     </row>
     <row r="3" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="56" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="55" t="s">
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="41" t="s">
+      <c r="S3" s="61"/>
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="61"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="42" t="s">
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="42"/>
+      <c r="AB3" s="52"/>
       <c r="AC3" s="27" t="s">
         <v>79</v>
       </c>
@@ -1586,14 +1586,14 @@
       <c r="AF3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AG3" s="43" t="s">
+      <c r="AG3" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="50"/>
+      <c r="AK3" s="50"/>
+      <c r="AL3" s="50"/>
       <c r="AM3" s="27" t="s">
         <v>79</v>
       </c>
@@ -1606,15 +1606,15 @@
       <c r="AP3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AQ3" s="43" t="s">
+      <c r="AQ3" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="43"/>
-      <c r="AW3" s="43"/>
+      <c r="AR3" s="50"/>
+      <c r="AS3" s="50"/>
+      <c r="AT3" s="50"/>
+      <c r="AU3" s="50"/>
+      <c r="AV3" s="50"/>
+      <c r="AW3" s="50"/>
     </row>
     <row r="4" spans="2:49" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="32" t="s">
@@ -1644,25 +1644,25 @@
       <c r="J4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="K4" s="57" t="s">
+      <c r="K4" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="57" t="s">
+      <c r="L4" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="M4" s="57" t="s">
+      <c r="M4" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="N4" s="57" t="s">
+      <c r="N4" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="O4" s="57" t="s">
+      <c r="O4" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="P4" s="57" t="s">
+      <c r="P4" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="Q4" s="57" t="s">
+      <c r="Q4" s="44" t="s">
         <v>32</v>
       </c>
       <c r="R4" s="28" t="s">
@@ -1790,25 +1790,25 @@
       <c r="J5" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="58" t="s">
+      <c r="K5" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="L5" s="58" t="s">
+      <c r="L5" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="M5" s="58" t="s">
+      <c r="M5" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="N5" s="58" t="s">
+      <c r="N5" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="O5" s="58" t="s">
+      <c r="O5" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="P5" s="58" t="s">
+      <c r="P5" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="Q5" s="58" t="s">
+      <c r="Q5" s="45" t="s">
         <v>31</v>
       </c>
       <c r="R5" s="29" t="s">
@@ -1897,10 +1897,10 @@
       </c>
     </row>
     <row r="6" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="48" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1922,28 +1922,28 @@
         <f>4114692-23118-19420-59031</f>
         <v>4013123</v>
       </c>
-      <c r="J6" s="52">
+      <c r="J6" s="42">
         <f>36904556/48179055</f>
         <v>0.76598754375734435</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="47">
         <f>637405+109397</f>
         <v>746802</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="47">
         <f>28762+40930</f>
         <v>69692</v>
       </c>
       <c r="M6" s="37">
         <v>-400918</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="43">
         <v>0.25</v>
       </c>
       <c r="O6" s="37">
         <v>366946</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="46">
         <f>(K6+L6/2+M6)*(1-N6)</f>
         <v>285547.5</v>
       </c>
@@ -1960,58 +1960,58 @@
         <v>0.53684644658155711</v>
       </c>
       <c r="T6" s="34">
-        <f>P6/I6</f>
+        <f t="shared" ref="T6:T12" si="1">P6/I6</f>
         <v>7.115343835710991E-2</v>
       </c>
       <c r="U6" s="35">
-        <f>K6/H6</f>
+        <f t="shared" ref="U6:U12" si="2">K6/H6</f>
         <v>1.4274303010950491E-2</v>
       </c>
       <c r="V6" s="36">
-        <f>H6/I6</f>
+        <f t="shared" ref="V6:V12" si="3">H6/I6</f>
         <v>13.036712555284252</v>
       </c>
       <c r="W6" s="34">
-        <f>P6/K6</f>
+        <f t="shared" ref="W6:W11" si="4">P6/K6</f>
         <v>0.38236038468027672</v>
       </c>
       <c r="X6" s="36">
-        <f>I6/(G6/1000000)*$AK6</f>
+        <f t="shared" ref="X6:X12" si="5">I6/(G6/1000000)*$AK6</f>
         <v>11.259967860210329</v>
       </c>
       <c r="Y6" s="36">
-        <f>P6/(G6/1000000)*$AK6</f>
+        <f t="shared" ref="Y6:Y12" si="6">P6/(G6/1000000)*$AK6</f>
         <v>0.8011854290445144</v>
       </c>
       <c r="Z6" s="6">
-        <f>Q6/Y6</f>
+        <f t="shared" ref="Z6:Z12" si="7">Q6/Y6</f>
         <v>0.38443035636246864</v>
       </c>
       <c r="AA6" s="7">
-        <f>(T6-g)/(k-g)</f>
+        <f t="shared" ref="AA6:AA12" si="8">(T6-g)/(k-g)</f>
         <v>0.85255730595183177</v>
       </c>
       <c r="AB6" s="7">
-        <f>X6*AA6</f>
+        <f t="shared" ref="AB6:AB12" si="9">X6*AA6</f>
         <v>9.5997678640051305</v>
       </c>
       <c r="AC6" s="7">
-        <f>PV(Target_return,Holding_Period,-Q6,-AB6)</f>
+        <f t="shared" ref="AC6:AC12" si="10">PV(Target_return,Holding_Period,-Q6,-AB6)</f>
         <v>4.9874504439696281</v>
       </c>
       <c r="AD6" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q6,-AB6)</f>
+        <f t="shared" ref="AD6:AD12" si="11">PV(Entry_yield,Holding_Period,-Q6,-AB6)</f>
         <v>6.1930254837762826</v>
       </c>
       <c r="AE6" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q6,-AB6)</f>
+        <f t="shared" ref="AE6:AE12" si="12">PV(Benchmark_yield,Holding_Period,-Q6,-AB6)</f>
         <v>7.623815149844293</v>
       </c>
       <c r="AF6" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q6,-AB6)</f>
+        <f t="shared" ref="AF6:AF12" si="13">PV(Base_Cost_of_Equity,Holding_Period,-Q6,-AB6)</f>
         <v>8.5862102417703685</v>
       </c>
-      <c r="AG6" s="62" t="s">
+      <c r="AG6" s="49" t="s">
         <v>144</v>
       </c>
       <c r="AH6" s="12">
@@ -2021,7 +2021,7 @@
         <v>3</v>
       </c>
       <c r="AJ6" s="7" t="str">
-        <f>AI6&amp;D6</f>
+        <f t="shared" ref="AJ6:AJ12" si="14">AI6&amp;D6</f>
         <v>CNYCNY</v>
       </c>
       <c r="AK6" s="7">
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="AL6" s="5">
-        <f>Q6/AH6</f>
+        <f t="shared" ref="AL6:AL12" si="15">Q6/AH6</f>
         <v>4.2424242424242427E-2</v>
       </c>
       <c r="AM6" s="7">
@@ -2037,18 +2037,18 @@
         <v>5.6038769033366611</v>
       </c>
       <c r="AN6" s="7">
-        <f t="shared" ref="AN6:AP12" si="1">IF($AQ6="","na",AD6/$AV6)</f>
+        <f t="shared" ref="AN6:AP12" si="16">IF($AQ6="","na",AD6/$AV6)</f>
         <v>6.9584555997486319</v>
       </c>
       <c r="AO6" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>8.5660844380272962</v>
       </c>
       <c r="AP6" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>9.6474272379442336</v>
       </c>
-      <c r="AQ6" s="62" t="s">
+      <c r="AQ6" s="49" t="s">
         <v>154</v>
       </c>
       <c r="AR6" s="12">
@@ -2075,10 +2075,10 @@
       </c>
     </row>
     <row r="7" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="48" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -2100,29 +2100,29 @@
         <f>3563298-4942-2461</f>
         <v>3555895</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7" s="42">
         <f>30469491/40847989</f>
         <v>0.74592389358506728</v>
       </c>
-      <c r="K7" s="60">
+      <c r="K7" s="47">
         <f>589882+104928</f>
         <v>694810</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="47">
         <f>21210+21417</f>
         <v>42627</v>
       </c>
       <c r="M7" s="37">
         <v>-365879</v>
       </c>
-      <c r="N7" s="53">
+      <c r="N7" s="43">
         <v>0.25</v>
       </c>
       <c r="O7" s="37">
         <v>335577</v>
       </c>
-      <c r="P7" s="59">
-        <f t="shared" ref="P7:P12" si="2">(K7+L7/2+M7)*(1-N7)</f>
+      <c r="P7" s="46">
+        <f t="shared" ref="P7:P12" si="17">(K7+L7/2+M7)*(1-N7)</f>
         <v>262683.375</v>
       </c>
       <c r="Q7" s="38">
@@ -2138,58 +2138,58 @@
         <v>0.52658856378002616</v>
       </c>
       <c r="T7" s="34">
-        <f>P7/I7</f>
+        <f t="shared" si="1"/>
         <v>7.3872646689511365E-2</v>
       </c>
       <c r="U7" s="35">
-        <f>K7/H7</f>
+        <f t="shared" si="2"/>
         <v>1.5637305085642945E-2</v>
       </c>
       <c r="V7" s="36">
-        <f>H7/I7</f>
+        <f t="shared" si="3"/>
         <v>12.495545565884257</v>
       </c>
       <c r="W7" s="34">
-        <f>P7/K7</f>
+        <f t="shared" si="4"/>
         <v>0.37806504655949108</v>
       </c>
       <c r="X7" s="36">
-        <f>I7/(G7/1000000)*$AK7</f>
+        <f t="shared" si="5"/>
         <v>13.592850974329741</v>
       </c>
       <c r="Y7" s="36">
-        <f>P7/(G7/1000000)*$AK7</f>
+        <f t="shared" si="6"/>
         <v>1.0041398775298411</v>
       </c>
       <c r="Z7" s="6">
-        <f>Q7/Y7</f>
+        <f t="shared" si="7"/>
         <v>0.40133850772998869</v>
       </c>
       <c r="AA7" s="7">
-        <f>(T7-g)/(k-g)</f>
+        <f t="shared" si="8"/>
         <v>0.89787744482518939</v>
       </c>
       <c r="AB7" s="7">
-        <f>X7*AA7</f>
+        <f t="shared" si="9"/>
         <v>12.204714300720774</v>
       </c>
       <c r="AC7" s="7">
-        <f>PV(Target_return,Holding_Period,-Q7,-AB7)</f>
+        <f t="shared" si="10"/>
         <v>6.3617224896519993</v>
       </c>
       <c r="AD7" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q7,-AB7)</f>
+        <f t="shared" si="11"/>
         <v>7.8975680604798519</v>
       </c>
       <c r="AE7" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q7,-AB7)</f>
+        <f t="shared" si="12"/>
         <v>9.7201348785712796</v>
       </c>
       <c r="AF7" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q7,-AB7)</f>
+        <f t="shared" si="13"/>
         <v>10.945962753461778</v>
       </c>
-      <c r="AG7" s="62" t="s">
+      <c r="AG7" s="49" t="s">
         <v>145</v>
       </c>
       <c r="AH7" s="12">
@@ -2199,7 +2199,7 @@
         <v>3</v>
       </c>
       <c r="AJ7" s="7" t="str">
-        <f>AI7&amp;D7</f>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AK7" s="7">
@@ -2207,26 +2207,26 @@
         <v>1</v>
       </c>
       <c r="AL7" s="5">
-        <f>Q7/AH7</f>
+        <f t="shared" si="15"/>
         <v>4.642857142857143E-2</v>
       </c>
       <c r="AM7" s="7">
-        <f t="shared" ref="AM7:AM12" si="3">IF($AQ7="","na",AC7/$AV7)</f>
+        <f t="shared" ref="AM7:AM12" si="18">IF($AQ7="","na",AC7/$AV7)</f>
         <v>7.148002797361797</v>
       </c>
       <c r="AN7" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>8.8736719780672484</v>
       </c>
       <c r="AO7" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>10.921499863563236</v>
       </c>
       <c r="AP7" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>12.298834554451435</v>
       </c>
-      <c r="AQ7" s="62" t="s">
+      <c r="AQ7" s="49" t="s">
         <v>153</v>
       </c>
       <c r="AR7" s="12">
@@ -2236,11 +2236,11 @@
         <v>107</v>
       </c>
       <c r="AT7" s="34">
-        <f t="shared" ref="AT7:AT12" si="4">IF($AQ7="","na",AR7/(AH7/AV7)-1)</f>
+        <f t="shared" ref="AT7:AT12" si="19">IF($AQ7="","na",AR7/(AH7/AV7)-1)</f>
         <v>-0.21561059907834101</v>
       </c>
       <c r="AU7" s="7" t="str">
-        <f t="shared" ref="AU7:AU12" si="5">IF($AQ7="","na",AS7&amp;D7)</f>
+        <f t="shared" ref="AU7:AU12" si="20">IF($AQ7="","na",AS7&amp;D7)</f>
         <v>HKDCNY</v>
       </c>
       <c r="AV7" s="7">
@@ -2248,15 +2248,15 @@
         <v>0.89</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" ref="AW7:AW12" si="6">IF($AQ7="","na",(Q7/AV7)/AR7)</f>
+        <f t="shared" ref="AW7:AW12" si="21">IF($AQ7="","na",(Q7/AV7)/AR7)</f>
         <v>5.9190717485496071E-2</v>
       </c>
     </row>
     <row r="8" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="48" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -2278,29 +2278,29 @@
         <f>3143100-28563-1381-300488</f>
         <v>2812668</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8" s="42">
         <f>31900486/43706637</f>
         <v>0.72987738681427261</v>
       </c>
-      <c r="K8" s="60">
+      <c r="K8" s="47">
         <f>580692+75567</f>
         <v>656259</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="47">
         <f>7943+31139</f>
         <v>39082</v>
       </c>
       <c r="M8" s="37">
         <v>-390774</v>
       </c>
-      <c r="N8" s="53">
+      <c r="N8" s="43">
         <v>0.25</v>
       </c>
       <c r="O8" s="37">
         <v>282083</v>
       </c>
-      <c r="P8" s="59">
-        <f t="shared" si="2"/>
+      <c r="P8" s="46">
+        <f t="shared" si="17"/>
         <v>213769.5</v>
       </c>
       <c r="Q8" s="38">
@@ -2316,58 +2316,58 @@
         <v>0.59545697659003538</v>
       </c>
       <c r="T8" s="34">
-        <f>P8/I8</f>
+        <f t="shared" si="1"/>
         <v>7.6002393457030831E-2</v>
       </c>
       <c r="U8" s="35">
-        <f>K8/H8</f>
+        <f t="shared" si="2"/>
         <v>1.400590551307138E-2</v>
       </c>
       <c r="V8" s="36">
-        <f>H8/I8</f>
+        <f t="shared" si="3"/>
         <v>16.658872643340771</v>
       </c>
       <c r="W8" s="34">
-        <f>P8/K8</f>
+        <f t="shared" si="4"/>
         <v>0.32573953271497991</v>
       </c>
       <c r="X8" s="36">
-        <f>I8/(G8/1000000)*$AK8</f>
+        <f t="shared" si="5"/>
         <v>8.0365838562924345</v>
       </c>
       <c r="Y8" s="36">
-        <f>P8/(G8/1000000)*$AK8</f>
+        <f t="shared" si="6"/>
         <v>0.61079960829635971</v>
       </c>
       <c r="Z8" s="6">
-        <f>Q8/Y8</f>
+        <f t="shared" si="7"/>
         <v>0.39603823695091539</v>
       </c>
       <c r="AA8" s="7">
-        <f>(T8-g)/(k-g)</f>
+        <f t="shared" si="8"/>
         <v>0.93337322428384717</v>
       </c>
       <c r="AB8" s="7">
-        <f>X8*AA8</f>
+        <f t="shared" si="9"/>
         <v>7.5011321861751838</v>
       </c>
       <c r="AC8" s="7">
-        <f>PV(Target_return,Holding_Period,-Q8,-AB8)</f>
+        <f t="shared" si="10"/>
         <v>3.8993840391989112</v>
       </c>
       <c r="AD8" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q8,-AB8)</f>
+        <f t="shared" si="11"/>
         <v>4.8417424890972054</v>
       </c>
       <c r="AE8" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q8,-AB8)</f>
+        <f t="shared" si="12"/>
         <v>5.9601231499834695</v>
       </c>
       <c r="AF8" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q8,-AB8)</f>
+        <f t="shared" si="13"/>
         <v>6.712372290957056</v>
       </c>
-      <c r="AG8" s="62" t="s">
+      <c r="AG8" s="49" t="s">
         <v>146</v>
       </c>
       <c r="AH8" s="12">
@@ -2377,7 +2377,7 @@
         <v>3</v>
       </c>
       <c r="AJ8" s="7" t="str">
-        <f>AI8&amp;D8</f>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AK8" s="7">
@@ -2385,26 +2385,26 @@
         <v>1</v>
       </c>
       <c r="AL8" s="5">
-        <f>Q8/AH8</f>
+        <f t="shared" si="15"/>
         <v>3.5159883720930235E-2</v>
       </c>
       <c r="AM8" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="18"/>
         <v>4.3813303811223721</v>
       </c>
       <c r="AN8" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>5.4401601001092192</v>
       </c>
       <c r="AO8" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>6.6967675842510896</v>
       </c>
       <c r="AP8" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>7.5419913381539958</v>
       </c>
-      <c r="AQ8" s="62" t="s">
+      <c r="AQ8" s="49" t="s">
         <v>155</v>
       </c>
       <c r="AR8" s="12">
@@ -2414,11 +2414,11 @@
         <v>107</v>
       </c>
       <c r="AT8" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="19"/>
         <v>-0.30274709302325575</v>
       </c>
       <c r="AU8" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AV8" s="7">
@@ -2426,15 +2426,15 @@
         <v>0.89</v>
       </c>
       <c r="AW8" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>5.0426299222446902E-2</v>
       </c>
     </row>
     <row r="9" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="48" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2456,29 +2456,29 @@
         <f>2987590-29158-2795-395040</f>
         <v>2560597</v>
       </c>
-      <c r="J9" s="52">
+      <c r="J9" s="42">
         <f>25638312/33664948</f>
         <v>0.76157289772139258</v>
       </c>
-      <c r="K9" s="60">
+      <c r="K9" s="47">
         <f>448934+76590</f>
         <v>525524</v>
       </c>
-      <c r="L9" s="60">
+      <c r="L9" s="47">
         <f>52049+41453</f>
         <v>93502</v>
       </c>
       <c r="M9" s="37">
         <v>-337627</v>
       </c>
-      <c r="N9" s="53">
+      <c r="N9" s="43">
         <v>0.25</v>
       </c>
       <c r="O9" s="37">
         <v>252719</v>
       </c>
-      <c r="P9" s="59">
-        <f t="shared" si="2"/>
+      <c r="P9" s="46">
+        <f t="shared" si="17"/>
         <v>175986</v>
       </c>
       <c r="Q9" s="38">
@@ -2494,58 +2494,58 @@
         <v>0.64245781353468157</v>
       </c>
       <c r="T9" s="34">
-        <f>P9/I9</f>
+        <f t="shared" si="1"/>
         <v>6.8728503548195985E-2</v>
       </c>
       <c r="U9" s="35">
-        <f>K9/H9</f>
+        <f t="shared" si="2"/>
         <v>1.4284187110445809E-2</v>
       </c>
       <c r="V9" s="36">
-        <f>H9/I9</f>
+        <f t="shared" si="3"/>
         <v>14.367982544695632</v>
       </c>
       <c r="W9" s="34">
-        <f>P9/K9</f>
+        <f t="shared" si="4"/>
         <v>0.33487718924349791</v>
       </c>
       <c r="X9" s="36">
-        <f>I9/(G9/1000000)*$AK9</f>
+        <f t="shared" si="5"/>
         <v>7.9469222975747051</v>
       </c>
       <c r="Y9" s="36">
-        <f>P9/(G9/1000000)*$AK9</f>
+        <f t="shared" si="6"/>
         <v>0.54618007732610097</v>
       </c>
       <c r="Z9" s="6">
-        <f>Q9/Y9</f>
+        <f t="shared" si="7"/>
         <v>0.44380967022214041</v>
       </c>
       <c r="AA9" s="7">
-        <f>(T9-g)/(k-g)</f>
+        <f t="shared" si="8"/>
         <v>0.81214172580326638</v>
       </c>
       <c r="AB9" s="7">
-        <f>X9*AA9</f>
+        <f t="shared" si="9"/>
         <v>6.45402718957678</v>
       </c>
       <c r="AC9" s="7">
-        <f>PV(Target_return,Holding_Period,-Q9,-AB9)</f>
+        <f t="shared" si="10"/>
         <v>3.4177621001950751</v>
       </c>
       <c r="AD9" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q9,-AB9)</f>
+        <f t="shared" si="11"/>
         <v>4.2379685002558771</v>
       </c>
       <c r="AE9" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q9,-AB9)</f>
+        <f t="shared" si="12"/>
         <v>5.2108060626568031</v>
       </c>
       <c r="AF9" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q9,-AB9)</f>
+        <f t="shared" si="13"/>
         <v>5.864892240591038</v>
       </c>
-      <c r="AG9" s="62" t="s">
+      <c r="AG9" s="49" t="s">
         <v>147</v>
       </c>
       <c r="AH9" s="12">
@@ -2555,7 +2555,7 @@
         <v>3</v>
       </c>
       <c r="AJ9" s="7" t="str">
-        <f>AI9&amp;D9</f>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AK9" s="7">
@@ -2563,26 +2563,26 @@
         <v>1</v>
       </c>
       <c r="AL9" s="5">
-        <f>Q9/AH9</f>
+        <f t="shared" si="15"/>
         <v>4.5393258426966294E-2</v>
       </c>
       <c r="AM9" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="18"/>
         <v>3.8401821350506462</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>4.7617623598380643</v>
       </c>
       <c r="AO9" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>5.8548382726480934</v>
       </c>
       <c r="AP9" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>6.5897665624618407</v>
       </c>
-      <c r="AQ9" s="62" t="s">
+      <c r="AQ9" s="49" t="s">
         <v>156</v>
       </c>
       <c r="AR9" s="12">
@@ -2592,11 +2592,11 @@
         <v>107</v>
       </c>
       <c r="AT9" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="19"/>
         <v>-0.255</v>
       </c>
       <c r="AU9" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AV9" s="7">
@@ -2604,15 +2604,15 @@
         <v>0.89</v>
       </c>
       <c r="AW9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>6.0930548224115838E-2</v>
       </c>
     </row>
     <row r="10" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="48" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="10" t="s">
@@ -2634,29 +2634,29 @@
         <f>881747-1054-532-78891</f>
         <v>801270</v>
       </c>
-      <c r="J10" s="52">
+      <c r="J10" s="42">
         <f>5964497/9720864</f>
         <v>0.6135768384374064</v>
       </c>
-      <c r="K10" s="60">
+      <c r="K10" s="47">
         <f>148107+24096+661</f>
         <v>172864</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="47">
         <f>503+36202</f>
         <v>36705</v>
       </c>
       <c r="M10" s="37">
         <v>-125029</v>
       </c>
-      <c r="N10" s="53">
+      <c r="N10" s="43">
         <v>0.25</v>
       </c>
       <c r="O10" s="37">
         <v>77205</v>
       </c>
-      <c r="P10" s="59">
-        <f t="shared" si="2"/>
+      <c r="P10" s="46">
+        <f t="shared" si="17"/>
         <v>49640.625</v>
       </c>
       <c r="Q10" s="38">
@@ -2671,58 +2671,58 @@
         <v>0.72327957238059981</v>
       </c>
       <c r="T10" s="34">
-        <f>P10/I10</f>
+        <f t="shared" si="1"/>
         <v>6.195243176457374E-2</v>
       </c>
       <c r="U10" s="35">
-        <f>K10/H10</f>
+        <f t="shared" si="2"/>
         <v>1.6285837245637425E-2</v>
       </c>
       <c r="V10" s="36">
-        <f>H10/I10</f>
+        <f t="shared" si="3"/>
         <v>13.246940481984849</v>
       </c>
       <c r="W10" s="34">
-        <f>P10/K10</f>
+        <f t="shared" si="4"/>
         <v>0.28716577772121438</v>
       </c>
       <c r="X10" s="36">
-        <f>I10/(G10/1000000)*$AK10</f>
+        <f t="shared" si="5"/>
         <v>37.862093398033004</v>
       </c>
       <c r="Y10" s="36">
-        <f>P10/(G10/1000000)*$AK10</f>
+        <f t="shared" si="6"/>
         <v>2.3456487577055571</v>
       </c>
       <c r="Z10" s="6">
-        <f>Q10/Y10</f>
+        <f t="shared" si="7"/>
         <v>0.45190056546951218</v>
       </c>
       <c r="AA10" s="7">
-        <f>(T10-g)/(k-g)</f>
+        <f t="shared" si="8"/>
         <v>0.69920719607622894</v>
       </c>
       <c r="AB10" s="7">
-        <f>X10*AA10</f>
+        <f t="shared" si="9"/>
         <v>26.473448162414957</v>
       </c>
       <c r="AC10" s="7">
-        <f>PV(Target_return,Holding_Period,-Q10,-AB10)</f>
+        <f t="shared" si="10"/>
         <v>14.139388367642148</v>
       </c>
       <c r="AD10" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q10,-AB10)</f>
+        <f t="shared" si="11"/>
         <v>17.521766588388239</v>
       </c>
       <c r="AE10" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q10,-AB10)</f>
+        <f t="shared" si="12"/>
         <v>21.532478422844516</v>
       </c>
       <c r="AF10" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q10,-AB10)</f>
+        <f t="shared" si="13"/>
         <v>24.228568841811072</v>
       </c>
-      <c r="AG10" s="62" t="s">
+      <c r="AG10" s="49" t="s">
         <v>148</v>
       </c>
       <c r="AH10" s="12">
@@ -2732,7 +2732,7 @@
         <v>3</v>
       </c>
       <c r="AJ10" s="7" t="str">
-        <f>AI10&amp;D10</f>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AK10" s="7">
@@ -2740,34 +2740,34 @@
         <v>1</v>
       </c>
       <c r="AL10" s="5">
-        <f>Q10/AH10</f>
+        <f t="shared" si="15"/>
         <v>5.5818852027382841E-2</v>
       </c>
       <c r="AM10" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="18"/>
         <v>na</v>
       </c>
       <c r="AN10" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>na</v>
       </c>
       <c r="AO10" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>na</v>
       </c>
       <c r="AP10" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>na</v>
       </c>
-      <c r="AQ10" s="62"/>
+      <c r="AQ10" s="49"/>
       <c r="AR10" s="12"/>
       <c r="AS10" s="12"/>
       <c r="AT10" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="19"/>
         <v>na</v>
       </c>
       <c r="AU10" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>na</v>
       </c>
       <c r="AV10" s="7" t="str">
@@ -2775,15 +2775,15 @@
         <v>na</v>
       </c>
       <c r="AW10" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>na</v>
       </c>
     </row>
     <row r="11" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="48" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -2805,29 +2805,29 @@
         <f>1138639-7832</f>
         <v>1130807</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11" s="42">
         <f>16108809/17049715</f>
         <v>0.94481397489635455</v>
       </c>
-      <c r="K11" s="60">
+      <c r="K11" s="47">
         <f>286123+25282</f>
         <v>311405</v>
       </c>
-      <c r="L11" s="60">
+      <c r="L11" s="47">
         <f>917+31715</f>
         <v>32632</v>
       </c>
       <c r="M11" s="37">
         <v>-255176</v>
       </c>
-      <c r="N11" s="53">
+      <c r="N11" s="43">
         <v>0.25</v>
       </c>
       <c r="O11" s="37">
         <v>86479</v>
       </c>
-      <c r="P11" s="59">
-        <f t="shared" si="2"/>
+      <c r="P11" s="46">
+        <f t="shared" si="17"/>
         <v>54408.75</v>
       </c>
       <c r="Q11" s="38">
@@ -2843,58 +2843,58 @@
         <v>0.81943449848268335</v>
       </c>
       <c r="T11" s="34">
-        <f>P11/I11</f>
+        <f t="shared" si="1"/>
         <v>4.8114974527041304E-2</v>
       </c>
       <c r="U11" s="35">
-        <f>K11/H11</f>
+        <f t="shared" si="2"/>
         <v>1.7119080866347919E-2</v>
       </c>
       <c r="V11" s="36">
-        <f>H11/I11</f>
+        <f t="shared" si="3"/>
         <v>16.086318001215062</v>
       </c>
       <c r="W11" s="34">
-        <f>P11/K11</f>
+        <f t="shared" si="4"/>
         <v>0.17472021964965237</v>
       </c>
       <c r="X11" s="36">
-        <f>I11/(G11/1000000)*$AK11</f>
+        <f t="shared" si="5"/>
         <v>9.4159331889162896</v>
       </c>
       <c r="Y11" s="36">
-        <f>P11/(G11/1000000)*$AK11</f>
+        <f t="shared" si="6"/>
         <v>0.45304738553303009</v>
       </c>
       <c r="Z11" s="6">
-        <f>Q11/Y11</f>
+        <f t="shared" si="7"/>
         <v>0.57742304304927428</v>
       </c>
       <c r="AA11" s="7">
-        <f>(T11-g)/(k-g)</f>
+        <f t="shared" si="8"/>
         <v>0.46858290878402176</v>
       </c>
       <c r="AB11" s="7">
-        <f>X11*AA11</f>
+        <f t="shared" si="9"/>
         <v>4.4121453625784044</v>
       </c>
       <c r="AC11" s="7">
-        <f>PV(Target_return,Holding_Period,-Q11,-AB11)</f>
+        <f t="shared" si="10"/>
         <v>2.5119358831760321</v>
       </c>
       <c r="AD11" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q11,-AB11)</f>
+        <f t="shared" si="11"/>
         <v>3.0989390499793994</v>
       </c>
       <c r="AE11" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q11,-AB11)</f>
+        <f t="shared" si="12"/>
         <v>3.7935880218656868</v>
       </c>
       <c r="AF11" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q11,-AB11)</f>
+        <f t="shared" si="13"/>
         <v>4.259894726825121</v>
       </c>
-      <c r="AG11" s="62" t="s">
+      <c r="AG11" s="49" t="s">
         <v>149</v>
       </c>
       <c r="AH11" s="12">
@@ -2904,7 +2904,7 @@
         <v>3</v>
       </c>
       <c r="AJ11" s="7" t="str">
-        <f>AI11&amp;D11</f>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AK11" s="7">
@@ -2912,26 +2912,26 @@
         <v>1</v>
       </c>
       <c r="AL11" s="5">
-        <f>Q11/AH11</f>
+        <f t="shared" si="15"/>
         <v>5.0599613152804646E-2</v>
       </c>
       <c r="AM11" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="18"/>
         <v>2.8223998687371146</v>
       </c>
       <c r="AN11" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>3.4819539887408983</v>
       </c>
       <c r="AO11" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>4.2624584515344797</v>
       </c>
       <c r="AP11" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>4.7863985694664279</v>
       </c>
-      <c r="AQ11" s="62" t="s">
+      <c r="AQ11" s="49" t="s">
         <v>157</v>
       </c>
       <c r="AR11" s="12">
@@ -2941,11 +2941,11 @@
         <v>107</v>
       </c>
       <c r="AT11" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="19"/>
         <v>-0.13926499032882012</v>
       </c>
       <c r="AU11" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AV11" s="7">
@@ -2953,15 +2953,15 @@
         <v>0.89</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>5.8786516853932581E-2</v>
       </c>
     </row>
     <row r="12" spans="2:49" x14ac:dyDescent="0.45">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="48" t="s">
         <v>116</v>
       </c>
       <c r="D12" s="10" t="s">
@@ -2983,29 +2983,29 @@
         <f>1289233-6153-9954-47907</f>
         <v>1225219</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12" s="42">
         <f>9509526/11360291</f>
         <v>0.83708471904460902</v>
       </c>
-      <c r="K12" s="60">
+      <c r="K12" s="47">
         <f>211277+72094</f>
         <v>283371</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="47">
         <f>14126+29880</f>
         <v>44006</v>
       </c>
       <c r="M12" s="37">
         <v>-158469</v>
       </c>
-      <c r="N12" s="53">
+      <c r="N12" s="43">
         <v>0.25</v>
       </c>
       <c r="O12" s="37">
         <v>149559</v>
       </c>
-      <c r="P12" s="59">
-        <f t="shared" si="2"/>
+      <c r="P12" s="46">
+        <f t="shared" si="17"/>
         <v>110178.75</v>
       </c>
       <c r="Q12" s="38">
@@ -3020,58 +3020,58 @@
         <v>0.55922800851180965</v>
       </c>
       <c r="T12" s="34">
-        <f>P12/I12</f>
+        <f t="shared" si="1"/>
         <v>8.9925760211031658E-2</v>
       </c>
       <c r="U12" s="35">
-        <f>K12/H12</f>
+        <f t="shared" si="2"/>
         <v>2.2388213587718121E-2</v>
       </c>
       <c r="V12" s="36">
-        <f>H12/I12</f>
+        <f t="shared" si="3"/>
         <v>10.33052131904582</v>
       </c>
       <c r="W12" s="34">
-        <f t="shared" ref="W12" si="7">P12/K12</f>
+        <f t="shared" ref="W12" si="22">P12/K12</f>
         <v>0.38881448701525562</v>
       </c>
       <c r="X12" s="36">
-        <f>I12/(G12/1000000)*$AK12</f>
+        <f t="shared" si="5"/>
         <v>48.581542463979972</v>
       </c>
       <c r="Y12" s="36">
-        <f>P12/(G12/1000000)*$AK12</f>
+        <f t="shared" si="6"/>
         <v>4.368732138297915</v>
       </c>
       <c r="Z12" s="6">
-        <f>Q12/Y12</f>
+        <f t="shared" si="7"/>
         <v>0.45779872436381791</v>
       </c>
       <c r="AA12" s="7">
-        <f>(T12-g)/(k-g)</f>
+        <f t="shared" si="8"/>
         <v>1.1654293368505275</v>
       </c>
       <c r="AB12" s="7">
-        <f>X12*AA12</f>
+        <f t="shared" si="9"/>
         <v>56.618354816971923</v>
       </c>
       <c r="AC12" s="7">
-        <f>PV(Target_return,Holding_Period,-Q12,-AB12)</f>
+        <f t="shared" si="10"/>
         <v>29.75111090197689</v>
       </c>
       <c r="AD12" s="7">
-        <f>PV(Entry_yield,Holding_Period,-Q12,-AB12)</f>
+        <f t="shared" si="11"/>
         <v>36.911750749106794</v>
       </c>
       <c r="AE12" s="7">
-        <f>PV(Benchmark_yield,Holding_Period,-Q12,-AB12)</f>
+        <f t="shared" si="12"/>
         <v>45.407000502341631</v>
       </c>
       <c r="AF12" s="7">
-        <f>PV(Base_Cost_of_Equity,Holding_Period,-Q12,-AB12)</f>
+        <f t="shared" si="13"/>
         <v>51.11974717559962</v>
       </c>
-      <c r="AG12" s="62" t="s">
+      <c r="AG12" s="49" t="s">
         <v>150</v>
       </c>
       <c r="AH12" s="12">
@@ -3081,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="AJ12" s="7" t="str">
-        <f>AI12&amp;D12</f>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AK12" s="7">
@@ -3089,26 +3089,26 @@
         <v>1</v>
       </c>
       <c r="AL12" s="5">
-        <f>Q12/AH12</f>
+        <f t="shared" si="15"/>
         <v>5.2562417871222081E-2</v>
       </c>
       <c r="AM12" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="18"/>
         <v>33.428214496603246</v>
       </c>
       <c r="AN12" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>41.473877246187406</v>
       </c>
       <c r="AO12" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>51.019101688024307</v>
       </c>
       <c r="AP12" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="16"/>
         <v>57.437918174831033</v>
       </c>
-      <c r="AQ12" s="62" t="s">
+      <c r="AQ12" s="49" t="s">
         <v>158</v>
       </c>
       <c r="AR12" s="12">
@@ -3118,11 +3118,11 @@
         <v>107</v>
       </c>
       <c r="AT12" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="19"/>
         <v>8.7180026281209022E-2</v>
       </c>
       <c r="AU12" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AV12" s="7">
@@ -3130,7 +3130,7 @@
         <v>0.89</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>4.8347483030033465E-2</v>
       </c>
     </row>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FB43D6-FE21-4CA7-B17D-038AFBC06517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87292F5E-6821-4649-B69E-6070DE8569DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="165">
   <si>
     <t>Name</t>
   </si>
@@ -532,6 +532,15 @@
   </si>
   <si>
     <t>市场溢价</t>
+  </si>
+  <si>
+    <t>Company specific Premium</t>
+  </si>
+  <si>
+    <t>风险溢价</t>
+  </si>
+  <si>
+    <t>股票代码</t>
   </si>
 </sst>
 </file>
@@ -733,7 +742,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -902,6 +911,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1420,25 +1432,24 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:AW12"/>
+  <dimension ref="B2:AX12"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="9" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="18.6640625" customWidth="1" collapsed="1"/>
-    <col min="11" max="17" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="18.6640625" customWidth="1" collapsed="1"/>
-    <col min="19" max="23" width="18.6640625" customWidth="1"/>
-    <col min="24" max="26" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="18.796875" customWidth="1" collapsed="1"/>
-    <col min="28" max="32" width="18.796875" customWidth="1"/>
-    <col min="33" max="35" width="16.59765625" customWidth="1"/>
-    <col min="36" max="37" width="16.59765625" hidden="1" customWidth="1"/>
-    <col min="38" max="49" width="16.59765625" customWidth="1"/>
+    <col min="4" max="10" width="18.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="18.6640625" customWidth="1"/>
+    <col min="12" max="18" width="18.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="24" width="18.6640625" customWidth="1"/>
+    <col min="25" max="27" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="18.796875" customWidth="1" collapsed="1"/>
+    <col min="29" max="33" width="18.796875" customWidth="1"/>
+    <col min="34" max="36" width="16.59765625" customWidth="1"/>
+    <col min="37" max="38" width="16.59765625" hidden="1" customWidth="1"/>
+    <col min="39" max="50" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:49" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:50" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>103</v>
       </c>
@@ -1454,69 +1465,69 @@
       <c r="F2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AC2" s="15"/>
       <c r="AD2" s="15"/>
       <c r="AE2" s="15"/>
       <c r="AF2" s="15"/>
-      <c r="AG2" s="2"/>
+      <c r="AG2" s="15"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -1533,8 +1544,9 @@
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
-    </row>
-    <row r="3" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AX2" s="2"/>
+    </row>
+    <row r="3" spans="2:50" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="53" t="s">
         <v>55</v>
       </c>
@@ -1547,76 +1559,77 @@
       <c r="G3" s="57"/>
       <c r="H3" s="57"/>
       <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59" t="s">
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="L3" s="59"/>
       <c r="M3" s="59"/>
       <c r="N3" s="59"/>
       <c r="O3" s="59"/>
       <c r="P3" s="59"/>
       <c r="Q3" s="59"/>
-      <c r="R3" s="60" t="s">
+      <c r="R3" s="59"/>
+      <c r="S3" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="S3" s="61"/>
       <c r="T3" s="61"/>
       <c r="U3" s="61"/>
       <c r="V3" s="61"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="51" t="s">
+      <c r="W3" s="61"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="Y3" s="51"/>
       <c r="Z3" s="51"/>
-      <c r="AA3" s="52" t="s">
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="27" t="s">
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="AD3" s="27" t="s">
+      <c r="AE3" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AF3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="AF3" s="27" t="s">
+      <c r="AG3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AG3" s="50" t="s">
+      <c r="AH3" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="AH3" s="50"/>
       <c r="AI3" s="50"/>
       <c r="AJ3" s="50"/>
       <c r="AK3" s="50"/>
       <c r="AL3" s="50"/>
-      <c r="AM3" s="27" t="s">
+      <c r="AM3" s="50"/>
+      <c r="AN3" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="AN3" s="27" t="s">
+      <c r="AO3" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AP3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="AP3" s="27" t="s">
+      <c r="AQ3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AQ3" s="50" t="s">
+      <c r="AR3" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="AR3" s="50"/>
       <c r="AS3" s="50"/>
       <c r="AT3" s="50"/>
       <c r="AU3" s="50"/>
       <c r="AV3" s="50"/>
       <c r="AW3" s="50"/>
-    </row>
-    <row r="4" spans="2:49" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="AX3" s="50"/>
+    </row>
+    <row r="4" spans="2:50" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="32" t="s">
         <v>73</v>
       </c>
@@ -1633,136 +1646,139 @@
         <v>69</v>
       </c>
       <c r="G4" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="I4" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="J4" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="K4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="K4" s="44" t="s">
+      <c r="L4" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="44" t="s">
+      <c r="M4" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="M4" s="44" t="s">
+      <c r="N4" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="N4" s="44" t="s">
+      <c r="O4" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="O4" s="44" t="s">
+      <c r="P4" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="P4" s="44" t="s">
+      <c r="Q4" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="Q4" s="44" t="s">
+      <c r="R4" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="S4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="S4" s="28" t="s">
+      <c r="T4" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="T4" s="28" t="s">
+      <c r="U4" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="28" t="s">
+      <c r="V4" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="28" t="s">
+      <c r="W4" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="W4" s="28" t="s">
+      <c r="X4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="Y4" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Y4" s="24" t="s">
+      <c r="Z4" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="Z4" s="24" t="s">
+      <c r="AA4" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="AA4" s="22" t="s">
+      <c r="AB4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="AB4" s="22" t="s">
+      <c r="AC4" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AC4" s="18" t="s">
+      <c r="AD4" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="AD4" s="18" t="s">
+      <c r="AE4" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="AE4" s="18" t="s">
+      <c r="AF4" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="AF4" s="18" t="s">
+      <c r="AG4" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="AG4" s="20" t="s">
+      <c r="AH4" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="AH4" s="20" t="s">
+      <c r="AI4" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="AI4" s="20" t="s">
+      <c r="AJ4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="AJ4" s="20" t="s">
+      <c r="AK4" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="AK4" s="20" t="s">
+      <c r="AL4" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="AL4" s="20" t="s">
+      <c r="AM4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="AM4" s="18" t="s">
+      <c r="AN4" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="AN4" s="18" t="s">
+      <c r="AO4" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="AO4" s="18" t="s">
+      <c r="AP4" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="AP4" s="18" t="s">
+      <c r="AQ4" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="AQ4" s="20" t="s">
+      <c r="AR4" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="AR4" s="20" t="s">
+      <c r="AS4" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="AS4" s="20" t="s">
+      <c r="AT4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="AT4" s="20" t="s">
+      <c r="AU4" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="AU4" s="20" t="s">
+      <c r="AV4" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="AV4" s="20" t="s">
+      <c r="AW4" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="AW4" s="20" t="s">
+      <c r="AX4" s="20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B5" s="33" t="s">
         <v>72</v>
       </c>
@@ -1779,124 +1795,135 @@
         <v>50</v>
       </c>
       <c r="G5" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="I5" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="J5" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="K5" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="45" t="s">
+      <c r="L5" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="L5" s="45" t="s">
+      <c r="M5" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="M5" s="45" t="s">
+      <c r="N5" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="N5" s="45" t="s">
+      <c r="O5" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="O5" s="45" t="s">
+      <c r="P5" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="P5" s="45" t="s">
+      <c r="Q5" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="Q5" s="45" t="s">
+      <c r="R5" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="29" t="s">
+      <c r="S5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="29" t="s">
+      <c r="T5" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="U5" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="U5" s="29" t="s">
+      <c r="V5" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="W5" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="W5" s="29" t="s">
+      <c r="X5" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="X5" s="25" t="s">
+      <c r="Y5" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="Y5" s="26" t="s">
+      <c r="Z5" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="Z5" s="26" t="s">
+      <c r="AA5" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AB5" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AB5" s="23" t="s">
+      <c r="AC5" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AC5" s="19" t="s">
+      <c r="AD5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="AD5" s="19" t="s">
+      <c r="AE5" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AE5" s="19" t="s">
+      <c r="AF5" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="AF5" s="19" t="s">
+      <c r="AG5" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="AG5" s="21"/>
       <c r="AH5" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI5" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="AI5" s="21" t="s">
+      <c r="AJ5" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="AJ5" s="21"/>
       <c r="AK5" s="21"/>
-      <c r="AL5" s="21" t="s">
+      <c r="AL5" s="21"/>
+      <c r="AM5" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="AM5" s="19" t="s">
+      <c r="AN5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="AN5" s="19" t="s">
+      <c r="AO5" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AO5" s="19" t="s">
+      <c r="AP5" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="AP5" s="19" t="s">
+      <c r="AQ5" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="AQ5" s="21"/>
       <c r="AR5" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS5" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="AS5" s="21" t="s">
+      <c r="AT5" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="AT5" s="21" t="s">
+      <c r="AU5" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AU5" s="21"/>
-      <c r="AV5" s="21"/>
+      <c r="AV5" s="21" t="s">
+        <v>53</v>
+      </c>
       <c r="AW5" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="AX5" s="21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B6" s="48" t="s">
         <v>22</v>
       </c>
@@ -1912,169 +1939,172 @@
       <c r="F6" s="9">
         <v>45838</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="63">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37">
         <v>356406257089</v>
       </c>
-      <c r="H6" s="37">
+      <c r="I6" s="37">
         <v>52317931</v>
       </c>
-      <c r="I6" s="37">
+      <c r="J6" s="37">
         <f>4114692-23118-19420-59031</f>
         <v>4013123</v>
       </c>
-      <c r="J6" s="42">
+      <c r="K6" s="42">
         <f>36904556/48179055</f>
         <v>0.76598754375734435</v>
       </c>
-      <c r="K6" s="47">
+      <c r="L6" s="47">
         <f>637405+109397</f>
         <v>746802</v>
       </c>
-      <c r="L6" s="47">
+      <c r="M6" s="47">
         <f>28762+40930</f>
         <v>69692</v>
       </c>
-      <c r="M6" s="37">
+      <c r="N6" s="37">
         <v>-400918</v>
       </c>
-      <c r="N6" s="43">
+      <c r="O6" s="43">
         <v>0.25</v>
       </c>
-      <c r="O6" s="37">
+      <c r="P6" s="37">
         <v>366946</v>
       </c>
-      <c r="P6" s="46">
-        <f>(K6+L6/2+M6)*(1-N6)</f>
+      <c r="Q6" s="46">
+        <f>(L6+M6/2+N6)*(1-O6)</f>
         <v>285547.5</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="R6" s="38">
         <f>0.1646+0.1434</f>
         <v>0.308</v>
       </c>
-      <c r="R6" s="11">
+      <c r="S6" s="11">
         <f>637405/27613781</f>
         <v>2.3082858519085089E-2</v>
       </c>
-      <c r="S6" s="34">
-        <f t="shared" ref="S6:S11" si="0">-M6/K6</f>
+      <c r="T6" s="34">
+        <f t="shared" ref="T6:T11" si="0">-N6/L6</f>
         <v>0.53684644658155711</v>
       </c>
-      <c r="T6" s="34">
-        <f t="shared" ref="T6:T12" si="1">P6/I6</f>
+      <c r="U6" s="34">
+        <f t="shared" ref="U6:U12" si="1">Q6/J6</f>
         <v>7.115343835710991E-2</v>
       </c>
-      <c r="U6" s="35">
-        <f t="shared" ref="U6:U12" si="2">K6/H6</f>
+      <c r="V6" s="35">
+        <f t="shared" ref="V6:V12" si="2">L6/I6</f>
         <v>1.4274303010950491E-2</v>
       </c>
-      <c r="V6" s="36">
-        <f t="shared" ref="V6:V12" si="3">H6/I6</f>
+      <c r="W6" s="36">
+        <f t="shared" ref="W6:W12" si="3">I6/J6</f>
         <v>13.036712555284252</v>
       </c>
-      <c r="W6" s="34">
-        <f t="shared" ref="W6:W11" si="4">P6/K6</f>
+      <c r="X6" s="34">
+        <f t="shared" ref="X6:X11" si="4">Q6/L6</f>
         <v>0.38236038468027672</v>
       </c>
-      <c r="X6" s="36">
-        <f t="shared" ref="X6:X12" si="5">I6/(G6/1000000)*$AK6</f>
+      <c r="Y6" s="36">
+        <f t="shared" ref="Y6:Y12" si="5">J6/(H6/1000000)*$AL6</f>
         <v>11.259967860210329</v>
       </c>
-      <c r="Y6" s="36">
-        <f t="shared" ref="Y6:Y12" si="6">P6/(G6/1000000)*$AK6</f>
+      <c r="Z6" s="36">
+        <f t="shared" ref="Z6:Z12" si="6">Q6/(H6/1000000)*$AL6</f>
         <v>0.8011854290445144</v>
       </c>
-      <c r="Z6" s="6">
-        <f t="shared" ref="Z6:Z12" si="7">Q6/Y6</f>
+      <c r="AA6" s="6">
+        <f t="shared" ref="AA6:AA12" si="7">R6/Z6</f>
         <v>0.38443035636246864</v>
       </c>
-      <c r="AA6" s="7">
-        <f t="shared" ref="AA6:AA12" si="8">(T6-g)/(k-g)</f>
+      <c r="AB6" s="7">
+        <f>(U6-g)/((k+G6)-g)</f>
         <v>0.85255730595183177</v>
       </c>
-      <c r="AB6" s="7">
-        <f t="shared" ref="AB6:AB12" si="9">X6*AA6</f>
+      <c r="AC6" s="7">
+        <f t="shared" ref="AC6:AC12" si="8">Y6*AB6</f>
         <v>9.5997678640051305</v>
       </c>
-      <c r="AC6" s="7">
-        <f t="shared" ref="AC6:AC12" si="10">PV(Target_return,Holding_Period,-Q6,-AB6)</f>
+      <c r="AD6" s="7">
+        <f t="shared" ref="AD6:AD12" si="9">PV(Target_return,Holding_Period,-R6,-AC6)</f>
         <v>4.9874504439696281</v>
       </c>
-      <c r="AD6" s="7">
-        <f t="shared" ref="AD6:AD12" si="11">PV(Entry_yield,Holding_Period,-Q6,-AB6)</f>
+      <c r="AE6" s="7">
+        <f t="shared" ref="AE6:AE12" si="10">PV(Entry_yield,Holding_Period,-R6,-AC6)</f>
         <v>6.1930254837762826</v>
       </c>
-      <c r="AE6" s="7">
-        <f t="shared" ref="AE6:AE12" si="12">PV(Benchmark_yield,Holding_Period,-Q6,-AB6)</f>
+      <c r="AF6" s="7">
+        <f t="shared" ref="AF6:AF12" si="11">PV(Benchmark_yield,Holding_Period,-R6,-AC6)</f>
         <v>7.623815149844293</v>
       </c>
-      <c r="AF6" s="7">
-        <f t="shared" ref="AF6:AF12" si="13">PV(Base_Cost_of_Equity,Holding_Period,-Q6,-AB6)</f>
+      <c r="AG6" s="7">
+        <f t="shared" ref="AG6:AG12" si="12">PV(Base_Cost_of_Equity,Holding_Period,-R6,-AC6)</f>
         <v>8.5862102417703685</v>
       </c>
-      <c r="AG6" s="49" t="s">
+      <c r="AH6" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="AH6" s="12">
+      <c r="AI6" s="12">
         <v>7.26</v>
       </c>
-      <c r="AI6" s="12" t="s">
+      <c r="AJ6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="AJ6" s="7" t="str">
-        <f t="shared" ref="AJ6:AJ12" si="14">AI6&amp;D6</f>
+      <c r="AK6" s="7" t="str">
+        <f t="shared" ref="AK6:AK12" si="13">AJ6&amp;D6</f>
         <v>CNYCNY</v>
       </c>
-      <c r="AK6" s="7">
-        <f>IFERROR(VLOOKUP(AJ6,Assumptions!B$12:C$13,2,FALSE),1)</f>
+      <c r="AL6" s="7">
+        <f>IFERROR(VLOOKUP(AK6,Assumptions!B$12:C$13,2,FALSE),1)</f>
         <v>1</v>
       </c>
-      <c r="AL6" s="5">
-        <f t="shared" ref="AL6:AL12" si="15">Q6/AH6</f>
+      <c r="AM6" s="5">
+        <f t="shared" ref="AM6:AM12" si="14">R6/AI6</f>
         <v>4.2424242424242427E-2</v>
       </c>
-      <c r="AM6" s="7">
-        <f>IF($AQ6="","na",AC6/$AV6)</f>
+      <c r="AN6" s="7">
+        <f>IF($AR6="","na",AD6/$AW6)</f>
         <v>5.6038769033366611</v>
       </c>
-      <c r="AN6" s="7">
-        <f t="shared" ref="AN6:AP12" si="16">IF($AQ6="","na",AD6/$AV6)</f>
+      <c r="AO6" s="7">
+        <f t="shared" ref="AO6:AQ12" si="15">IF($AR6="","na",AE6/$AW6)</f>
         <v>6.9584555997486319</v>
       </c>
-      <c r="AO6" s="7">
-        <f t="shared" si="16"/>
+      <c r="AP6" s="7">
+        <f t="shared" si="15"/>
         <v>8.5660844380272962</v>
       </c>
-      <c r="AP6" s="7">
-        <f t="shared" si="16"/>
+      <c r="AQ6" s="7">
+        <f t="shared" si="15"/>
         <v>9.6474272379442336</v>
       </c>
-      <c r="AQ6" s="49" t="s">
+      <c r="AR6" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="AR6" s="12">
+      <c r="AS6" s="12">
         <v>6.23</v>
       </c>
-      <c r="AS6" s="12" t="s">
+      <c r="AT6" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="AT6" s="34">
-        <f>IF($AQ6="","na",AR6/(AH6/AV6)-1)</f>
+      <c r="AU6" s="34">
+        <f>IF($AR6="","na",AS6/(AI6/AW6)-1)</f>
         <v>-0.2362672176308539</v>
       </c>
-      <c r="AU6" s="7" t="str">
-        <f>IF($AQ6="","na",AS6&amp;D6)</f>
+      <c r="AV6" s="7" t="str">
+        <f>IF($AR6="","na",AT6&amp;D6)</f>
         <v>HKDCNY</v>
       </c>
-      <c r="AV6" s="7">
-        <f>IF($AQ6="","na",IFERROR(VLOOKUP(AU6,Assumptions!B$12:C$13,2,FALSE),1))</f>
+      <c r="AW6" s="7">
+        <f>IF($AR6="","na",IFERROR(VLOOKUP(AV6,Assumptions!B$12:C$13,2,FALSE),1))</f>
         <v>0.89</v>
       </c>
-      <c r="AW6" s="5">
-        <f>IF($AQ6="","na",(Q6/AV6)/AR6)</f>
+      <c r="AX6" s="5">
+        <f>IF($AR6="","na",(R6/AW6)/AS6)</f>
         <v>5.5548541850776408E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B7" s="48" t="s">
         <v>23</v>
       </c>
@@ -2090,169 +2120,172 @@
       <c r="F7" s="9">
         <v>45838</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="63">
+        <v>0</v>
+      </c>
+      <c r="H7" s="37">
         <v>261600381459</v>
       </c>
-      <c r="H7" s="37">
+      <c r="I7" s="37">
         <v>44432848</v>
       </c>
-      <c r="I7" s="37">
+      <c r="J7" s="37">
         <f>3563298-4942-2461</f>
         <v>3555895</v>
       </c>
-      <c r="J7" s="42">
+      <c r="K7" s="42">
         <f>30469491/40847989</f>
         <v>0.74592389358506728</v>
       </c>
-      <c r="K7" s="47">
+      <c r="L7" s="47">
         <f>589882+104928</f>
         <v>694810</v>
       </c>
-      <c r="L7" s="47">
+      <c r="M7" s="47">
         <f>21210+21417</f>
         <v>42627</v>
       </c>
-      <c r="M7" s="37">
+      <c r="N7" s="37">
         <v>-365879</v>
       </c>
-      <c r="N7" s="43">
+      <c r="O7" s="43">
         <v>0.25</v>
       </c>
-      <c r="O7" s="37">
+      <c r="P7" s="37">
         <v>335577</v>
       </c>
-      <c r="P7" s="46">
-        <f t="shared" ref="P7:P12" si="17">(K7+L7/2+M7)*(1-N7)</f>
+      <c r="Q7" s="46">
+        <f t="shared" ref="Q7:Q12" si="16">(L7+M7/2+N7)*(1-O7)</f>
         <v>262683.375</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="R7" s="38">
         <f>0.206+0.197</f>
         <v>0.40300000000000002</v>
       </c>
-      <c r="R7" s="11">
+      <c r="S7" s="11">
         <f>589882/25040400</f>
         <v>2.3557211546141436E-2</v>
       </c>
-      <c r="S7" s="34">
+      <c r="T7" s="34">
         <f t="shared" si="0"/>
         <v>0.52658856378002616</v>
       </c>
-      <c r="T7" s="34">
+      <c r="U7" s="34">
         <f t="shared" si="1"/>
         <v>7.3872646689511365E-2</v>
       </c>
-      <c r="U7" s="35">
+      <c r="V7" s="35">
         <f t="shared" si="2"/>
         <v>1.5637305085642945E-2</v>
       </c>
-      <c r="V7" s="36">
+      <c r="W7" s="36">
         <f t="shared" si="3"/>
         <v>12.495545565884257</v>
       </c>
-      <c r="W7" s="34">
+      <c r="X7" s="34">
         <f t="shared" si="4"/>
         <v>0.37806504655949108</v>
       </c>
-      <c r="X7" s="36">
+      <c r="Y7" s="36">
         <f t="shared" si="5"/>
         <v>13.592850974329741</v>
       </c>
-      <c r="Y7" s="36">
+      <c r="Z7" s="36">
         <f t="shared" si="6"/>
         <v>1.0041398775298411</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="AA7" s="6">
         <f t="shared" si="7"/>
         <v>0.40133850772998869</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AB7" s="7">
+        <f>(U7-g)/((k+G7)-g)</f>
+        <v>0.89787744482518939</v>
+      </c>
+      <c r="AC7" s="7">
         <f t="shared" si="8"/>
-        <v>0.89787744482518939</v>
-      </c>
-      <c r="AB7" s="7">
+        <v>12.204714300720774</v>
+      </c>
+      <c r="AD7" s="7">
         <f t="shared" si="9"/>
-        <v>12.204714300720774</v>
-      </c>
-      <c r="AC7" s="7">
+        <v>6.3617224896519993</v>
+      </c>
+      <c r="AE7" s="7">
         <f t="shared" si="10"/>
-        <v>6.3617224896519993</v>
-      </c>
-      <c r="AD7" s="7">
+        <v>7.8975680604798519</v>
+      </c>
+      <c r="AF7" s="7">
         <f t="shared" si="11"/>
-        <v>7.8975680604798519</v>
-      </c>
-      <c r="AE7" s="7">
+        <v>9.7201348785712796</v>
+      </c>
+      <c r="AG7" s="7">
         <f t="shared" si="12"/>
-        <v>9.7201348785712796</v>
-      </c>
-      <c r="AF7" s="7">
+        <v>10.945962753461778</v>
+      </c>
+      <c r="AH7" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI7" s="12">
+        <v>8.68</v>
+      </c>
+      <c r="AJ7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>10.945962753461778</v>
-      </c>
-      <c r="AG7" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="AH7" s="12">
-        <v>8.68</v>
-      </c>
-      <c r="AI7" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ7" s="7" t="str">
+        <v>CNYCNY</v>
+      </c>
+      <c r="AL7" s="7">
+        <f>IFERROR(VLOOKUP(AK7,Assumptions!B$12:C$13,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AM7" s="5">
         <f t="shared" si="14"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AK7" s="7">
-        <f>IFERROR(VLOOKUP(AJ7,Assumptions!B$12:C$13,2,FALSE),1)</f>
-        <v>1</v>
-      </c>
-      <c r="AL7" s="5">
+        <v>4.642857142857143E-2</v>
+      </c>
+      <c r="AN7" s="7">
+        <f t="shared" ref="AN7:AN12" si="17">IF($AR7="","na",AD7/$AW7)</f>
+        <v>7.148002797361797</v>
+      </c>
+      <c r="AO7" s="7">
         <f t="shared" si="15"/>
-        <v>4.642857142857143E-2</v>
-      </c>
-      <c r="AM7" s="7">
-        <f t="shared" ref="AM7:AM12" si="18">IF($AQ7="","na",AC7/$AV7)</f>
-        <v>7.148002797361797</v>
-      </c>
-      <c r="AN7" s="7">
-        <f t="shared" si="16"/>
         <v>8.8736719780672484</v>
       </c>
-      <c r="AO7" s="7">
-        <f t="shared" si="16"/>
+      <c r="AP7" s="7">
+        <f t="shared" si="15"/>
         <v>10.921499863563236</v>
       </c>
-      <c r="AP7" s="7">
-        <f t="shared" si="16"/>
+      <c r="AQ7" s="7">
+        <f t="shared" si="15"/>
         <v>12.298834554451435</v>
       </c>
-      <c r="AQ7" s="49" t="s">
+      <c r="AR7" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="AR7" s="12">
+      <c r="AS7" s="12">
         <v>7.65</v>
       </c>
-      <c r="AS7" s="12" t="s">
+      <c r="AT7" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="AT7" s="34">
-        <f t="shared" ref="AT7:AT12" si="19">IF($AQ7="","na",AR7/(AH7/AV7)-1)</f>
+      <c r="AU7" s="34">
+        <f t="shared" ref="AU7:AU12" si="18">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
         <v>-0.21561059907834101</v>
       </c>
-      <c r="AU7" s="7" t="str">
-        <f t="shared" ref="AU7:AU12" si="20">IF($AQ7="","na",AS7&amp;D7)</f>
+      <c r="AV7" s="7" t="str">
+        <f t="shared" ref="AV7:AV12" si="19">IF($AR7="","na",AT7&amp;D7)</f>
         <v>HKDCNY</v>
       </c>
-      <c r="AV7" s="7">
-        <f>IF($AQ7="","na",IFERROR(VLOOKUP(AU7,Assumptions!B$12:C$13,2,FALSE),1))</f>
+      <c r="AW7" s="7">
+        <f>IF($AR7="","na",IFERROR(VLOOKUP(AV7,Assumptions!B$12:C$13,2,FALSE),1))</f>
         <v>0.89</v>
       </c>
-      <c r="AW7" s="5">
-        <f t="shared" ref="AW7:AW12" si="21">IF($AQ7="","na",(Q7/AV7)/AR7)</f>
+      <c r="AX7" s="5">
+        <f t="shared" ref="AX7:AX12" si="20">IF($AR7="","na",(R7/AW7)/AS7)</f>
         <v>5.9190717485496071E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B8" s="48" t="s">
         <v>24</v>
       </c>
@@ -2268,169 +2301,172 @@
       <c r="F8" s="9">
         <v>45838</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="63">
+        <v>0</v>
+      </c>
+      <c r="H8" s="37">
         <v>349983033873</v>
       </c>
-      <c r="H8" s="37">
+      <c r="I8" s="37">
         <v>46855878</v>
       </c>
-      <c r="I8" s="37">
+      <c r="J8" s="37">
         <f>3143100-28563-1381-300488</f>
         <v>2812668</v>
       </c>
-      <c r="J8" s="42">
+      <c r="K8" s="42">
         <f>31900486/43706637</f>
         <v>0.72987738681427261</v>
       </c>
-      <c r="K8" s="47">
+      <c r="L8" s="47">
         <f>580692+75567</f>
         <v>656259</v>
       </c>
-      <c r="L8" s="47">
+      <c r="M8" s="47">
         <f>7943+31139</f>
         <v>39082</v>
       </c>
-      <c r="M8" s="37">
+      <c r="N8" s="37">
         <v>-390774</v>
       </c>
-      <c r="N8" s="43">
+      <c r="O8" s="43">
         <v>0.25</v>
       </c>
-      <c r="O8" s="37">
+      <c r="P8" s="37">
         <v>282083</v>
       </c>
-      <c r="P8" s="46">
-        <f t="shared" si="17"/>
+      <c r="Q8" s="46">
+        <f t="shared" si="16"/>
         <v>213769.5</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="R8" s="38">
         <f>0.1255+0.1164</f>
         <v>0.2419</v>
       </c>
-      <c r="R8" s="11">
+      <c r="S8" s="11">
         <f>580692/23977013</f>
         <v>2.4218696465652331E-2</v>
       </c>
-      <c r="S8" s="34">
+      <c r="T8" s="34">
         <f t="shared" si="0"/>
         <v>0.59545697659003538</v>
       </c>
-      <c r="T8" s="34">
+      <c r="U8" s="34">
         <f t="shared" si="1"/>
         <v>7.6002393457030831E-2</v>
       </c>
-      <c r="U8" s="35">
+      <c r="V8" s="35">
         <f t="shared" si="2"/>
         <v>1.400590551307138E-2</v>
       </c>
-      <c r="V8" s="36">
+      <c r="W8" s="36">
         <f t="shared" si="3"/>
         <v>16.658872643340771</v>
       </c>
-      <c r="W8" s="34">
+      <c r="X8" s="34">
         <f t="shared" si="4"/>
         <v>0.32573953271497991</v>
       </c>
-      <c r="X8" s="36">
+      <c r="Y8" s="36">
         <f t="shared" si="5"/>
         <v>8.0365838562924345</v>
       </c>
-      <c r="Y8" s="36">
+      <c r="Z8" s="36">
         <f t="shared" si="6"/>
         <v>0.61079960829635971</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="AA8" s="6">
         <f t="shared" si="7"/>
         <v>0.39603823695091539</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AB8" s="7">
+        <f>(U8-g)/((k+G8)-g)</f>
+        <v>0.93337322428384717</v>
+      </c>
+      <c r="AC8" s="7">
         <f t="shared" si="8"/>
-        <v>0.93337322428384717</v>
-      </c>
-      <c r="AB8" s="7">
+        <v>7.5011321861751838</v>
+      </c>
+      <c r="AD8" s="7">
         <f t="shared" si="9"/>
-        <v>7.5011321861751838</v>
-      </c>
-      <c r="AC8" s="7">
+        <v>3.8993840391989112</v>
+      </c>
+      <c r="AE8" s="7">
         <f t="shared" si="10"/>
-        <v>3.8993840391989112</v>
-      </c>
-      <c r="AD8" s="7">
+        <v>4.8417424890972054</v>
+      </c>
+      <c r="AF8" s="7">
         <f t="shared" si="11"/>
-        <v>4.8417424890972054</v>
-      </c>
-      <c r="AE8" s="7">
+        <v>5.9601231499834695</v>
+      </c>
+      <c r="AG8" s="7">
         <f t="shared" si="12"/>
-        <v>5.9601231499834695</v>
-      </c>
-      <c r="AF8" s="7">
+        <v>6.712372290957056</v>
+      </c>
+      <c r="AH8" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI8" s="12">
+        <v>6.88</v>
+      </c>
+      <c r="AJ8" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK8" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>6.712372290957056</v>
-      </c>
-      <c r="AG8" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH8" s="12">
-        <v>6.88</v>
-      </c>
-      <c r="AI8" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ8" s="7" t="str">
+        <v>CNYCNY</v>
+      </c>
+      <c r="AL8" s="7">
+        <f>IFERROR(VLOOKUP(AK8,Assumptions!B$12:C$13,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AM8" s="5">
         <f t="shared" si="14"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AK8" s="7">
-        <f>IFERROR(VLOOKUP(AJ8,Assumptions!B$12:C$13,2,FALSE),1)</f>
-        <v>1</v>
-      </c>
-      <c r="AL8" s="5">
+        <v>3.5159883720930235E-2</v>
+      </c>
+      <c r="AN8" s="7">
+        <f t="shared" si="17"/>
+        <v>4.3813303811223721</v>
+      </c>
+      <c r="AO8" s="7">
         <f t="shared" si="15"/>
-        <v>3.5159883720930235E-2</v>
-      </c>
-      <c r="AM8" s="7">
+        <v>5.4401601001092192</v>
+      </c>
+      <c r="AP8" s="7">
+        <f t="shared" si="15"/>
+        <v>6.6967675842510896</v>
+      </c>
+      <c r="AQ8" s="7">
+        <f t="shared" si="15"/>
+        <v>7.5419913381539958</v>
+      </c>
+      <c r="AR8" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="AS8" s="12">
+        <v>5.39</v>
+      </c>
+      <c r="AT8" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU8" s="34">
         <f t="shared" si="18"/>
-        <v>4.3813303811223721</v>
-      </c>
-      <c r="AN8" s="7">
-        <f t="shared" si="16"/>
-        <v>5.4401601001092192</v>
-      </c>
-      <c r="AO8" s="7">
-        <f t="shared" si="16"/>
-        <v>6.6967675842510896</v>
-      </c>
-      <c r="AP8" s="7">
-        <f t="shared" si="16"/>
-        <v>7.5419913381539958</v>
-      </c>
-      <c r="AQ8" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="AR8" s="12">
-        <v>5.39</v>
-      </c>
-      <c r="AS8" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AT8" s="34">
+        <v>-0.30274709302325575</v>
+      </c>
+      <c r="AV8" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>-0.30274709302325575</v>
-      </c>
-      <c r="AU8" s="7" t="str">
+        <v>HKDCNY</v>
+      </c>
+      <c r="AW8" s="7">
+        <f>IF($AR8="","na",IFERROR(VLOOKUP(AV8,Assumptions!B$12:C$13,2,FALSE),1))</f>
+        <v>0.89</v>
+      </c>
+      <c r="AX8" s="5">
         <f t="shared" si="20"/>
-        <v>HKDCNY</v>
-      </c>
-      <c r="AV8" s="7">
-        <f>IF($AQ8="","na",IFERROR(VLOOKUP(AU8,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>0.89</v>
-      </c>
-      <c r="AW8" s="5">
-        <f t="shared" si="21"/>
         <v>5.0426299222446902E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B9" s="48" t="s">
         <v>25</v>
       </c>
@@ -2446,169 +2482,172 @@
       <c r="F9" s="9">
         <v>45838</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="63">
+        <v>0</v>
+      </c>
+      <c r="H9" s="37">
         <v>322212411814</v>
       </c>
-      <c r="H9" s="37">
+      <c r="I9" s="37">
         <v>36790613</v>
       </c>
-      <c r="I9" s="37">
+      <c r="J9" s="37">
         <f>2987590-29158-2795-395040</f>
         <v>2560597</v>
       </c>
-      <c r="J9" s="42">
+      <c r="K9" s="42">
         <f>25638312/33664948</f>
         <v>0.76157289772139258</v>
       </c>
-      <c r="K9" s="47">
+      <c r="L9" s="47">
         <f>448934+76590</f>
         <v>525524</v>
       </c>
-      <c r="L9" s="47">
+      <c r="M9" s="47">
         <f>52049+41453</f>
         <v>93502</v>
       </c>
-      <c r="M9" s="37">
+      <c r="N9" s="37">
         <v>-337627</v>
       </c>
-      <c r="N9" s="43">
+      <c r="O9" s="43">
         <v>0.25</v>
       </c>
-      <c r="O9" s="37">
+      <c r="P9" s="37">
         <v>252719</v>
       </c>
-      <c r="P9" s="46">
-        <f t="shared" si="17"/>
+      <c r="Q9" s="46">
+        <f t="shared" si="16"/>
         <v>175986</v>
       </c>
-      <c r="Q9" s="38">
+      <c r="R9" s="38">
         <f>0.1216+0.1208</f>
         <v>0.2424</v>
       </c>
-      <c r="R9" s="11">
+      <c r="S9" s="11">
         <f>448934/21055282</f>
         <v>2.1321680707007393E-2</v>
       </c>
-      <c r="S9" s="34">
+      <c r="T9" s="34">
         <f t="shared" si="0"/>
         <v>0.64245781353468157</v>
       </c>
-      <c r="T9" s="34">
+      <c r="U9" s="34">
         <f t="shared" si="1"/>
         <v>6.8728503548195985E-2</v>
       </c>
-      <c r="U9" s="35">
+      <c r="V9" s="35">
         <f t="shared" si="2"/>
         <v>1.4284187110445809E-2</v>
       </c>
-      <c r="V9" s="36">
+      <c r="W9" s="36">
         <f t="shared" si="3"/>
         <v>14.367982544695632</v>
       </c>
-      <c r="W9" s="34">
+      <c r="X9" s="34">
         <f t="shared" si="4"/>
         <v>0.33487718924349791</v>
       </c>
-      <c r="X9" s="36">
+      <c r="Y9" s="36">
         <f t="shared" si="5"/>
         <v>7.9469222975747051</v>
       </c>
-      <c r="Y9" s="36">
+      <c r="Z9" s="36">
         <f t="shared" si="6"/>
         <v>0.54618007732610097</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="AA9" s="6">
         <f t="shared" si="7"/>
         <v>0.44380967022214041</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AB9" s="7">
+        <f>(U9-g)/((k+G9)-g)</f>
+        <v>0.81214172580326638</v>
+      </c>
+      <c r="AC9" s="7">
         <f t="shared" si="8"/>
-        <v>0.81214172580326638</v>
-      </c>
-      <c r="AB9" s="7">
+        <v>6.45402718957678</v>
+      </c>
+      <c r="AD9" s="7">
         <f t="shared" si="9"/>
-        <v>6.45402718957678</v>
-      </c>
-      <c r="AC9" s="7">
+        <v>3.4177621001950751</v>
+      </c>
+      <c r="AE9" s="7">
         <f t="shared" si="10"/>
-        <v>3.4177621001950751</v>
-      </c>
-      <c r="AD9" s="7">
+        <v>4.2379685002558771</v>
+      </c>
+      <c r="AF9" s="7">
         <f t="shared" si="11"/>
-        <v>4.2379685002558771</v>
-      </c>
-      <c r="AE9" s="7">
+        <v>5.2108060626568031</v>
+      </c>
+      <c r="AG9" s="7">
         <f t="shared" si="12"/>
-        <v>5.2108060626568031</v>
-      </c>
-      <c r="AF9" s="7">
+        <v>5.864892240591038</v>
+      </c>
+      <c r="AH9" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI9" s="12">
+        <v>5.34</v>
+      </c>
+      <c r="AJ9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>5.864892240591038</v>
-      </c>
-      <c r="AG9" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="AH9" s="12">
-        <v>5.34</v>
-      </c>
-      <c r="AI9" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="7" t="str">
+        <v>CNYCNY</v>
+      </c>
+      <c r="AL9" s="7">
+        <f>IFERROR(VLOOKUP(AK9,Assumptions!B$12:C$13,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AM9" s="5">
         <f t="shared" si="14"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AK9" s="7">
-        <f>IFERROR(VLOOKUP(AJ9,Assumptions!B$12:C$13,2,FALSE),1)</f>
-        <v>1</v>
-      </c>
-      <c r="AL9" s="5">
+        <v>4.5393258426966294E-2</v>
+      </c>
+      <c r="AN9" s="7">
+        <f t="shared" si="17"/>
+        <v>3.8401821350506462</v>
+      </c>
+      <c r="AO9" s="7">
         <f t="shared" si="15"/>
-        <v>4.5393258426966294E-2</v>
-      </c>
-      <c r="AM9" s="7">
+        <v>4.7617623598380643</v>
+      </c>
+      <c r="AP9" s="7">
+        <f t="shared" si="15"/>
+        <v>5.8548382726480934</v>
+      </c>
+      <c r="AQ9" s="7">
+        <f t="shared" si="15"/>
+        <v>6.5897665624618407</v>
+      </c>
+      <c r="AR9" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS9" s="12">
+        <v>4.47</v>
+      </c>
+      <c r="AT9" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU9" s="34">
         <f t="shared" si="18"/>
-        <v>3.8401821350506462</v>
-      </c>
-      <c r="AN9" s="7">
-        <f t="shared" si="16"/>
-        <v>4.7617623598380643</v>
-      </c>
-      <c r="AO9" s="7">
-        <f t="shared" si="16"/>
-        <v>5.8548382726480934</v>
-      </c>
-      <c r="AP9" s="7">
-        <f t="shared" si="16"/>
-        <v>6.5897665624618407</v>
-      </c>
-      <c r="AQ9" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR9" s="12">
-        <v>4.47</v>
-      </c>
-      <c r="AS9" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AT9" s="34">
+        <v>-0.255</v>
+      </c>
+      <c r="AV9" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>-0.255</v>
-      </c>
-      <c r="AU9" s="7" t="str">
+        <v>HKDCNY</v>
+      </c>
+      <c r="AW9" s="7">
+        <f>IF($AR9="","na",IFERROR(VLOOKUP(AV9,Assumptions!B$12:C$13,2,FALSE),1))</f>
+        <v>0.89</v>
+      </c>
+      <c r="AX9" s="5">
         <f t="shared" si="20"/>
-        <v>HKDCNY</v>
-      </c>
-      <c r="AV9" s="7">
-        <f>IF($AQ9="","na",IFERROR(VLOOKUP(AU9,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>0.89</v>
-      </c>
-      <c r="AW9" s="5">
-        <f t="shared" si="21"/>
         <v>6.0930548224115838E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B10" s="48" t="s">
         <v>26</v>
       </c>
@@ -2624,162 +2663,165 @@
       <c r="F10" s="9">
         <v>45838</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="63">
+        <v>0</v>
+      </c>
+      <c r="H10" s="37">
         <v>21162855196</v>
       </c>
-      <c r="H10" s="37">
+      <c r="I10" s="37">
         <v>10614376</v>
       </c>
-      <c r="I10" s="37">
+      <c r="J10" s="37">
         <f>881747-1054-532-78891</f>
         <v>801270</v>
       </c>
-      <c r="J10" s="42">
+      <c r="K10" s="42">
         <f>5964497/9720864</f>
         <v>0.6135768384374064</v>
       </c>
-      <c r="K10" s="47">
+      <c r="L10" s="47">
         <f>148107+24096+661</f>
         <v>172864</v>
       </c>
-      <c r="L10" s="47">
+      <c r="M10" s="47">
         <f>503+36202</f>
         <v>36705</v>
       </c>
-      <c r="M10" s="37">
+      <c r="N10" s="37">
         <v>-125029</v>
       </c>
-      <c r="N10" s="43">
+      <c r="O10" s="43">
         <v>0.25</v>
       </c>
-      <c r="O10" s="37">
+      <c r="P10" s="37">
         <v>77205</v>
       </c>
-      <c r="P10" s="46">
-        <f t="shared" si="17"/>
+      <c r="Q10" s="46">
+        <f t="shared" si="16"/>
         <v>49640.625</v>
       </c>
-      <c r="Q10" s="38">
+      <c r="R10" s="38">
         <v>1.06</v>
       </c>
-      <c r="R10" s="11">
+      <c r="S10" s="11">
         <f>148107/5608859</f>
         <v>2.6405905372197804E-2</v>
       </c>
-      <c r="S10" s="34">
+      <c r="T10" s="34">
         <f t="shared" si="0"/>
         <v>0.72327957238059981</v>
       </c>
-      <c r="T10" s="34">
+      <c r="U10" s="34">
         <f t="shared" si="1"/>
         <v>6.195243176457374E-2</v>
       </c>
-      <c r="U10" s="35">
+      <c r="V10" s="35">
         <f t="shared" si="2"/>
         <v>1.6285837245637425E-2</v>
       </c>
-      <c r="V10" s="36">
+      <c r="W10" s="36">
         <f t="shared" si="3"/>
         <v>13.246940481984849</v>
       </c>
-      <c r="W10" s="34">
+      <c r="X10" s="34">
         <f t="shared" si="4"/>
         <v>0.28716577772121438</v>
       </c>
-      <c r="X10" s="36">
+      <c r="Y10" s="36">
         <f t="shared" si="5"/>
         <v>37.862093398033004</v>
       </c>
-      <c r="Y10" s="36">
+      <c r="Z10" s="36">
         <f t="shared" si="6"/>
         <v>2.3456487577055571</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="AA10" s="6">
         <f t="shared" si="7"/>
         <v>0.45190056546951218</v>
       </c>
-      <c r="AA10" s="7">
+      <c r="AB10" s="7">
+        <f>(U10-g)/((k+G10)-g)</f>
+        <v>0.69920719607622894</v>
+      </c>
+      <c r="AC10" s="7">
         <f t="shared" si="8"/>
-        <v>0.69920719607622894</v>
-      </c>
-      <c r="AB10" s="7">
+        <v>26.473448162414957</v>
+      </c>
+      <c r="AD10" s="7">
         <f t="shared" si="9"/>
-        <v>26.473448162414957</v>
-      </c>
-      <c r="AC10" s="7">
+        <v>14.139388367642148</v>
+      </c>
+      <c r="AE10" s="7">
         <f t="shared" si="10"/>
-        <v>14.139388367642148</v>
-      </c>
-      <c r="AD10" s="7">
+        <v>17.521766588388239</v>
+      </c>
+      <c r="AF10" s="7">
         <f t="shared" si="11"/>
-        <v>17.521766588388239</v>
-      </c>
-      <c r="AE10" s="7">
+        <v>21.532478422844516</v>
+      </c>
+      <c r="AG10" s="7">
         <f t="shared" si="12"/>
-        <v>21.532478422844516</v>
-      </c>
-      <c r="AF10" s="7">
+        <v>24.228568841811072</v>
+      </c>
+      <c r="AH10" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI10" s="12">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="AJ10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>24.228568841811072</v>
-      </c>
-      <c r="AG10" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="AH10" s="12">
-        <v>18.989999999999998</v>
-      </c>
-      <c r="AI10" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ10" s="7" t="str">
+        <v>CNYCNY</v>
+      </c>
+      <c r="AL10" s="7">
+        <f>IFERROR(VLOOKUP(AK10,Assumptions!B$12:C$13,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AM10" s="5">
         <f t="shared" si="14"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AK10" s="7">
-        <f>IFERROR(VLOOKUP(AJ10,Assumptions!B$12:C$13,2,FALSE),1)</f>
-        <v>1</v>
-      </c>
-      <c r="AL10" s="5">
+        <v>5.5818852027382841E-2</v>
+      </c>
+      <c r="AN10" s="7" t="str">
+        <f t="shared" si="17"/>
+        <v>na</v>
+      </c>
+      <c r="AO10" s="7" t="str">
         <f t="shared" si="15"/>
-        <v>5.5818852027382841E-2</v>
-      </c>
-      <c r="AM10" s="7" t="str">
+        <v>na</v>
+      </c>
+      <c r="AP10" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>na</v>
+      </c>
+      <c r="AQ10" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>na</v>
+      </c>
+      <c r="AR10" s="49"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="34" t="str">
         <f t="shared" si="18"/>
         <v>na</v>
       </c>
-      <c r="AN10" s="7" t="str">
-        <f t="shared" si="16"/>
-        <v>na</v>
-      </c>
-      <c r="AO10" s="7" t="str">
-        <f t="shared" si="16"/>
-        <v>na</v>
-      </c>
-      <c r="AP10" s="7" t="str">
-        <f t="shared" si="16"/>
-        <v>na</v>
-      </c>
-      <c r="AQ10" s="49"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="34" t="str">
+      <c r="AV10" s="7" t="str">
         <f t="shared" si="19"/>
         <v>na</v>
       </c>
-      <c r="AU10" s="7" t="str">
+      <c r="AW10" s="7" t="str">
+        <f>IF($AR10="","na",IFERROR(VLOOKUP(AV10,Assumptions!B$12:C$13,2,FALSE),1))</f>
+        <v>na</v>
+      </c>
+      <c r="AX10" s="5" t="str">
         <f t="shared" si="20"/>
         <v>na</v>
       </c>
-      <c r="AV10" s="7" t="str">
-        <f>IF($AQ10="","na",IFERROR(VLOOKUP(AU10,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>na</v>
-      </c>
-      <c r="AW10" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v>na</v>
-      </c>
-    </row>
-    <row r="11" spans="2:49" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B11" s="48" t="s">
         <v>27</v>
       </c>
@@ -2795,169 +2837,172 @@
       <c r="F11" s="9">
         <v>45838</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="63">
+        <v>0</v>
+      </c>
+      <c r="H11" s="37">
         <v>120095053492</v>
       </c>
-      <c r="H11" s="37">
+      <c r="I11" s="37">
         <v>18190521</v>
       </c>
-      <c r="I11" s="37">
+      <c r="J11" s="37">
         <f>1138639-7832</f>
         <v>1130807</v>
       </c>
-      <c r="J11" s="42">
+      <c r="K11" s="42">
         <f>16108809/17049715</f>
         <v>0.94481397489635455</v>
       </c>
-      <c r="K11" s="47">
+      <c r="L11" s="47">
         <f>286123+25282</f>
         <v>311405</v>
       </c>
-      <c r="L11" s="47">
+      <c r="M11" s="47">
         <f>917+31715</f>
         <v>32632</v>
       </c>
-      <c r="M11" s="37">
+      <c r="N11" s="37">
         <v>-255176</v>
       </c>
-      <c r="N11" s="43">
+      <c r="O11" s="43">
         <v>0.25</v>
       </c>
-      <c r="O11" s="37">
+      <c r="P11" s="37">
         <v>86479</v>
       </c>
-      <c r="P11" s="46">
-        <f t="shared" si="17"/>
+      <c r="Q11" s="46">
+        <f t="shared" si="16"/>
         <v>54408.75</v>
       </c>
-      <c r="Q11" s="38">
+      <c r="R11" s="38">
         <f>0.1139 +0.1477</f>
         <v>0.2616</v>
       </c>
-      <c r="R11" s="11">
+      <c r="S11" s="11">
         <f>286123/8684144</f>
         <v>3.2947749369425475E-2</v>
       </c>
-      <c r="S11" s="34">
+      <c r="T11" s="34">
         <f t="shared" si="0"/>
         <v>0.81943449848268335</v>
       </c>
-      <c r="T11" s="34">
+      <c r="U11" s="34">
         <f t="shared" si="1"/>
         <v>4.8114974527041304E-2</v>
       </c>
-      <c r="U11" s="35">
+      <c r="V11" s="35">
         <f t="shared" si="2"/>
         <v>1.7119080866347919E-2</v>
       </c>
-      <c r="V11" s="36">
+      <c r="W11" s="36">
         <f t="shared" si="3"/>
         <v>16.086318001215062</v>
       </c>
-      <c r="W11" s="34">
+      <c r="X11" s="34">
         <f t="shared" si="4"/>
         <v>0.17472021964965237</v>
       </c>
-      <c r="X11" s="36">
+      <c r="Y11" s="36">
         <f t="shared" si="5"/>
         <v>9.4159331889162896</v>
       </c>
-      <c r="Y11" s="36">
+      <c r="Z11" s="36">
         <f t="shared" si="6"/>
         <v>0.45304738553303009</v>
       </c>
-      <c r="Z11" s="6">
+      <c r="AA11" s="6">
         <f t="shared" si="7"/>
         <v>0.57742304304927428</v>
       </c>
-      <c r="AA11" s="7">
+      <c r="AB11" s="7">
+        <f>(U11-g)/((k+G11)-g)</f>
+        <v>0.46858290878402176</v>
+      </c>
+      <c r="AC11" s="7">
         <f t="shared" si="8"/>
-        <v>0.46858290878402176</v>
-      </c>
-      <c r="AB11" s="7">
+        <v>4.4121453625784044</v>
+      </c>
+      <c r="AD11" s="7">
         <f t="shared" si="9"/>
-        <v>4.4121453625784044</v>
-      </c>
-      <c r="AC11" s="7">
+        <v>2.5119358831760321</v>
+      </c>
+      <c r="AE11" s="7">
         <f t="shared" si="10"/>
-        <v>2.5119358831760321</v>
-      </c>
-      <c r="AD11" s="7">
+        <v>3.0989390499793994</v>
+      </c>
+      <c r="AF11" s="7">
         <f t="shared" si="11"/>
-        <v>3.0989390499793994</v>
-      </c>
-      <c r="AE11" s="7">
+        <v>3.7935880218656868</v>
+      </c>
+      <c r="AG11" s="7">
         <f t="shared" si="12"/>
-        <v>3.7935880218656868</v>
-      </c>
-      <c r="AF11" s="7">
+        <v>4.259894726825121</v>
+      </c>
+      <c r="AH11" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI11" s="12">
+        <v>5.17</v>
+      </c>
+      <c r="AJ11" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK11" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>4.259894726825121</v>
-      </c>
-      <c r="AG11" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH11" s="12">
-        <v>5.17</v>
-      </c>
-      <c r="AI11" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ11" s="7" t="str">
+        <v>CNYCNY</v>
+      </c>
+      <c r="AL11" s="7">
+        <f>IFERROR(VLOOKUP(AK11,Assumptions!B$12:C$13,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AM11" s="5">
         <f t="shared" si="14"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AK11" s="7">
-        <f>IFERROR(VLOOKUP(AJ11,Assumptions!B$12:C$13,2,FALSE),1)</f>
-        <v>1</v>
-      </c>
-      <c r="AL11" s="5">
+        <v>5.0599613152804646E-2</v>
+      </c>
+      <c r="AN11" s="7">
+        <f t="shared" si="17"/>
+        <v>2.8223998687371146</v>
+      </c>
+      <c r="AO11" s="7">
         <f t="shared" si="15"/>
-        <v>5.0599613152804646E-2</v>
-      </c>
-      <c r="AM11" s="7">
+        <v>3.4819539887408983</v>
+      </c>
+      <c r="AP11" s="7">
+        <f t="shared" si="15"/>
+        <v>4.2624584515344797</v>
+      </c>
+      <c r="AQ11" s="7">
+        <f t="shared" si="15"/>
+        <v>4.7863985694664279</v>
+      </c>
+      <c r="AR11" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS11" s="12">
+        <v>5</v>
+      </c>
+      <c r="AT11" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU11" s="34">
         <f t="shared" si="18"/>
-        <v>2.8223998687371146</v>
-      </c>
-      <c r="AN11" s="7">
-        <f t="shared" si="16"/>
-        <v>3.4819539887408983</v>
-      </c>
-      <c r="AO11" s="7">
-        <f t="shared" si="16"/>
-        <v>4.2624584515344797</v>
-      </c>
-      <c r="AP11" s="7">
-        <f t="shared" si="16"/>
-        <v>4.7863985694664279</v>
-      </c>
-      <c r="AQ11" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="AR11" s="12">
-        <v>5</v>
-      </c>
-      <c r="AS11" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AT11" s="34">
+        <v>-0.13926499032882012</v>
+      </c>
+      <c r="AV11" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>-0.13926499032882012</v>
-      </c>
-      <c r="AU11" s="7" t="str">
+        <v>HKDCNY</v>
+      </c>
+      <c r="AW11" s="7">
+        <f>IF($AR11="","na",IFERROR(VLOOKUP(AV11,Assumptions!B$12:C$13,2,FALSE),1))</f>
+        <v>0.89</v>
+      </c>
+      <c r="AX11" s="5">
         <f t="shared" si="20"/>
-        <v>HKDCNY</v>
-      </c>
-      <c r="AV11" s="7">
-        <f>IF($AQ11="","na",IFERROR(VLOOKUP(AU11,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>0.89</v>
-      </c>
-      <c r="AW11" s="5">
-        <f t="shared" si="21"/>
         <v>5.8786516853932581E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:49" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B12" s="48" t="s">
         <v>115</v>
       </c>
@@ -2973,180 +3018,183 @@
       <c r="F12" s="9">
         <v>45838</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="63">
+        <v>0</v>
+      </c>
+      <c r="H12" s="37">
         <v>25219845601</v>
       </c>
-      <c r="H12" s="37">
+      <c r="I12" s="37">
         <v>12657151</v>
       </c>
-      <c r="I12" s="37">
+      <c r="J12" s="37">
         <f>1289233-6153-9954-47907</f>
         <v>1225219</v>
       </c>
-      <c r="J12" s="42">
+      <c r="K12" s="42">
         <f>9509526/11360291</f>
         <v>0.83708471904460902</v>
       </c>
-      <c r="K12" s="47">
+      <c r="L12" s="47">
         <f>211277+72094</f>
         <v>283371</v>
       </c>
-      <c r="L12" s="47">
+      <c r="M12" s="47">
         <f>14126+29880</f>
         <v>44006</v>
       </c>
-      <c r="M12" s="37">
+      <c r="N12" s="37">
         <v>-158469</v>
       </c>
-      <c r="N12" s="43">
+      <c r="O12" s="43">
         <v>0.25</v>
       </c>
-      <c r="O12" s="37">
+      <c r="P12" s="37">
         <v>149559</v>
       </c>
-      <c r="P12" s="46">
-        <f t="shared" si="17"/>
+      <c r="Q12" s="46">
+        <f t="shared" si="16"/>
         <v>110178.75</v>
       </c>
-      <c r="Q12" s="38">
+      <c r="R12" s="38">
         <v>2</v>
       </c>
-      <c r="R12" s="11">
+      <c r="S12" s="11">
         <f>211277/6300684</f>
         <v>3.3532391086428075E-2</v>
       </c>
-      <c r="S12" s="34">
-        <f>-M12/K12</f>
+      <c r="T12" s="34">
+        <f>-N12/L12</f>
         <v>0.55922800851180965</v>
       </c>
-      <c r="T12" s="34">
+      <c r="U12" s="34">
         <f t="shared" si="1"/>
         <v>8.9925760211031658E-2</v>
       </c>
-      <c r="U12" s="35">
+      <c r="V12" s="35">
         <f t="shared" si="2"/>
         <v>2.2388213587718121E-2</v>
       </c>
-      <c r="V12" s="36">
+      <c r="W12" s="36">
         <f t="shared" si="3"/>
         <v>10.33052131904582</v>
       </c>
-      <c r="W12" s="34">
-        <f t="shared" ref="W12" si="22">P12/K12</f>
+      <c r="X12" s="34">
+        <f t="shared" ref="X12" si="21">Q12/L12</f>
         <v>0.38881448701525562</v>
       </c>
-      <c r="X12" s="36">
+      <c r="Y12" s="36">
         <f t="shared" si="5"/>
         <v>48.581542463979972</v>
       </c>
-      <c r="Y12" s="36">
+      <c r="Z12" s="36">
         <f t="shared" si="6"/>
         <v>4.368732138297915</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="AA12" s="6">
         <f t="shared" si="7"/>
         <v>0.45779872436381791</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AB12" s="7">
+        <f>(U12-g)/((k+G12)-g)</f>
+        <v>1.1654293368505275</v>
+      </c>
+      <c r="AC12" s="7">
         <f t="shared" si="8"/>
-        <v>1.1654293368505275</v>
-      </c>
-      <c r="AB12" s="7">
+        <v>56.618354816971923</v>
+      </c>
+      <c r="AD12" s="7">
         <f t="shared" si="9"/>
-        <v>56.618354816971923</v>
-      </c>
-      <c r="AC12" s="7">
+        <v>29.75111090197689</v>
+      </c>
+      <c r="AE12" s="7">
         <f t="shared" si="10"/>
-        <v>29.75111090197689</v>
-      </c>
-      <c r="AD12" s="7">
+        <v>36.911750749106794</v>
+      </c>
+      <c r="AF12" s="7">
         <f t="shared" si="11"/>
-        <v>36.911750749106794</v>
-      </c>
-      <c r="AE12" s="7">
+        <v>45.407000502341631</v>
+      </c>
+      <c r="AG12" s="7">
         <f t="shared" si="12"/>
-        <v>45.407000502341631</v>
-      </c>
-      <c r="AF12" s="7">
+        <v>51.11974717559962</v>
+      </c>
+      <c r="AH12" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI12" s="12">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AJ12" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK12" s="7" t="str">
         <f t="shared" si="13"/>
-        <v>51.11974717559962</v>
-      </c>
-      <c r="AG12" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="AH12" s="12">
-        <v>38.049999999999997</v>
-      </c>
-      <c r="AI12" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ12" s="7" t="str">
+        <v>CNYCNY</v>
+      </c>
+      <c r="AL12" s="7">
+        <f>IFERROR(VLOOKUP(AK12,Assumptions!B$12:C$13,2,FALSE),1)</f>
+        <v>1</v>
+      </c>
+      <c r="AM12" s="5">
         <f t="shared" si="14"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AK12" s="7">
-        <f>IFERROR(VLOOKUP(AJ12,Assumptions!B$12:C$13,2,FALSE),1)</f>
-        <v>1</v>
-      </c>
-      <c r="AL12" s="5">
+        <v>5.2562417871222081E-2</v>
+      </c>
+      <c r="AN12" s="7">
+        <f t="shared" si="17"/>
+        <v>33.428214496603246</v>
+      </c>
+      <c r="AO12" s="7">
         <f t="shared" si="15"/>
-        <v>5.2562417871222081E-2</v>
-      </c>
-      <c r="AM12" s="7">
+        <v>41.473877246187406</v>
+      </c>
+      <c r="AP12" s="7">
+        <f t="shared" si="15"/>
+        <v>51.019101688024307</v>
+      </c>
+      <c r="AQ12" s="7">
+        <f t="shared" si="15"/>
+        <v>57.437918174831033</v>
+      </c>
+      <c r="AR12" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="AS12" s="12">
+        <v>46.48</v>
+      </c>
+      <c r="AT12" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU12" s="34">
         <f t="shared" si="18"/>
-        <v>33.428214496603246</v>
-      </c>
-      <c r="AN12" s="7">
-        <f t="shared" si="16"/>
-        <v>41.473877246187406</v>
-      </c>
-      <c r="AO12" s="7">
-        <f t="shared" si="16"/>
-        <v>51.019101688024307</v>
-      </c>
-      <c r="AP12" s="7">
-        <f t="shared" si="16"/>
-        <v>57.437918174831033</v>
-      </c>
-      <c r="AQ12" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="AR12" s="12">
-        <v>46.48</v>
-      </c>
-      <c r="AS12" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AT12" s="34">
+        <v>8.7180026281209022E-2</v>
+      </c>
+      <c r="AV12" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>8.7180026281209022E-2</v>
-      </c>
-      <c r="AU12" s="7" t="str">
+        <v>HKDCNY</v>
+      </c>
+      <c r="AW12" s="7">
+        <f>IF($AR12="","na",IFERROR(VLOOKUP(AV12,Assumptions!B$12:C$13,2,FALSE),1))</f>
+        <v>0.89</v>
+      </c>
+      <c r="AX12" s="5">
         <f t="shared" si="20"/>
-        <v>HKDCNY</v>
-      </c>
-      <c r="AV12" s="7">
-        <f>IF($AQ12="","na",IFERROR(VLOOKUP(AU12,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>0.89</v>
-      </c>
-      <c r="AW12" s="5">
-        <f t="shared" si="21"/>
         <v>4.8347483030033465E-2</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="8">
-    <mergeCell ref="AQ3:AW3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AG3:AL3"/>
+    <mergeCell ref="AR3:AX3"/>
+    <mergeCell ref="Y3:AA3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="AH3:AM3"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="L3:R3"/>
+    <mergeCell ref="S3:X3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="26" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="17" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87292F5E-6821-4649-B69E-6070DE8569DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE3FB05-4D0E-4865-AEFF-96D97FE9D424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="164">
   <si>
     <t>Name</t>
   </si>
@@ -248,9 +248,6 @@
   <si>
     <t>End Date of Last Statement
 (YYYY/MM/DD)</t>
-  </si>
-  <si>
-    <t>12/31</t>
   </si>
   <si>
     <t>Fair Price 
@@ -742,7 +739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -761,9 +758,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -873,6 +867,9 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -911,9 +908,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1265,18 +1259,18 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="13">
+        <v>83</v>
+      </c>
+      <c r="C3" s="12">
         <v>0.08</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="13">
+        <v>73</v>
+      </c>
+      <c r="C4" s="12">
         <v>0.02</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1285,52 +1279,52 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="14">
+        <v>74</v>
+      </c>
+      <c r="C5" s="13">
         <v>3</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="13">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12">
         <v>0.29465259038036606</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="13">
+        <v>76</v>
+      </c>
+      <c r="C7" s="12">
         <v>0.20075184365903009</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="13">
+        <v>77</v>
+      </c>
+      <c r="C8" s="12">
         <v>0.1174</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="13">
+        <v>82</v>
+      </c>
+      <c r="C9" s="12">
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>2</v>
@@ -1341,38 +1335,38 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="40">
+        <v>108</v>
+      </c>
+      <c r="C12" s="39">
         <v>7.8</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="40">
+        <v>109</v>
+      </c>
+      <c r="C13" s="39">
         <v>0.89</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="41">
+        <v>117</v>
+      </c>
+      <c r="C14" s="40">
         <v>1000000</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
-      <c r="C15" s="39"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="1"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1393,11 +1387,11 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1451,7 +1445,7 @@
   <sheetData>
     <row r="2" spans="2:50" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -1467,32 +1461,32 @@
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>20</v>
@@ -1504,7 +1498,7 @@
         <v>17</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>45</v>
@@ -1524,10 +1518,10 @@
       <c r="AC2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -1553,7 +1547,7 @@
       <c r="C3" s="54"/>
       <c r="D3" s="55"/>
       <c r="E3" s="56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
@@ -1562,7 +1556,7 @@
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
       <c r="L3" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M3" s="59"/>
       <c r="N3" s="59"/>
@@ -1571,7 +1565,7 @@
       <c r="Q3" s="59"/>
       <c r="R3" s="59"/>
       <c r="S3" s="60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T3" s="61"/>
       <c r="U3" s="61"/>
@@ -1579,7 +1573,7 @@
       <c r="W3" s="61"/>
       <c r="X3" s="62"/>
       <c r="Y3" s="51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z3" s="51"/>
       <c r="AA3" s="51"/>
@@ -1587,40 +1581,40 @@
         <v>62</v>
       </c>
       <c r="AC3" s="52"/>
-      <c r="AD3" s="27" t="s">
+      <c r="AD3" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE3" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AF3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="AF3" s="27" t="s">
+      <c r="AG3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="27" t="s">
-        <v>82</v>
-      </c>
       <c r="AH3" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AI3" s="50"/>
       <c r="AJ3" s="50"/>
       <c r="AK3" s="50"/>
       <c r="AL3" s="50"/>
       <c r="AM3" s="50"/>
-      <c r="AN3" s="27" t="s">
+      <c r="AN3" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO3" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AP3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="AP3" s="27" t="s">
+      <c r="AQ3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AQ3" s="27" t="s">
-        <v>82</v>
-      </c>
       <c r="AR3" s="50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AS3" s="50"/>
       <c r="AT3" s="50"/>
@@ -1630,386 +1624,386 @@
       <c r="AX3" s="50"/>
     </row>
     <row r="4" spans="2:50" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="32" t="s">
+      <c r="B4" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="L4" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="M4" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="N4" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="O4" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="P4" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="R4" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="W4" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA4" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB4" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI4" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK4" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="AM4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR4" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AS4" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="AV4" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AW4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="AX4" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="2:50" x14ac:dyDescent="0.45">
+      <c r="B5" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="H4" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="L4" s="44" t="s">
+      <c r="H5" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="M5" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="M4" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="N4" s="44" t="s">
+      <c r="O5" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="O4" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="P4" s="44" t="s">
+      <c r="P5" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="Q4" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="R4" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="28" t="s">
+      <c r="Q5" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="R5" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="T5" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="U4" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="V4" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="W4" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="X4" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA4" s="24" t="s">
+      <c r="U5" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W5" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="X5" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z5" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA5" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="AB4" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC4" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD4" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE4" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH4" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="AI4" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ4" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK4" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="AL4" s="20" t="s">
+      <c r="AB5" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="AM4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN4" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO4" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR4" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="AS4" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT4" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="AU4" s="20" t="s">
+      <c r="AC5" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD5" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE5" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH5" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI5" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ5" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN5" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO5" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR5" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="AS5" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT5" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU5" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="AV4" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="AW4" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="AX4" s="20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B5" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="K5" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="L5" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="M5" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="N5" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="O5" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="P5" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q5" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="R5" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="T5" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="V5" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="W5" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="X5" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y5" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z5" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA5" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB5" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC5" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD5" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE5" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF5" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG5" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI5" s="21" t="s">
+      <c r="AV5" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="AJ5" s="21" t="s">
+      <c r="AW5" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="21"/>
-      <c r="AL5" s="21"/>
-      <c r="AM5" s="21" t="s">
+      <c r="AX5" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="AN5" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO5" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP5" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ5" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR5" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="AS5" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT5" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="AU5" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="AV5" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="AW5" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX5" s="21" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="6" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="E6" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F6" s="8">
         <v>45838</v>
       </c>
-      <c r="G6" s="63">
+      <c r="G6" s="49">
         <v>0</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="36">
         <v>356406257089</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="36">
         <v>52317931</v>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="36">
         <f>4114692-23118-19420-59031</f>
         <v>4013123</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="41">
         <f>36904556/48179055</f>
         <v>0.76598754375734435</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="46">
         <f>637405+109397</f>
         <v>746802</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="46">
         <f>28762+40930</f>
         <v>69692</v>
       </c>
-      <c r="N6" s="37">
+      <c r="N6" s="36">
         <v>-400918</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="42">
         <v>0.25</v>
       </c>
-      <c r="P6" s="37">
+      <c r="P6" s="36">
         <v>366946</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="45">
         <f>(L6+M6/2+N6)*(1-O6)</f>
         <v>285547.5</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="37">
         <f>0.1646+0.1434</f>
         <v>0.308</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6" s="10">
         <f>637405/27613781</f>
         <v>2.3082858519085089E-2</v>
       </c>
-      <c r="T6" s="34">
+      <c r="T6" s="33">
         <f t="shared" ref="T6:T11" si="0">-N6/L6</f>
         <v>0.53684644658155711</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="33">
         <f t="shared" ref="U6:U12" si="1">Q6/J6</f>
         <v>7.115343835710991E-2</v>
       </c>
-      <c r="V6" s="35">
+      <c r="V6" s="34">
         <f t="shared" ref="V6:V12" si="2">L6/I6</f>
         <v>1.4274303010950491E-2</v>
       </c>
-      <c r="W6" s="36">
+      <c r="W6" s="35">
         <f t="shared" ref="W6:W12" si="3">I6/J6</f>
         <v>13.036712555284252</v>
       </c>
-      <c r="X6" s="34">
+      <c r="X6" s="33">
         <f t="shared" ref="X6:X11" si="4">Q6/L6</f>
         <v>0.38236038468027672</v>
       </c>
-      <c r="Y6" s="36">
+      <c r="Y6" s="35">
         <f t="shared" ref="Y6:Y12" si="5">J6/(H6/1000000)*$AL6</f>
         <v>11.259967860210329</v>
       </c>
-      <c r="Z6" s="36">
+      <c r="Z6" s="35">
         <f t="shared" ref="Z6:Z12" si="6">Q6/(H6/1000000)*$AL6</f>
         <v>0.8011854290445144</v>
       </c>
@@ -2018,40 +2012,40 @@
         <v>0.38443035636246864</v>
       </c>
       <c r="AB6" s="7">
-        <f>(U6-g)/((k+G6)-g)</f>
+        <f t="shared" ref="AB6:AB12" si="8">(U6-g)/((k+G6)-g)</f>
         <v>0.85255730595183177</v>
       </c>
       <c r="AC6" s="7">
-        <f t="shared" ref="AC6:AC12" si="8">Y6*AB6</f>
+        <f t="shared" ref="AC6:AC12" si="9">Y6*AB6</f>
         <v>9.5997678640051305</v>
       </c>
       <c r="AD6" s="7">
-        <f t="shared" ref="AD6:AD12" si="9">PV(Target_return,Holding_Period,-R6,-AC6)</f>
+        <f t="shared" ref="AD6:AD12" si="10">PV(Target_return,Holding_Period,-R6,-AC6)</f>
         <v>4.9874504439696281</v>
       </c>
       <c r="AE6" s="7">
-        <f t="shared" ref="AE6:AE12" si="10">PV(Entry_yield,Holding_Period,-R6,-AC6)</f>
+        <f t="shared" ref="AE6:AE12" si="11">PV(Entry_yield,Holding_Period,-R6,-AC6)</f>
         <v>6.1930254837762826</v>
       </c>
       <c r="AF6" s="7">
-        <f t="shared" ref="AF6:AF12" si="11">PV(Benchmark_yield,Holding_Period,-R6,-AC6)</f>
+        <f t="shared" ref="AF6:AF12" si="12">PV(Benchmark_yield,Holding_Period,-R6,-AC6)</f>
         <v>7.623815149844293</v>
       </c>
       <c r="AG6" s="7">
-        <f t="shared" ref="AG6:AG12" si="12">PV(Base_Cost_of_Equity,Holding_Period,-R6,-AC6)</f>
+        <f t="shared" ref="AG6:AG12" si="13">PV(Base_Cost_of_Equity,Holding_Period,-R6,-AC6)</f>
         <v>8.5862102417703685</v>
       </c>
-      <c r="AH6" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI6" s="12">
+      <c r="AH6" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI6" s="11">
         <v>7.26</v>
       </c>
-      <c r="AJ6" s="12" t="s">
+      <c r="AJ6" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK6" s="7" t="str">
-        <f t="shared" ref="AK6:AK12" si="13">AJ6&amp;D6</f>
+        <f t="shared" ref="AK6:AK12" si="14">AJ6&amp;D6</f>
         <v>CNYCNY</v>
       </c>
       <c r="AL6" s="7">
@@ -2059,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="AM6" s="5">
-        <f t="shared" ref="AM6:AM12" si="14">R6/AI6</f>
+        <f t="shared" ref="AM6:AM12" si="15">R6/AI6</f>
         <v>4.2424242424242427E-2</v>
       </c>
       <c r="AN6" s="7">
@@ -2067,27 +2061,27 @@
         <v>5.6038769033366611</v>
       </c>
       <c r="AO6" s="7">
-        <f t="shared" ref="AO6:AQ12" si="15">IF($AR6="","na",AE6/$AW6)</f>
+        <f t="shared" ref="AO6:AQ12" si="16">IF($AR6="","na",AE6/$AW6)</f>
         <v>6.9584555997486319</v>
       </c>
       <c r="AP6" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.5660844380272962</v>
       </c>
       <c r="AQ6" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.6474272379442336</v>
       </c>
-      <c r="AR6" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="AS6" s="12">
+      <c r="AR6" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS6" s="11">
         <v>6.23</v>
       </c>
-      <c r="AT6" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU6" s="34">
+      <c r="AT6" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU6" s="33">
         <f>IF($AR6="","na",AS6/(AI6/AW6)-1)</f>
         <v>-0.2362672176308539</v>
       </c>
@@ -2105,92 +2099,92 @@
       </c>
     </row>
     <row r="7" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="E7" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="8">
         <v>45838</v>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="49">
         <v>0</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="36">
         <v>261600381459</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="36">
         <v>44432848</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="36">
         <f>3563298-4942-2461</f>
         <v>3555895</v>
       </c>
-      <c r="K7" s="42">
+      <c r="K7" s="41">
         <f>30469491/40847989</f>
         <v>0.74592389358506728</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L7" s="46">
         <f>589882+104928</f>
         <v>694810</v>
       </c>
-      <c r="M7" s="47">
+      <c r="M7" s="46">
         <f>21210+21417</f>
         <v>42627</v>
       </c>
-      <c r="N7" s="37">
+      <c r="N7" s="36">
         <v>-365879</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="42">
         <v>0.25</v>
       </c>
-      <c r="P7" s="37">
+      <c r="P7" s="36">
         <v>335577</v>
       </c>
-      <c r="Q7" s="46">
-        <f t="shared" ref="Q7:Q12" si="16">(L7+M7/2+N7)*(1-O7)</f>
+      <c r="Q7" s="45">
+        <f t="shared" ref="Q7:Q12" si="17">(L7+M7/2+N7)*(1-O7)</f>
         <v>262683.375</v>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="37">
         <f>0.206+0.197</f>
         <v>0.40300000000000002</v>
       </c>
-      <c r="S7" s="11">
+      <c r="S7" s="10">
         <f>589882/25040400</f>
         <v>2.3557211546141436E-2</v>
       </c>
-      <c r="T7" s="34">
+      <c r="T7" s="33">
         <f t="shared" si="0"/>
         <v>0.52658856378002616</v>
       </c>
-      <c r="U7" s="34">
+      <c r="U7" s="33">
         <f t="shared" si="1"/>
         <v>7.3872646689511365E-2</v>
       </c>
-      <c r="V7" s="35">
+      <c r="V7" s="34">
         <f t="shared" si="2"/>
         <v>1.5637305085642945E-2</v>
       </c>
-      <c r="W7" s="36">
+      <c r="W7" s="35">
         <f t="shared" si="3"/>
         <v>12.495545565884257</v>
       </c>
-      <c r="X7" s="34">
+      <c r="X7" s="33">
         <f t="shared" si="4"/>
         <v>0.37806504655949108</v>
       </c>
-      <c r="Y7" s="36">
+      <c r="Y7" s="35">
         <f t="shared" si="5"/>
         <v>13.592850974329741</v>
       </c>
-      <c r="Z7" s="36">
+      <c r="Z7" s="35">
         <f t="shared" si="6"/>
         <v>1.0041398775298411</v>
       </c>
@@ -2199,40 +2193,40 @@
         <v>0.40133850772998869</v>
       </c>
       <c r="AB7" s="7">
-        <f>(U7-g)/((k+G7)-g)</f>
+        <f t="shared" si="8"/>
         <v>0.89787744482518939</v>
       </c>
       <c r="AC7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12.204714300720774</v>
       </c>
       <c r="AD7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.3617224896519993</v>
       </c>
       <c r="AE7" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.8975680604798519</v>
       </c>
       <c r="AF7" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.7201348785712796</v>
       </c>
       <c r="AG7" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.945962753461778</v>
       </c>
-      <c r="AH7" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="AI7" s="12">
+      <c r="AH7" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI7" s="11">
         <v>8.68</v>
       </c>
-      <c r="AJ7" s="12" t="s">
+      <c r="AJ7" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK7" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AL7" s="7">
@@ -2240,40 +2234,40 @@
         <v>1</v>
       </c>
       <c r="AM7" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.642857142857143E-2</v>
       </c>
       <c r="AN7" s="7">
-        <f t="shared" ref="AN7:AN12" si="17">IF($AR7="","na",AD7/$AW7)</f>
+        <f t="shared" ref="AN7:AN12" si="18">IF($AR7="","na",AD7/$AW7)</f>
         <v>7.148002797361797</v>
       </c>
       <c r="AO7" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.8736719780672484</v>
       </c>
       <c r="AP7" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10.921499863563236</v>
       </c>
       <c r="AQ7" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12.298834554451435</v>
       </c>
-      <c r="AR7" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="AS7" s="12">
+      <c r="AR7" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS7" s="11">
         <v>7.65</v>
       </c>
-      <c r="AT7" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU7" s="34">
-        <f t="shared" ref="AU7:AU12" si="18">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
+      <c r="AT7" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU7" s="33">
+        <f t="shared" ref="AU7:AU12" si="19">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
         <v>-0.21561059907834101</v>
       </c>
       <c r="AV7" s="7" t="str">
-        <f t="shared" ref="AV7:AV12" si="19">IF($AR7="","na",AT7&amp;D7)</f>
+        <f t="shared" ref="AV7:AV12" si="20">IF($AR7="","na",AT7&amp;D7)</f>
         <v>HKDCNY</v>
       </c>
       <c r="AW7" s="7">
@@ -2281,97 +2275,97 @@
         <v>0.89</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" ref="AX7:AX12" si="20">IF($AR7="","na",(R7/AW7)/AS7)</f>
+        <f t="shared" ref="AX7:AX12" si="21">IF($AR7="","na",(R7/AW7)/AS7)</f>
         <v>5.9190717485496071E-2</v>
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="E8" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F8" s="8">
         <v>45838</v>
       </c>
-      <c r="G8" s="63">
+      <c r="G8" s="49">
         <v>0</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="36">
         <v>349983033873</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="36">
         <v>46855878</v>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="36">
         <f>3143100-28563-1381-300488</f>
         <v>2812668</v>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="41">
         <f>31900486/43706637</f>
         <v>0.72987738681427261</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="46">
         <f>580692+75567</f>
         <v>656259</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="46">
         <f>7943+31139</f>
         <v>39082</v>
       </c>
-      <c r="N8" s="37">
+      <c r="N8" s="36">
         <v>-390774</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="42">
         <v>0.25</v>
       </c>
-      <c r="P8" s="37">
+      <c r="P8" s="36">
         <v>282083</v>
       </c>
-      <c r="Q8" s="46">
-        <f t="shared" si="16"/>
+      <c r="Q8" s="45">
+        <f t="shared" si="17"/>
         <v>213769.5</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="37">
         <f>0.1255+0.1164</f>
         <v>0.2419</v>
       </c>
-      <c r="S8" s="11">
+      <c r="S8" s="10">
         <f>580692/23977013</f>
         <v>2.4218696465652331E-2</v>
       </c>
-      <c r="T8" s="34">
+      <c r="T8" s="33">
         <f t="shared" si="0"/>
         <v>0.59545697659003538</v>
       </c>
-      <c r="U8" s="34">
+      <c r="U8" s="33">
         <f t="shared" si="1"/>
         <v>7.6002393457030831E-2</v>
       </c>
-      <c r="V8" s="35">
+      <c r="V8" s="34">
         <f t="shared" si="2"/>
         <v>1.400590551307138E-2</v>
       </c>
-      <c r="W8" s="36">
+      <c r="W8" s="35">
         <f t="shared" si="3"/>
         <v>16.658872643340771</v>
       </c>
-      <c r="X8" s="34">
+      <c r="X8" s="33">
         <f t="shared" si="4"/>
         <v>0.32573953271497991</v>
       </c>
-      <c r="Y8" s="36">
+      <c r="Y8" s="35">
         <f t="shared" si="5"/>
         <v>8.0365838562924345</v>
       </c>
-      <c r="Z8" s="36">
+      <c r="Z8" s="35">
         <f t="shared" si="6"/>
         <v>0.61079960829635971</v>
       </c>
@@ -2380,40 +2374,40 @@
         <v>0.39603823695091539</v>
       </c>
       <c r="AB8" s="7">
-        <f>(U8-g)/((k+G8)-g)</f>
+        <f t="shared" si="8"/>
         <v>0.93337322428384717</v>
       </c>
       <c r="AC8" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7.5011321861751838</v>
       </c>
       <c r="AD8" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.8993840391989112</v>
       </c>
       <c r="AE8" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.8417424890972054</v>
       </c>
       <c r="AF8" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.9601231499834695</v>
       </c>
       <c r="AG8" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.712372290957056</v>
       </c>
-      <c r="AH8" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI8" s="12">
+      <c r="AH8" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI8" s="11">
         <v>6.88</v>
       </c>
-      <c r="AJ8" s="12" t="s">
+      <c r="AJ8" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK8" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AL8" s="7">
@@ -2421,40 +2415,40 @@
         <v>1</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.5159883720930235E-2</v>
       </c>
       <c r="AN8" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.3813303811223721</v>
       </c>
       <c r="AO8" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.4401601001092192</v>
       </c>
       <c r="AP8" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.6967675842510896</v>
       </c>
       <c r="AQ8" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.5419913381539958</v>
       </c>
-      <c r="AR8" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="AS8" s="12">
+      <c r="AR8" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="AS8" s="11">
         <v>5.39</v>
       </c>
-      <c r="AT8" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU8" s="34">
-        <f t="shared" si="18"/>
+      <c r="AT8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU8" s="33">
+        <f t="shared" si="19"/>
         <v>-0.30274709302325575</v>
       </c>
       <c r="AV8" s="7" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW8" s="7">
@@ -2462,97 +2456,97 @@
         <v>0.89</v>
       </c>
       <c r="AX8" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.0426299222446902E-2</v>
       </c>
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="E9" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F9" s="8">
         <v>45838</v>
       </c>
-      <c r="G9" s="63">
+      <c r="G9" s="49">
         <v>0</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="36">
         <v>322212411814</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="36">
         <v>36790613</v>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="36">
         <f>2987590-29158-2795-395040</f>
         <v>2560597</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="41">
         <f>25638312/33664948</f>
         <v>0.76157289772139258</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="46">
         <f>448934+76590</f>
         <v>525524</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="46">
         <f>52049+41453</f>
         <v>93502</v>
       </c>
-      <c r="N9" s="37">
+      <c r="N9" s="36">
         <v>-337627</v>
       </c>
-      <c r="O9" s="43">
+      <c r="O9" s="42">
         <v>0.25</v>
       </c>
-      <c r="P9" s="37">
+      <c r="P9" s="36">
         <v>252719</v>
       </c>
-      <c r="Q9" s="46">
-        <f t="shared" si="16"/>
+      <c r="Q9" s="45">
+        <f t="shared" si="17"/>
         <v>175986</v>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="37">
         <f>0.1216+0.1208</f>
         <v>0.2424</v>
       </c>
-      <c r="S9" s="11">
+      <c r="S9" s="10">
         <f>448934/21055282</f>
         <v>2.1321680707007393E-2</v>
       </c>
-      <c r="T9" s="34">
+      <c r="T9" s="33">
         <f t="shared" si="0"/>
         <v>0.64245781353468157</v>
       </c>
-      <c r="U9" s="34">
+      <c r="U9" s="33">
         <f t="shared" si="1"/>
         <v>6.8728503548195985E-2</v>
       </c>
-      <c r="V9" s="35">
+      <c r="V9" s="34">
         <f t="shared" si="2"/>
         <v>1.4284187110445809E-2</v>
       </c>
-      <c r="W9" s="36">
+      <c r="W9" s="35">
         <f t="shared" si="3"/>
         <v>14.367982544695632</v>
       </c>
-      <c r="X9" s="34">
+      <c r="X9" s="33">
         <f t="shared" si="4"/>
         <v>0.33487718924349791</v>
       </c>
-      <c r="Y9" s="36">
+      <c r="Y9" s="35">
         <f t="shared" si="5"/>
         <v>7.9469222975747051</v>
       </c>
-      <c r="Z9" s="36">
+      <c r="Z9" s="35">
         <f t="shared" si="6"/>
         <v>0.54618007732610097</v>
       </c>
@@ -2561,40 +2555,40 @@
         <v>0.44380967022214041</v>
       </c>
       <c r="AB9" s="7">
-        <f>(U9-g)/((k+G9)-g)</f>
+        <f t="shared" si="8"/>
         <v>0.81214172580326638</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.45402718957678</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.4177621001950751</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.2379685002558771</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.2108060626568031</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.864892240591038</v>
       </c>
-      <c r="AH9" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="AI9" s="12">
+      <c r="AH9" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI9" s="11">
         <v>5.34</v>
       </c>
-      <c r="AJ9" s="12" t="s">
+      <c r="AJ9" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK9" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AL9" s="7">
@@ -2602,40 +2596,40 @@
         <v>1</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.5393258426966294E-2</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.8401821350506462</v>
       </c>
       <c r="AO9" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.7617623598380643</v>
       </c>
       <c r="AP9" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.8548382726480934</v>
       </c>
       <c r="AQ9" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.5897665624618407</v>
       </c>
-      <c r="AR9" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="AS9" s="12">
+      <c r="AR9" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="AS9" s="11">
         <v>4.47</v>
       </c>
-      <c r="AT9" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU9" s="34">
-        <f t="shared" si="18"/>
+      <c r="AT9" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU9" s="33">
+        <f t="shared" si="19"/>
         <v>-0.255</v>
       </c>
       <c r="AV9" s="7" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW9" s="7">
@@ -2643,96 +2637,96 @@
         <v>0.89</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.0930548224115838E-2</v>
       </c>
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="E10" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F10" s="8">
         <v>45838</v>
       </c>
-      <c r="G10" s="63">
+      <c r="G10" s="49">
         <v>0</v>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="36">
         <v>21162855196</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="36">
         <v>10614376</v>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="36">
         <f>881747-1054-532-78891</f>
         <v>801270</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="41">
         <f>5964497/9720864</f>
         <v>0.6135768384374064</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="46">
         <f>148107+24096+661</f>
         <v>172864</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="46">
         <f>503+36202</f>
         <v>36705</v>
       </c>
-      <c r="N10" s="37">
+      <c r="N10" s="36">
         <v>-125029</v>
       </c>
-      <c r="O10" s="43">
+      <c r="O10" s="42">
         <v>0.25</v>
       </c>
-      <c r="P10" s="37">
+      <c r="P10" s="36">
         <v>77205</v>
       </c>
-      <c r="Q10" s="46">
-        <f t="shared" si="16"/>
+      <c r="Q10" s="45">
+        <f t="shared" si="17"/>
         <v>49640.625</v>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="37">
         <v>1.06</v>
       </c>
-      <c r="S10" s="11">
+      <c r="S10" s="10">
         <f>148107/5608859</f>
         <v>2.6405905372197804E-2</v>
       </c>
-      <c r="T10" s="34">
+      <c r="T10" s="33">
         <f t="shared" si="0"/>
         <v>0.72327957238059981</v>
       </c>
-      <c r="U10" s="34">
+      <c r="U10" s="33">
         <f t="shared" si="1"/>
         <v>6.195243176457374E-2</v>
       </c>
-      <c r="V10" s="35">
+      <c r="V10" s="34">
         <f t="shared" si="2"/>
         <v>1.6285837245637425E-2</v>
       </c>
-      <c r="W10" s="36">
+      <c r="W10" s="35">
         <f t="shared" si="3"/>
         <v>13.246940481984849</v>
       </c>
-      <c r="X10" s="34">
+      <c r="X10" s="33">
         <f t="shared" si="4"/>
         <v>0.28716577772121438</v>
       </c>
-      <c r="Y10" s="36">
+      <c r="Y10" s="35">
         <f t="shared" si="5"/>
         <v>37.862093398033004</v>
       </c>
-      <c r="Z10" s="36">
+      <c r="Z10" s="35">
         <f t="shared" si="6"/>
         <v>2.3456487577055571</v>
       </c>
@@ -2741,40 +2735,40 @@
         <v>0.45190056546951218</v>
       </c>
       <c r="AB10" s="7">
-        <f>(U10-g)/((k+G10)-g)</f>
+        <f t="shared" si="8"/>
         <v>0.69920719607622894</v>
       </c>
       <c r="AC10" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>26.473448162414957</v>
       </c>
       <c r="AD10" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14.139388367642148</v>
       </c>
       <c r="AE10" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>17.521766588388239</v>
       </c>
       <c r="AF10" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21.532478422844516</v>
       </c>
       <c r="AG10" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24.228568841811072</v>
       </c>
-      <c r="AH10" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI10" s="12">
+      <c r="AH10" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI10" s="11">
         <v>18.989999999999998</v>
       </c>
-      <c r="AJ10" s="12" t="s">
+      <c r="AJ10" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK10" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AL10" s="7">
@@ -2782,132 +2776,138 @@
         <v>1</v>
       </c>
       <c r="AM10" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.5818852027382841E-2</v>
       </c>
-      <c r="AN10" s="7" t="str">
-        <f t="shared" si="17"/>
-        <v>na</v>
-      </c>
-      <c r="AO10" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v>na</v>
-      </c>
-      <c r="AP10" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v>na</v>
-      </c>
-      <c r="AQ10" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v>na</v>
-      </c>
-      <c r="AR10" s="49"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="12"/>
-      <c r="AU10" s="34" t="str">
+      <c r="AN10" s="7">
         <f t="shared" si="18"/>
-        <v>na</v>
+        <v>14.139388367642148</v>
+      </c>
+      <c r="AO10" s="7">
+        <f t="shared" si="16"/>
+        <v>17.521766588388239</v>
+      </c>
+      <c r="AP10" s="7">
+        <f t="shared" si="16"/>
+        <v>21.532478422844516</v>
+      </c>
+      <c r="AQ10" s="7">
+        <f t="shared" si="16"/>
+        <v>24.228568841811072</v>
+      </c>
+      <c r="AR10" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS10" s="11">
+        <v>18.59</v>
+      </c>
+      <c r="AT10" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU10" s="33">
+        <f t="shared" si="19"/>
+        <v>-2.1063717746182098E-2</v>
       </c>
       <c r="AV10" s="7" t="str">
-        <f t="shared" si="19"/>
-        <v>na</v>
-      </c>
-      <c r="AW10" s="7" t="str">
+        <f t="shared" si="20"/>
+        <v>CNYCNY</v>
+      </c>
+      <c r="AW10" s="7">
         <f>IF($AR10="","na",IFERROR(VLOOKUP(AV10,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>na</v>
-      </c>
-      <c r="AX10" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>na</v>
+        <v>1</v>
+      </c>
+      <c r="AX10" s="5">
+        <f t="shared" si="21"/>
+        <v>5.7019903173749331E-2</v>
       </c>
     </row>
     <row r="11" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="E11" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F11" s="8">
         <v>45838</v>
       </c>
-      <c r="G11" s="63">
+      <c r="G11" s="49">
         <v>0</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="36">
         <v>120095053492</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="36">
         <v>18190521</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="36">
         <f>1138639-7832</f>
         <v>1130807</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="41">
         <f>16108809/17049715</f>
         <v>0.94481397489635455</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="46">
         <f>286123+25282</f>
         <v>311405</v>
       </c>
-      <c r="M11" s="47">
+      <c r="M11" s="46">
         <f>917+31715</f>
         <v>32632</v>
       </c>
-      <c r="N11" s="37">
+      <c r="N11" s="36">
         <v>-255176</v>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="42">
         <v>0.25</v>
       </c>
-      <c r="P11" s="37">
+      <c r="P11" s="36">
         <v>86479</v>
       </c>
-      <c r="Q11" s="46">
-        <f t="shared" si="16"/>
+      <c r="Q11" s="45">
+        <f t="shared" si="17"/>
         <v>54408.75</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="37">
         <f>0.1139 +0.1477</f>
         <v>0.2616</v>
       </c>
-      <c r="S11" s="11">
+      <c r="S11" s="10">
         <f>286123/8684144</f>
         <v>3.2947749369425475E-2</v>
       </c>
-      <c r="T11" s="34">
+      <c r="T11" s="33">
         <f t="shared" si="0"/>
         <v>0.81943449848268335</v>
       </c>
-      <c r="U11" s="34">
+      <c r="U11" s="33">
         <f t="shared" si="1"/>
         <v>4.8114974527041304E-2</v>
       </c>
-      <c r="V11" s="35">
+      <c r="V11" s="34">
         <f t="shared" si="2"/>
         <v>1.7119080866347919E-2</v>
       </c>
-      <c r="W11" s="36">
+      <c r="W11" s="35">
         <f t="shared" si="3"/>
         <v>16.086318001215062</v>
       </c>
-      <c r="X11" s="34">
+      <c r="X11" s="33">
         <f t="shared" si="4"/>
         <v>0.17472021964965237</v>
       </c>
-      <c r="Y11" s="36">
+      <c r="Y11" s="35">
         <f t="shared" si="5"/>
         <v>9.4159331889162896</v>
       </c>
-      <c r="Z11" s="36">
+      <c r="Z11" s="35">
         <f t="shared" si="6"/>
         <v>0.45304738553303009</v>
       </c>
@@ -2916,40 +2916,40 @@
         <v>0.57742304304927428</v>
       </c>
       <c r="AB11" s="7">
-        <f>(U11-g)/((k+G11)-g)</f>
+        <f t="shared" si="8"/>
         <v>0.46858290878402176</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.4121453625784044</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5119358831760321</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.0989390499793994</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.7935880218656868</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.259894726825121</v>
       </c>
-      <c r="AH11" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI11" s="12">
+      <c r="AH11" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI11" s="11">
         <v>5.17</v>
       </c>
-      <c r="AJ11" s="12" t="s">
+      <c r="AJ11" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK11" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AL11" s="7">
@@ -2957,40 +2957,40 @@
         <v>1</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.0599613152804646E-2</v>
       </c>
       <c r="AN11" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.8223998687371146</v>
       </c>
       <c r="AO11" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.4819539887408983</v>
       </c>
       <c r="AP11" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.2624584515344797</v>
       </c>
       <c r="AQ11" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.7863985694664279</v>
       </c>
-      <c r="AR11" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="AS11" s="12">
+      <c r="AR11" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS11" s="11">
         <v>5</v>
       </c>
-      <c r="AT11" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU11" s="34">
-        <f t="shared" si="18"/>
+      <c r="AT11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU11" s="33">
+        <f t="shared" si="19"/>
         <v>-0.13926499032882012</v>
       </c>
       <c r="AV11" s="7" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW11" s="7">
@@ -2998,96 +2998,96 @@
         <v>0.89</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.8786516853932581E-2</v>
       </c>
     </row>
     <row r="12" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="E12" s="8">
+        <v>45657</v>
+      </c>
+      <c r="F12" s="8">
         <v>45838</v>
       </c>
-      <c r="G12" s="63">
+      <c r="G12" s="49">
         <v>0</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="36">
         <v>25219845601</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="36">
         <v>12657151</v>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="36">
         <f>1289233-6153-9954-47907</f>
         <v>1225219</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="41">
         <f>9509526/11360291</f>
         <v>0.83708471904460902</v>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="46">
         <f>211277+72094</f>
         <v>283371</v>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="46">
         <f>14126+29880</f>
         <v>44006</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="36">
         <v>-158469</v>
       </c>
-      <c r="O12" s="43">
+      <c r="O12" s="42">
         <v>0.25</v>
       </c>
-      <c r="P12" s="37">
+      <c r="P12" s="36">
         <v>149559</v>
       </c>
-      <c r="Q12" s="46">
-        <f t="shared" si="16"/>
+      <c r="Q12" s="45">
+        <f t="shared" si="17"/>
         <v>110178.75</v>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="37">
         <v>2</v>
       </c>
-      <c r="S12" s="11">
+      <c r="S12" s="10">
         <f>211277/6300684</f>
         <v>3.3532391086428075E-2</v>
       </c>
-      <c r="T12" s="34">
+      <c r="T12" s="33">
         <f>-N12/L12</f>
         <v>0.55922800851180965</v>
       </c>
-      <c r="U12" s="34">
+      <c r="U12" s="33">
         <f t="shared" si="1"/>
         <v>8.9925760211031658E-2</v>
       </c>
-      <c r="V12" s="35">
+      <c r="V12" s="34">
         <f t="shared" si="2"/>
         <v>2.2388213587718121E-2</v>
       </c>
-      <c r="W12" s="36">
+      <c r="W12" s="35">
         <f t="shared" si="3"/>
         <v>10.33052131904582</v>
       </c>
-      <c r="X12" s="34">
-        <f t="shared" ref="X12" si="21">Q12/L12</f>
+      <c r="X12" s="33">
+        <f t="shared" ref="X12" si="22">Q12/L12</f>
         <v>0.38881448701525562</v>
       </c>
-      <c r="Y12" s="36">
+      <c r="Y12" s="35">
         <f t="shared" si="5"/>
         <v>48.581542463979972</v>
       </c>
-      <c r="Z12" s="36">
+      <c r="Z12" s="35">
         <f t="shared" si="6"/>
         <v>4.368732138297915</v>
       </c>
@@ -3096,40 +3096,40 @@
         <v>0.45779872436381791</v>
       </c>
       <c r="AB12" s="7">
-        <f>(U12-g)/((k+G12)-g)</f>
+        <f t="shared" si="8"/>
         <v>1.1654293368505275</v>
       </c>
       <c r="AC12" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>56.618354816971923</v>
       </c>
       <c r="AD12" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>29.75111090197689</v>
       </c>
       <c r="AE12" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>36.911750749106794</v>
       </c>
       <c r="AF12" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>45.407000502341631</v>
       </c>
       <c r="AG12" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>51.11974717559962</v>
       </c>
-      <c r="AH12" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI12" s="12">
+      <c r="AH12" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI12" s="11">
         <v>38.049999999999997</v>
       </c>
-      <c r="AJ12" s="12" t="s">
+      <c r="AJ12" s="11" t="s">
         <v>3</v>
       </c>
       <c r="AK12" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>CNYCNY</v>
       </c>
       <c r="AL12" s="7">
@@ -3137,40 +3137,40 @@
         <v>1</v>
       </c>
       <c r="AM12" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.2562417871222081E-2</v>
       </c>
       <c r="AN12" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>33.428214496603246</v>
       </c>
       <c r="AO12" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>41.473877246187406</v>
       </c>
       <c r="AP12" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>51.019101688024307</v>
       </c>
       <c r="AQ12" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>57.437918174831033</v>
       </c>
-      <c r="AR12" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="AS12" s="12">
+      <c r="AR12" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS12" s="11">
         <v>46.48</v>
       </c>
-      <c r="AT12" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU12" s="34">
-        <f t="shared" si="18"/>
+      <c r="AT12" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU12" s="33">
+        <f t="shared" si="19"/>
         <v>8.7180026281209022E-2</v>
       </c>
       <c r="AV12" s="7" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW12" s="7">
@@ -3178,7 +3178,7 @@
         <v>0.89</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.8347483030033465E-2</v>
       </c>
     </row>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE3FB05-4D0E-4865-AEFF-96D97FE9D424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A704E2A7-060D-48F5-8C79-726F241EF300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="164">
   <si>
     <t>Name</t>
   </si>
@@ -475,25 +475,7 @@
     <t>Primary Market</t>
   </si>
   <si>
-    <t>601398.SS</t>
-  </si>
-  <si>
-    <t>601939.SS</t>
-  </si>
-  <si>
-    <t>601288.SS</t>
-  </si>
-  <si>
-    <t>601988.SS</t>
-  </si>
-  <si>
     <t>601166.SS</t>
-  </si>
-  <si>
-    <t>601658.SS</t>
-  </si>
-  <si>
-    <t>600036.SS</t>
   </si>
   <si>
     <t>Primary Market 
@@ -538,18 +520,37 @@
   </si>
   <si>
     <t>股票代码</t>
+  </si>
+  <si>
+    <t>601398.SS</t>
+  </si>
+  <si>
+    <t>601939.SS</t>
+  </si>
+  <si>
+    <t>601288.SS</t>
+  </si>
+  <si>
+    <t>601988.SS</t>
+  </si>
+  <si>
+    <t>601658.SS</t>
+  </si>
+  <si>
+    <t>600036.SS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0&quot;yrs&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -739,7 +740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -870,13 +871,25 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1435,12 +1448,9 @@
     <col min="11" max="11" width="18.6640625" customWidth="1"/>
     <col min="12" max="18" width="18.6640625" customWidth="1" outlineLevel="1"/>
     <col min="19" max="24" width="18.6640625" customWidth="1"/>
-    <col min="25" max="27" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="18.796875" customWidth="1" collapsed="1"/>
-    <col min="29" max="33" width="18.796875" customWidth="1"/>
-    <col min="34" max="36" width="16.59765625" customWidth="1"/>
-    <col min="37" max="38" width="16.59765625" hidden="1" customWidth="1"/>
-    <col min="39" max="50" width="16.59765625" customWidth="1"/>
+    <col min="25" max="27" width="18.6640625" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="33" width="18.796875" customWidth="1"/>
+    <col min="34" max="50" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:50" ht="71.25" x14ac:dyDescent="0.45">
@@ -1541,46 +1551,46 @@
       <c r="AX2" s="2"/>
     </row>
     <row r="3" spans="2:50" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="56" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="59" t="s">
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="60" t="s">
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="T3" s="61"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="51" t="s">
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="52" t="s">
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" s="52"/>
+      <c r="AC3" s="55"/>
       <c r="AD3" s="26" t="s">
         <v>78</v>
       </c>
@@ -1593,14 +1603,14 @@
       <c r="AG3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AH3" s="50" t="s">
+      <c r="AH3" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
+      <c r="AI3" s="56"/>
+      <c r="AJ3" s="56"/>
+      <c r="AK3" s="56"/>
+      <c r="AL3" s="56"/>
+      <c r="AM3" s="56"/>
       <c r="AN3" s="26" t="s">
         <v>78</v>
       </c>
@@ -1613,15 +1623,15 @@
       <c r="AQ3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="AR3" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="AS3" s="50"/>
-      <c r="AT3" s="50"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="50"/>
-      <c r="AW3" s="50"/>
-      <c r="AX3" s="50"/>
+      <c r="AR3" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS3" s="52"/>
+      <c r="AT3" s="52"/>
+      <c r="AU3" s="52"/>
+      <c r="AV3" s="52"/>
+      <c r="AW3" s="52"/>
+      <c r="AX3" s="53"/>
     </row>
     <row r="4" spans="2:50" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="31" t="s">
@@ -1640,7 +1650,7 @@
         <v>69</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H4" s="29" t="s">
         <v>104</v>
@@ -1721,7 +1731,7 @@
         <v>92</v>
       </c>
       <c r="AH4" s="19" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="AI4" s="19" t="s">
         <v>88</v>
@@ -1751,7 +1761,7 @@
         <v>92</v>
       </c>
       <c r="AR4" s="19" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="AS4" s="19" t="s">
         <v>88</v>
@@ -1760,7 +1770,7 @@
         <v>28</v>
       </c>
       <c r="AU4" s="19" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="AV4" s="19" t="s">
         <v>110</v>
@@ -1789,7 +1799,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>96</v>
@@ -1870,7 +1880,7 @@
         <v>87</v>
       </c>
       <c r="AH5" s="20" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AI5" s="20" t="s">
         <v>53</v>
@@ -1896,7 +1906,7 @@
         <v>87</v>
       </c>
       <c r="AR5" s="20" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AS5" s="20" t="s">
         <v>53</v>
@@ -1905,7 +1915,7 @@
         <v>54</v>
       </c>
       <c r="AU5" s="20" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="AV5" s="20" t="s">
         <v>53</v>
@@ -2036,10 +2046,10 @@
         <v>8.5862102417703685</v>
       </c>
       <c r="AH6" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI6" s="11">
-        <v>7.26</v>
+        <v>158</v>
+      </c>
+      <c r="AI6" s="50">
+        <v>7.18</v>
       </c>
       <c r="AJ6" s="11" t="s">
         <v>3</v>
@@ -2054,14 +2064,14 @@
       </c>
       <c r="AM6" s="5">
         <f t="shared" ref="AM6:AM12" si="15">R6/AI6</f>
-        <v>4.2424242424242427E-2</v>
+        <v>4.2896935933147633E-2</v>
       </c>
       <c r="AN6" s="7">
-        <f>IF($AR6="","na",AD6/$AW6)</f>
+        <f t="shared" ref="AN6:AQ12" si="16">IF($AR6="","na",AD6/$AW6)</f>
         <v>5.6038769033366611</v>
       </c>
       <c r="AO6" s="7">
-        <f t="shared" ref="AO6:AQ12" si="16">IF($AR6="","na",AE6/$AW6)</f>
+        <f t="shared" si="16"/>
         <v>6.9584555997486319</v>
       </c>
       <c r="AP6" s="7">
@@ -2073,17 +2083,17 @@
         <v>9.6474272379442336</v>
       </c>
       <c r="AR6" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="AS6" s="11">
-        <v>6.23</v>
+        <v>147</v>
+      </c>
+      <c r="AS6" s="50">
+        <v>6.5</v>
       </c>
       <c r="AT6" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU6" s="33">
         <f>IF($AR6="","na",AS6/(AI6/AW6)-1)</f>
-        <v>-0.2362672176308539</v>
+        <v>-0.19428969359331472</v>
       </c>
       <c r="AV6" s="7" t="str">
         <f>IF($AR6="","na",AT6&amp;D6)</f>
@@ -2095,7 +2105,7 @@
       </c>
       <c r="AX6" s="5">
         <f>IF($AR6="","na",(R6/AW6)/AS6)</f>
-        <v>5.5548541850776408E-2</v>
+        <v>5.3241140881590314E-2</v>
       </c>
     </row>
     <row r="7" spans="2:50" x14ac:dyDescent="0.45">
@@ -2217,10 +2227,10 @@
         <v>10.945962753461778</v>
       </c>
       <c r="AH7" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI7" s="11">
-        <v>8.68</v>
+        <v>159</v>
+      </c>
+      <c r="AI7" s="50">
+        <v>8.81</v>
       </c>
       <c r="AJ7" s="11" t="s">
         <v>3</v>
@@ -2235,10 +2245,10 @@
       </c>
       <c r="AM7" s="5">
         <f t="shared" si="15"/>
-        <v>4.642857142857143E-2</v>
+        <v>4.5743473325766178E-2</v>
       </c>
       <c r="AN7" s="7">
-        <f t="shared" ref="AN7:AN12" si="18">IF($AR7="","na",AD7/$AW7)</f>
+        <f t="shared" si="16"/>
         <v>7.148002797361797</v>
       </c>
       <c r="AO7" s="7">
@@ -2254,20 +2264,20 @@
         <v>12.298834554451435</v>
       </c>
       <c r="AR7" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="AS7" s="11">
-        <v>7.65</v>
+        <v>146</v>
+      </c>
+      <c r="AS7" s="50">
+        <v>8.08</v>
       </c>
       <c r="AT7" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU7" s="33">
-        <f t="shared" ref="AU7:AU12" si="19">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
-        <v>-0.21561059907834101</v>
+        <f t="shared" ref="AU7:AU12" si="18">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
+        <v>-0.18374574347332584</v>
       </c>
       <c r="AV7" s="7" t="str">
-        <f t="shared" ref="AV7:AV12" si="20">IF($AR7="","na",AT7&amp;D7)</f>
+        <f t="shared" ref="AV7:AV12" si="19">IF($AR7="","na",AT7&amp;D7)</f>
         <v>HKDCNY</v>
       </c>
       <c r="AW7" s="7">
@@ -2275,8 +2285,8 @@
         <v>0.89</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" ref="AX7:AX12" si="21">IF($AR7="","na",(R7/AW7)/AS7)</f>
-        <v>5.9190717485496071E-2</v>
+        <f>IF($AR7="","na",(R7/AW7)/AS7)</f>
+        <v>5.6040716431193682E-2</v>
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.45">
@@ -2398,10 +2408,10 @@
         <v>6.712372290957056</v>
       </c>
       <c r="AH8" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="AI8" s="11">
-        <v>6.88</v>
+        <v>160</v>
+      </c>
+      <c r="AI8" s="50">
+        <v>6.61</v>
       </c>
       <c r="AJ8" s="11" t="s">
         <v>3</v>
@@ -2416,10 +2426,10 @@
       </c>
       <c r="AM8" s="5">
         <f t="shared" si="15"/>
-        <v>3.5159883720930235E-2</v>
+        <v>3.6596066565809382E-2</v>
       </c>
       <c r="AN8" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4.3813303811223721</v>
       </c>
       <c r="AO8" s="7">
@@ -2435,20 +2445,20 @@
         <v>7.5419913381539958</v>
       </c>
       <c r="AR8" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="AS8" s="11">
-        <v>5.39</v>
+        <v>148</v>
+      </c>
+      <c r="AS8" s="50">
+        <v>5.54</v>
       </c>
       <c r="AT8" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU8" s="33">
+        <f t="shared" si="18"/>
+        <v>-0.25406959152798791</v>
+      </c>
+      <c r="AV8" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>-0.30274709302325575</v>
-      </c>
-      <c r="AV8" s="7" t="str">
-        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW8" s="7">
@@ -2456,8 +2466,8 @@
         <v>0.89</v>
       </c>
       <c r="AX8" s="5">
-        <f t="shared" si="21"/>
-        <v>5.0426299222446902E-2</v>
+        <f>IF($AR8="","na",(R8/AW8)/AS8)</f>
+        <v>4.9060966211008805E-2</v>
       </c>
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
@@ -2579,9 +2589,9 @@
         <v>5.864892240591038</v>
       </c>
       <c r="AH9" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI9" s="11">
+        <v>161</v>
+      </c>
+      <c r="AI9" s="50">
         <v>5.34</v>
       </c>
       <c r="AJ9" s="11" t="s">
@@ -2600,7 +2610,7 @@
         <v>4.5393258426966294E-2</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>3.8401821350506462</v>
       </c>
       <c r="AO9" s="7">
@@ -2616,20 +2626,20 @@
         <v>6.5897665624618407</v>
       </c>
       <c r="AR9" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="AS9" s="11">
-        <v>4.47</v>
+        <v>149</v>
+      </c>
+      <c r="AS9" s="50">
+        <v>4.72</v>
       </c>
       <c r="AT9" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU9" s="33">
+        <f t="shared" si="18"/>
+        <v>-0.21333333333333337</v>
+      </c>
+      <c r="AV9" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>-0.255</v>
-      </c>
-      <c r="AV9" s="7" t="str">
-        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW9" s="7">
@@ -2637,8 +2647,8 @@
         <v>0.89</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" si="21"/>
-        <v>6.0930548224115838E-2</v>
+        <f>IF($AR9="","na",(R9/AW9)/AS9)</f>
+        <v>5.7703294610550383E-2</v>
       </c>
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
@@ -2759,10 +2769,10 @@
         <v>24.228568841811072</v>
       </c>
       <c r="AH10" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="AI10" s="11">
-        <v>18.989999999999998</v>
+        <v>143</v>
+      </c>
+      <c r="AI10" s="50">
+        <v>18.59</v>
       </c>
       <c r="AJ10" s="11" t="s">
         <v>3</v>
@@ -2777,49 +2787,31 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="15"/>
-        <v>5.5818852027382841E-2</v>
-      </c>
-      <c r="AN10" s="7">
-        <f t="shared" si="18"/>
-        <v>14.139388367642148</v>
-      </c>
-      <c r="AO10" s="7">
+        <v>5.7019903173749331E-2</v>
+      </c>
+      <c r="AN10" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>17.521766588388239</v>
-      </c>
-      <c r="AP10" s="7">
+        <v>na</v>
+      </c>
+      <c r="AO10" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>21.532478422844516</v>
-      </c>
-      <c r="AQ10" s="7">
+        <v>na</v>
+      </c>
+      <c r="AP10" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>24.228568841811072</v>
-      </c>
-      <c r="AR10" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS10" s="11">
-        <v>18.59</v>
-      </c>
-      <c r="AT10" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AU10" s="33">
-        <f t="shared" si="19"/>
-        <v>-2.1063717746182098E-2</v>
-      </c>
-      <c r="AV10" s="7" t="str">
-        <f t="shared" si="20"/>
-        <v>CNYCNY</v>
-      </c>
-      <c r="AW10" s="7">
-        <f>IF($AR10="","na",IFERROR(VLOOKUP(AV10,Assumptions!B$12:C$13,2,FALSE),1))</f>
-        <v>1</v>
-      </c>
-      <c r="AX10" s="5">
-        <f t="shared" si="21"/>
-        <v>5.7019903173749331E-2</v>
-      </c>
+        <v>na</v>
+      </c>
+      <c r="AQ10" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>na</v>
+      </c>
+      <c r="AR10" s="48"/>
+      <c r="AS10" s="50"/>
+      <c r="AT10" s="11"/>
+      <c r="AU10" s="33"/>
+      <c r="AV10" s="7"/>
+      <c r="AW10" s="7"/>
+      <c r="AX10" s="5"/>
     </row>
     <row r="11" spans="2:50" x14ac:dyDescent="0.45">
       <c r="B11" s="47" t="s">
@@ -2940,10 +2932,10 @@
         <v>4.259894726825121</v>
       </c>
       <c r="AH11" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI11" s="11">
-        <v>5.17</v>
+        <v>162</v>
+      </c>
+      <c r="AI11" s="50">
+        <v>5.1100000000000003</v>
       </c>
       <c r="AJ11" s="11" t="s">
         <v>3</v>
@@ -2958,10 +2950,10 @@
       </c>
       <c r="AM11" s="5">
         <f t="shared" si="15"/>
-        <v>5.0599613152804646E-2</v>
+        <v>5.1193737769080233E-2</v>
       </c>
       <c r="AN11" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>2.8223998687371146</v>
       </c>
       <c r="AO11" s="7">
@@ -2977,20 +2969,20 @@
         <v>4.7863985694664279</v>
       </c>
       <c r="AR11" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="AS11" s="11">
-        <v>5</v>
+        <v>150</v>
+      </c>
+      <c r="AS11" s="50">
+        <v>5.09</v>
       </c>
       <c r="AT11" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU11" s="33">
+        <f t="shared" si="18"/>
+        <v>-0.11348336594911945</v>
+      </c>
+      <c r="AV11" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>-0.13926499032882012</v>
-      </c>
-      <c r="AV11" s="7" t="str">
-        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW11" s="7">
@@ -2998,8 +2990,8 @@
         <v>0.89</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="21"/>
-        <v>5.8786516853932581E-2</v>
+        <f>IF($AR11="","na",(R11/AW11)/AS11)</f>
+        <v>5.7747069601112554E-2</v>
       </c>
     </row>
     <row r="12" spans="2:50" x14ac:dyDescent="0.45">
@@ -3080,7 +3072,7 @@
         <v>10.33052131904582</v>
       </c>
       <c r="X12" s="33">
-        <f t="shared" ref="X12" si="22">Q12/L12</f>
+        <f t="shared" ref="X12" si="20">Q12/L12</f>
         <v>0.38881448701525562</v>
       </c>
       <c r="Y12" s="35">
@@ -3120,10 +3112,10 @@
         <v>51.11974717559962</v>
       </c>
       <c r="AH12" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI12" s="11">
-        <v>38.049999999999997</v>
+        <v>163</v>
+      </c>
+      <c r="AI12" s="50">
+        <v>38.99</v>
       </c>
       <c r="AJ12" s="11" t="s">
         <v>3</v>
@@ -3138,10 +3130,10 @@
       </c>
       <c r="AM12" s="5">
         <f t="shared" si="15"/>
-        <v>5.2562417871222081E-2</v>
+        <v>5.129520389843549E-2</v>
       </c>
       <c r="AN12" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>33.428214496603246</v>
       </c>
       <c r="AO12" s="7">
@@ -3157,20 +3149,20 @@
         <v>57.437918174831033</v>
       </c>
       <c r="AR12" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="AS12" s="11">
-        <v>46.48</v>
+        <v>151</v>
+      </c>
+      <c r="AS12" s="50">
+        <v>49.62</v>
       </c>
       <c r="AT12" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU12" s="33">
+        <f t="shared" si="18"/>
+        <v>0.13264426776096427</v>
+      </c>
+      <c r="AV12" s="7" t="str">
         <f t="shared" si="19"/>
-        <v>8.7180026281209022E-2</v>
-      </c>
-      <c r="AV12" s="7" t="str">
-        <f t="shared" si="20"/>
         <v>HKDCNY</v>
       </c>
       <c r="AW12" s="7">
@@ -3178,8 +3170,8 @@
         <v>0.89</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" si="21"/>
-        <v>4.8347483030033465E-2</v>
+        <f>IF($AR12="","na",(R12/AW12)/AS12)</f>
+        <v>4.5288009093832231E-2</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A704E2A7-060D-48F5-8C79-726F241EF300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4327C7F-B691-4100-B623-428CC17DAB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="166">
   <si>
     <t>Name</t>
   </si>
@@ -507,12 +507,6 @@
     <t>Secondary Market</t>
   </si>
   <si>
-    <t>Market Difference</t>
-  </si>
-  <si>
-    <t>市场溢价</t>
-  </si>
-  <si>
     <t>Company specific Premium</t>
   </si>
   <si>
@@ -538,6 +532,19 @@
   </si>
   <si>
     <t>600036.SS</t>
+  </si>
+  <si>
+    <t>汇率</t>
+  </si>
+  <si>
+    <t>外汇符号</t>
+  </si>
+  <si>
+    <t>Intermarket 
+Price Gap</t>
+  </si>
+  <si>
+    <t>跨交易所价差</t>
   </si>
 </sst>
 </file>
@@ -610,7 +617,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -632,12 +639,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,7 +741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -786,29 +787,26 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -820,12 +818,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -852,10 +844,10 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -874,6 +866,45 @@
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -883,44 +914,11 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -928,7 +926,85 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1350,7 +1426,7 @@
       <c r="B12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="36">
         <v>7.8</v>
       </c>
       <c r="D12" s="1"/>
@@ -1359,7 +1435,7 @@
       <c r="B13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="36">
         <v>0.89</v>
       </c>
       <c r="D13" s="1"/>
@@ -1368,14 +1444,14 @@
       <c r="B14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="37">
         <v>1000000</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
-      <c r="C15" s="38"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="1"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.45">
@@ -1551,387 +1627,391 @@
       <c r="AX2" s="2"/>
     </row>
     <row r="3" spans="2:50" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60" t="s">
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63" t="s">
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="64" t="s">
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
-      <c r="Y3" s="54" t="s">
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="55" t="s">
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="26" t="s">
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="AE3" s="26" t="s">
+      <c r="AE3" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="AF3" s="26" t="s">
+      <c r="AF3" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="AG3" s="26" t="s">
+      <c r="AG3" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="AH3" s="56" t="s">
+      <c r="AH3" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="AI3" s="56"/>
-      <c r="AJ3" s="56"/>
-      <c r="AK3" s="56"/>
-      <c r="AL3" s="56"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="26" t="s">
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53"/>
+      <c r="AN3" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="AO3" s="26" t="s">
+      <c r="AO3" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="AP3" s="26" t="s">
+      <c r="AP3" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="AQ3" s="26" t="s">
+      <c r="AQ3" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="AR3" s="51" t="s">
+      <c r="AR3" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="53"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="49"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="50"/>
     </row>
     <row r="4" spans="2:50" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="29" t="s">
+      <c r="G4" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="M4" s="43" t="s">
+      <c r="M4" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="N4" s="43" t="s">
+      <c r="N4" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="O4" s="43" t="s">
+      <c r="O4" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="P4" s="43" t="s">
+      <c r="P4" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="Q4" s="43" t="s">
+      <c r="Q4" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="R4" s="43" t="s">
+      <c r="R4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="27" t="s">
+      <c r="S4" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="27" t="s">
+      <c r="T4" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="U4" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="W4" s="27" t="s">
+      <c r="W4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="27" t="s">
+      <c r="X4" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="Y4" s="23" t="s">
+      <c r="Y4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="Z4" s="23" t="s">
+      <c r="Z4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="AA4" s="23" t="s">
+      <c r="AA4" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="AB4" s="21" t="s">
+      <c r="AB4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AC4" s="21" t="s">
+      <c r="AC4" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="AD4" s="17" t="s">
+      <c r="AD4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="AE4" s="17" t="s">
+      <c r="AE4" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="AF4" s="17" t="s">
+      <c r="AF4" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="AG4" s="17" t="s">
+      <c r="AG4" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AH4" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="AI4" s="19" t="s">
+      <c r="AI4" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="AJ4" s="19" t="s">
+      <c r="AJ4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="AK4" s="19" t="s">
+      <c r="AK4" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="AL4" s="19" t="s">
+      <c r="AL4" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="AM4" s="19" t="s">
+      <c r="AM4" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AN4" s="17" t="s">
+      <c r="AN4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="AO4" s="17" t="s">
+      <c r="AO4" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="AP4" s="17" t="s">
+      <c r="AP4" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="AQ4" s="17" t="s">
+      <c r="AQ4" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="AR4" s="19" t="s">
+      <c r="AR4" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="AS4" s="19" t="s">
+      <c r="AS4" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="AT4" s="19" t="s">
+      <c r="AT4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="AU4" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AV4" s="19" t="s">
+      <c r="AU4" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV4" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="AW4" s="19" t="s">
+      <c r="AW4" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="AX4" s="19" t="s">
+      <c r="AX4" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="H5" s="30" t="s">
+      <c r="G5" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="I5" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="M5" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="N5" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="O5" s="44" t="s">
+      <c r="O5" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="P5" s="44" t="s">
+      <c r="P5" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="Q5" s="44" t="s">
+      <c r="Q5" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="R5" s="44" t="s">
+      <c r="R5" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="S5" s="28" t="s">
+      <c r="S5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="T5" s="28" t="s">
+      <c r="T5" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="U5" s="28" t="s">
+      <c r="U5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="V5" s="28" t="s">
+      <c r="V5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="28" t="s">
+      <c r="W5" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="X5" s="28" t="s">
+      <c r="X5" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="Y5" s="24" t="s">
+      <c r="Y5" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="Z5" s="25" t="s">
+      <c r="Z5" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="AA5" s="25" t="s">
+      <c r="AA5" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="AB5" s="22" t="s">
+      <c r="AB5" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="AC5" s="22" t="s">
+      <c r="AC5" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="AD5" s="18" t="s">
+      <c r="AD5" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="AE5" s="18" t="s">
+      <c r="AE5" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="AF5" s="18" t="s">
+      <c r="AF5" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="AG5" s="18" t="s">
+      <c r="AG5" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="AH5" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="AI5" s="20" t="s">
+      <c r="AH5" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="AJ5" s="20" t="s">
+      <c r="AJ5" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="20"/>
-      <c r="AL5" s="20"/>
-      <c r="AM5" s="20" t="s">
+      <c r="AK5" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL5" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="AM5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="AN5" s="18" t="s">
+      <c r="AN5" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="AO5" s="18" t="s">
+      <c r="AO5" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="AP5" s="18" t="s">
+      <c r="AP5" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="AQ5" s="18" t="s">
+      <c r="AQ5" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="AR5" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="AS5" s="20" t="s">
+      <c r="AR5" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="AS5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="AT5" s="20" t="s">
+      <c r="AT5" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="AU5" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="AV5" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="AW5" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX5" s="20" t="s">
+      <c r="AU5" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="AV5" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW5" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="AX5" s="18" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="44" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -1943,45 +2023,45 @@
       <c r="F6" s="8">
         <v>45838</v>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="46">
         <v>0</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="33">
         <v>356406257089</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="33">
         <v>52317931</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="33">
         <f>4114692-23118-19420-59031</f>
         <v>4013123</v>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="38">
         <f>36904556/48179055</f>
         <v>0.76598754375734435</v>
       </c>
-      <c r="L6" s="46">
+      <c r="L6" s="43">
         <f>637405+109397</f>
         <v>746802</v>
       </c>
-      <c r="M6" s="46">
+      <c r="M6" s="43">
         <f>28762+40930</f>
         <v>69692</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="33">
         <v>-400918</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="39">
         <v>0.25</v>
       </c>
-      <c r="P6" s="36">
+      <c r="P6" s="33">
         <v>366946</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="42">
         <f>(L6+M6/2+N6)*(1-O6)</f>
         <v>285547.5</v>
       </c>
-      <c r="R6" s="37">
+      <c r="R6" s="34">
         <f>0.1646+0.1434</f>
         <v>0.308</v>
       </c>
@@ -1989,31 +2069,31 @@
         <f>637405/27613781</f>
         <v>2.3082858519085089E-2</v>
       </c>
-      <c r="T6" s="33">
+      <c r="T6" s="30">
         <f t="shared" ref="T6:T11" si="0">-N6/L6</f>
         <v>0.53684644658155711</v>
       </c>
-      <c r="U6" s="33">
+      <c r="U6" s="30">
         <f t="shared" ref="U6:U12" si="1">Q6/J6</f>
         <v>7.115343835710991E-2</v>
       </c>
-      <c r="V6" s="34">
+      <c r="V6" s="31">
         <f t="shared" ref="V6:V12" si="2">L6/I6</f>
         <v>1.4274303010950491E-2</v>
       </c>
-      <c r="W6" s="35">
+      <c r="W6" s="32">
         <f t="shared" ref="W6:W12" si="3">I6/J6</f>
         <v>13.036712555284252</v>
       </c>
-      <c r="X6" s="33">
+      <c r="X6" s="30">
         <f t="shared" ref="X6:X11" si="4">Q6/L6</f>
         <v>0.38236038468027672</v>
       </c>
-      <c r="Y6" s="35">
+      <c r="Y6" s="32">
         <f t="shared" ref="Y6:Y12" si="5">J6/(H6/1000000)*$AL6</f>
         <v>11.259967860210329</v>
       </c>
-      <c r="Z6" s="35">
+      <c r="Z6" s="32">
         <f t="shared" ref="Z6:Z12" si="6">Q6/(H6/1000000)*$AL6</f>
         <v>0.8011854290445144</v>
       </c>
@@ -2045,10 +2125,10 @@
         <f t="shared" ref="AG6:AG12" si="13">PV(Base_Cost_of_Equity,Holding_Period,-R6,-AC6)</f>
         <v>8.5862102417703685</v>
       </c>
-      <c r="AH6" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI6" s="50">
+      <c r="AH6" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI6" s="47">
         <v>7.18</v>
       </c>
       <c r="AJ6" s="11" t="s">
@@ -2082,16 +2162,16 @@
         <f t="shared" si="16"/>
         <v>9.6474272379442336</v>
       </c>
-      <c r="AR6" s="48" t="s">
+      <c r="AR6" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="AS6" s="50">
+      <c r="AS6" s="47">
         <v>6.5</v>
       </c>
       <c r="AT6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU6" s="33">
+      <c r="AU6" s="30">
         <f>IF($AR6="","na",AS6/(AI6/AW6)-1)</f>
         <v>-0.19428969359331472</v>
       </c>
@@ -2109,10 +2189,10 @@
       </c>
     </row>
     <row r="7" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="44" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -2124,45 +2204,45 @@
       <c r="F7" s="8">
         <v>45838</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="46">
         <v>0</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="33">
         <v>261600381459</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="33">
         <v>44432848</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="33">
         <f>3563298-4942-2461</f>
         <v>3555895</v>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="38">
         <f>30469491/40847989</f>
         <v>0.74592389358506728</v>
       </c>
-      <c r="L7" s="46">
+      <c r="L7" s="43">
         <f>589882+104928</f>
         <v>694810</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="43">
         <f>21210+21417</f>
         <v>42627</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="33">
         <v>-365879</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="39">
         <v>0.25</v>
       </c>
-      <c r="P7" s="36">
+      <c r="P7" s="33">
         <v>335577</v>
       </c>
-      <c r="Q7" s="45">
+      <c r="Q7" s="42">
         <f t="shared" ref="Q7:Q12" si="17">(L7+M7/2+N7)*(1-O7)</f>
         <v>262683.375</v>
       </c>
-      <c r="R7" s="37">
+      <c r="R7" s="34">
         <f>0.206+0.197</f>
         <v>0.40300000000000002</v>
       </c>
@@ -2170,31 +2250,31 @@
         <f>589882/25040400</f>
         <v>2.3557211546141436E-2</v>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="30">
         <f t="shared" si="0"/>
         <v>0.52658856378002616</v>
       </c>
-      <c r="U7" s="33">
+      <c r="U7" s="30">
         <f t="shared" si="1"/>
         <v>7.3872646689511365E-2</v>
       </c>
-      <c r="V7" s="34">
+      <c r="V7" s="31">
         <f t="shared" si="2"/>
         <v>1.5637305085642945E-2</v>
       </c>
-      <c r="W7" s="35">
+      <c r="W7" s="32">
         <f t="shared" si="3"/>
         <v>12.495545565884257</v>
       </c>
-      <c r="X7" s="33">
+      <c r="X7" s="30">
         <f t="shared" si="4"/>
         <v>0.37806504655949108</v>
       </c>
-      <c r="Y7" s="35">
+      <c r="Y7" s="32">
         <f t="shared" si="5"/>
         <v>13.592850974329741</v>
       </c>
-      <c r="Z7" s="35">
+      <c r="Z7" s="32">
         <f t="shared" si="6"/>
         <v>1.0041398775298411</v>
       </c>
@@ -2226,10 +2306,10 @@
         <f t="shared" si="13"/>
         <v>10.945962753461778</v>
       </c>
-      <c r="AH7" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI7" s="50">
+      <c r="AH7" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI7" s="47">
         <v>8.81</v>
       </c>
       <c r="AJ7" s="11" t="s">
@@ -2263,16 +2343,16 @@
         <f t="shared" si="16"/>
         <v>12.298834554451435</v>
       </c>
-      <c r="AR7" s="48" t="s">
+      <c r="AR7" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="AS7" s="50">
+      <c r="AS7" s="47">
         <v>8.08</v>
       </c>
       <c r="AT7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU7" s="33">
+      <c r="AU7" s="30">
         <f t="shared" ref="AU7:AU12" si="18">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
         <v>-0.18374574347332584</v>
       </c>
@@ -2290,10 +2370,10 @@
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -2305,45 +2385,45 @@
       <c r="F8" s="8">
         <v>45838</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="46">
         <v>0</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="33">
         <v>349983033873</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="33">
         <v>46855878</v>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="33">
         <f>3143100-28563-1381-300488</f>
         <v>2812668</v>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="38">
         <f>31900486/43706637</f>
         <v>0.72987738681427261</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="43">
         <f>580692+75567</f>
         <v>656259</v>
       </c>
-      <c r="M8" s="46">
+      <c r="M8" s="43">
         <f>7943+31139</f>
         <v>39082</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="33">
         <v>-390774</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="39">
         <v>0.25</v>
       </c>
-      <c r="P8" s="36">
+      <c r="P8" s="33">
         <v>282083</v>
       </c>
-      <c r="Q8" s="45">
+      <c r="Q8" s="42">
         <f t="shared" si="17"/>
         <v>213769.5</v>
       </c>
-      <c r="R8" s="37">
+      <c r="R8" s="34">
         <f>0.1255+0.1164</f>
         <v>0.2419</v>
       </c>
@@ -2351,31 +2431,31 @@
         <f>580692/23977013</f>
         <v>2.4218696465652331E-2</v>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="30">
         <f t="shared" si="0"/>
         <v>0.59545697659003538</v>
       </c>
-      <c r="U8" s="33">
+      <c r="U8" s="30">
         <f t="shared" si="1"/>
         <v>7.6002393457030831E-2</v>
       </c>
-      <c r="V8" s="34">
+      <c r="V8" s="31">
         <f t="shared" si="2"/>
         <v>1.400590551307138E-2</v>
       </c>
-      <c r="W8" s="35">
+      <c r="W8" s="32">
         <f t="shared" si="3"/>
         <v>16.658872643340771</v>
       </c>
-      <c r="X8" s="33">
+      <c r="X8" s="30">
         <f t="shared" si="4"/>
         <v>0.32573953271497991</v>
       </c>
-      <c r="Y8" s="35">
+      <c r="Y8" s="32">
         <f t="shared" si="5"/>
         <v>8.0365838562924345</v>
       </c>
-      <c r="Z8" s="35">
+      <c r="Z8" s="32">
         <f t="shared" si="6"/>
         <v>0.61079960829635971</v>
       </c>
@@ -2407,10 +2487,10 @@
         <f t="shared" si="13"/>
         <v>6.712372290957056</v>
       </c>
-      <c r="AH8" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI8" s="50">
+      <c r="AH8" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI8" s="47">
         <v>6.61</v>
       </c>
       <c r="AJ8" s="11" t="s">
@@ -2444,16 +2524,16 @@
         <f t="shared" si="16"/>
         <v>7.5419913381539958</v>
       </c>
-      <c r="AR8" s="48" t="s">
+      <c r="AR8" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="AS8" s="50">
+      <c r="AS8" s="47">
         <v>5.54</v>
       </c>
       <c r="AT8" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU8" s="33">
+      <c r="AU8" s="30">
         <f t="shared" si="18"/>
         <v>-0.25406959152798791</v>
       </c>
@@ -2471,10 +2551,10 @@
       </c>
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="44" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -2486,45 +2566,45 @@
       <c r="F9" s="8">
         <v>45838</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="46">
         <v>0</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="33">
         <v>322212411814</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="33">
         <v>36790613</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="33">
         <f>2987590-29158-2795-395040</f>
         <v>2560597</v>
       </c>
-      <c r="K9" s="41">
+      <c r="K9" s="38">
         <f>25638312/33664948</f>
         <v>0.76157289772139258</v>
       </c>
-      <c r="L9" s="46">
+      <c r="L9" s="43">
         <f>448934+76590</f>
         <v>525524</v>
       </c>
-      <c r="M9" s="46">
+      <c r="M9" s="43">
         <f>52049+41453</f>
         <v>93502</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="33">
         <v>-337627</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="39">
         <v>0.25</v>
       </c>
-      <c r="P9" s="36">
+      <c r="P9" s="33">
         <v>252719</v>
       </c>
-      <c r="Q9" s="45">
+      <c r="Q9" s="42">
         <f t="shared" si="17"/>
         <v>175986</v>
       </c>
-      <c r="R9" s="37">
+      <c r="R9" s="34">
         <f>0.1216+0.1208</f>
         <v>0.2424</v>
       </c>
@@ -2532,31 +2612,31 @@
         <f>448934/21055282</f>
         <v>2.1321680707007393E-2</v>
       </c>
-      <c r="T9" s="33">
+      <c r="T9" s="30">
         <f t="shared" si="0"/>
         <v>0.64245781353468157</v>
       </c>
-      <c r="U9" s="33">
+      <c r="U9" s="30">
         <f t="shared" si="1"/>
         <v>6.8728503548195985E-2</v>
       </c>
-      <c r="V9" s="34">
+      <c r="V9" s="31">
         <f t="shared" si="2"/>
         <v>1.4284187110445809E-2</v>
       </c>
-      <c r="W9" s="35">
+      <c r="W9" s="32">
         <f t="shared" si="3"/>
         <v>14.367982544695632</v>
       </c>
-      <c r="X9" s="33">
+      <c r="X9" s="30">
         <f t="shared" si="4"/>
         <v>0.33487718924349791</v>
       </c>
-      <c r="Y9" s="35">
+      <c r="Y9" s="32">
         <f t="shared" si="5"/>
         <v>7.9469222975747051</v>
       </c>
-      <c r="Z9" s="35">
+      <c r="Z9" s="32">
         <f t="shared" si="6"/>
         <v>0.54618007732610097</v>
       </c>
@@ -2588,10 +2668,10 @@
         <f t="shared" si="13"/>
         <v>5.864892240591038</v>
       </c>
-      <c r="AH9" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="AI9" s="50">
+      <c r="AH9" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI9" s="47">
         <v>5.34</v>
       </c>
       <c r="AJ9" s="11" t="s">
@@ -2625,16 +2705,16 @@
         <f t="shared" si="16"/>
         <v>6.5897665624618407</v>
       </c>
-      <c r="AR9" s="48" t="s">
+      <c r="AR9" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="AS9" s="50">
+      <c r="AS9" s="47">
         <v>4.72</v>
       </c>
       <c r="AT9" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU9" s="33">
+      <c r="AU9" s="30">
         <f t="shared" si="18"/>
         <v>-0.21333333333333337</v>
       </c>
@@ -2652,10 +2732,10 @@
       </c>
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="44" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -2667,76 +2747,76 @@
       <c r="F10" s="8">
         <v>45838</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="46">
         <v>0</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="33">
         <v>21162855196</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="33">
         <v>10614376</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="33">
         <f>881747-1054-532-78891</f>
         <v>801270</v>
       </c>
-      <c r="K10" s="41">
+      <c r="K10" s="38">
         <f>5964497/9720864</f>
         <v>0.6135768384374064</v>
       </c>
-      <c r="L10" s="46">
+      <c r="L10" s="43">
         <f>148107+24096+661</f>
         <v>172864</v>
       </c>
-      <c r="M10" s="46">
+      <c r="M10" s="43">
         <f>503+36202</f>
         <v>36705</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="33">
         <v>-125029</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="39">
         <v>0.25</v>
       </c>
-      <c r="P10" s="36">
+      <c r="P10" s="33">
         <v>77205</v>
       </c>
-      <c r="Q10" s="45">
+      <c r="Q10" s="42">
         <f t="shared" si="17"/>
         <v>49640.625</v>
       </c>
-      <c r="R10" s="37">
+      <c r="R10" s="34">
         <v>1.06</v>
       </c>
       <c r="S10" s="10">
         <f>148107/5608859</f>
         <v>2.6405905372197804E-2</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10" s="30">
         <f t="shared" si="0"/>
         <v>0.72327957238059981</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10" s="30">
         <f t="shared" si="1"/>
         <v>6.195243176457374E-2</v>
       </c>
-      <c r="V10" s="34">
+      <c r="V10" s="31">
         <f t="shared" si="2"/>
         <v>1.6285837245637425E-2</v>
       </c>
-      <c r="W10" s="35">
+      <c r="W10" s="32">
         <f t="shared" si="3"/>
         <v>13.246940481984849</v>
       </c>
-      <c r="X10" s="33">
+      <c r="X10" s="30">
         <f t="shared" si="4"/>
         <v>0.28716577772121438</v>
       </c>
-      <c r="Y10" s="35">
+      <c r="Y10" s="32">
         <f t="shared" si="5"/>
         <v>37.862093398033004</v>
       </c>
-      <c r="Z10" s="35">
+      <c r="Z10" s="32">
         <f t="shared" si="6"/>
         <v>2.3456487577055571</v>
       </c>
@@ -2768,10 +2848,10 @@
         <f t="shared" si="13"/>
         <v>24.228568841811072</v>
       </c>
-      <c r="AH10" s="48" t="s">
+      <c r="AH10" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="AI10" s="50">
+      <c r="AI10" s="47">
         <v>18.59</v>
       </c>
       <c r="AJ10" s="11" t="s">
@@ -2805,19 +2885,19 @@
         <f t="shared" si="16"/>
         <v>na</v>
       </c>
-      <c r="AR10" s="48"/>
-      <c r="AS10" s="50"/>
+      <c r="AR10" s="45"/>
+      <c r="AS10" s="47"/>
       <c r="AT10" s="11"/>
-      <c r="AU10" s="33"/>
+      <c r="AU10" s="30"/>
       <c r="AV10" s="7"/>
       <c r="AW10" s="7"/>
       <c r="AX10" s="5"/>
     </row>
     <row r="11" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="44" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -2829,45 +2909,45 @@
       <c r="F11" s="8">
         <v>45838</v>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="46">
         <v>0</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="33">
         <v>120095053492</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="33">
         <v>18190521</v>
       </c>
-      <c r="J11" s="36">
+      <c r="J11" s="33">
         <f>1138639-7832</f>
         <v>1130807</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="38">
         <f>16108809/17049715</f>
         <v>0.94481397489635455</v>
       </c>
-      <c r="L11" s="46">
+      <c r="L11" s="43">
         <f>286123+25282</f>
         <v>311405</v>
       </c>
-      <c r="M11" s="46">
+      <c r="M11" s="43">
         <f>917+31715</f>
         <v>32632</v>
       </c>
-      <c r="N11" s="36">
+      <c r="N11" s="33">
         <v>-255176</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="39">
         <v>0.25</v>
       </c>
-      <c r="P11" s="36">
+      <c r="P11" s="33">
         <v>86479</v>
       </c>
-      <c r="Q11" s="45">
+      <c r="Q11" s="42">
         <f t="shared" si="17"/>
         <v>54408.75</v>
       </c>
-      <c r="R11" s="37">
+      <c r="R11" s="34">
         <f>0.1139 +0.1477</f>
         <v>0.2616</v>
       </c>
@@ -2875,31 +2955,31 @@
         <f>286123/8684144</f>
         <v>3.2947749369425475E-2</v>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="30">
         <f t="shared" si="0"/>
         <v>0.81943449848268335</v>
       </c>
-      <c r="U11" s="33">
+      <c r="U11" s="30">
         <f t="shared" si="1"/>
         <v>4.8114974527041304E-2</v>
       </c>
-      <c r="V11" s="34">
+      <c r="V11" s="31">
         <f t="shared" si="2"/>
         <v>1.7119080866347919E-2</v>
       </c>
-      <c r="W11" s="35">
+      <c r="W11" s="32">
         <f t="shared" si="3"/>
         <v>16.086318001215062</v>
       </c>
-      <c r="X11" s="33">
+      <c r="X11" s="30">
         <f t="shared" si="4"/>
         <v>0.17472021964965237</v>
       </c>
-      <c r="Y11" s="35">
+      <c r="Y11" s="32">
         <f t="shared" si="5"/>
         <v>9.4159331889162896</v>
       </c>
-      <c r="Z11" s="35">
+      <c r="Z11" s="32">
         <f t="shared" si="6"/>
         <v>0.45304738553303009</v>
       </c>
@@ -2931,10 +3011,10 @@
         <f t="shared" si="13"/>
         <v>4.259894726825121</v>
       </c>
-      <c r="AH11" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI11" s="50">
+      <c r="AH11" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI11" s="47">
         <v>5.1100000000000003</v>
       </c>
       <c r="AJ11" s="11" t="s">
@@ -2968,16 +3048,16 @@
         <f t="shared" si="16"/>
         <v>4.7863985694664279</v>
       </c>
-      <c r="AR11" s="48" t="s">
+      <c r="AR11" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="AS11" s="50">
+      <c r="AS11" s="47">
         <v>5.09</v>
       </c>
       <c r="AT11" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU11" s="33">
+      <c r="AU11" s="30">
         <f t="shared" si="18"/>
         <v>-0.11348336594911945</v>
       </c>
@@ -2995,10 +3075,10 @@
       </c>
     </row>
     <row r="12" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="44" t="s">
         <v>115</v>
       </c>
       <c r="D12" s="9" t="s">
@@ -3010,76 +3090,76 @@
       <c r="F12" s="8">
         <v>45838</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="46">
         <v>0</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="33">
         <v>25219845601</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="33">
         <v>12657151</v>
       </c>
-      <c r="J12" s="36">
+      <c r="J12" s="33">
         <f>1289233-6153-9954-47907</f>
         <v>1225219</v>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="38">
         <f>9509526/11360291</f>
         <v>0.83708471904460902</v>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="43">
         <f>211277+72094</f>
         <v>283371</v>
       </c>
-      <c r="M12" s="46">
+      <c r="M12" s="43">
         <f>14126+29880</f>
         <v>44006</v>
       </c>
-      <c r="N12" s="36">
+      <c r="N12" s="33">
         <v>-158469</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="39">
         <v>0.25</v>
       </c>
-      <c r="P12" s="36">
+      <c r="P12" s="33">
         <v>149559</v>
       </c>
-      <c r="Q12" s="45">
+      <c r="Q12" s="42">
         <f t="shared" si="17"/>
         <v>110178.75</v>
       </c>
-      <c r="R12" s="37">
+      <c r="R12" s="34">
         <v>2</v>
       </c>
       <c r="S12" s="10">
         <f>211277/6300684</f>
         <v>3.3532391086428075E-2</v>
       </c>
-      <c r="T12" s="33">
+      <c r="T12" s="30">
         <f>-N12/L12</f>
         <v>0.55922800851180965</v>
       </c>
-      <c r="U12" s="33">
+      <c r="U12" s="30">
         <f t="shared" si="1"/>
         <v>8.9925760211031658E-2</v>
       </c>
-      <c r="V12" s="34">
+      <c r="V12" s="31">
         <f t="shared" si="2"/>
         <v>2.2388213587718121E-2</v>
       </c>
-      <c r="W12" s="35">
+      <c r="W12" s="32">
         <f t="shared" si="3"/>
         <v>10.33052131904582</v>
       </c>
-      <c r="X12" s="33">
+      <c r="X12" s="30">
         <f t="shared" ref="X12" si="20">Q12/L12</f>
         <v>0.38881448701525562</v>
       </c>
-      <c r="Y12" s="35">
+      <c r="Y12" s="32">
         <f t="shared" si="5"/>
         <v>48.581542463979972</v>
       </c>
-      <c r="Z12" s="35">
+      <c r="Z12" s="32">
         <f t="shared" si="6"/>
         <v>4.368732138297915</v>
       </c>
@@ -3111,10 +3191,10 @@
         <f t="shared" si="13"/>
         <v>51.11974717559962</v>
       </c>
-      <c r="AH12" s="48" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI12" s="50">
+      <c r="AH12" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="AI12" s="47">
         <v>38.99</v>
       </c>
       <c r="AJ12" s="11" t="s">
@@ -3148,16 +3228,16 @@
         <f t="shared" si="16"/>
         <v>57.437918174831033</v>
       </c>
-      <c r="AR12" s="48" t="s">
+      <c r="AR12" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="AS12" s="50">
+      <c r="AS12" s="47">
         <v>49.62</v>
       </c>
       <c r="AT12" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU12" s="33">
+      <c r="AU12" s="30">
         <f t="shared" si="18"/>
         <v>0.13264426776096427</v>
       </c>
@@ -3186,6 +3266,46 @@
     <mergeCell ref="L3:R3"/>
     <mergeCell ref="S3:X3"/>
   </mergeCells>
+  <conditionalFormatting sqref="AD6:AD1048576">
+    <cfRule type="expression" dxfId="8" priority="8">
+      <formula>AI6&lt;AD6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE6:AE1048576">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>AI6&lt;AE6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF6:AF1048576">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>AF6&lt;AI6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG6:AG1048576">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>AG6&lt;AI6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN6:AN1048576">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>AS6&lt;AN6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO6:AO1048576">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>AS6&lt;AO6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP6:AP1048576">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AP6&lt;AS6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ6:AQ1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AQ6&lt;AS6</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="17" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4327C7F-B691-4100-B623-428CC17DAB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F56FD31-B9C9-402D-860C-D0BBF480498F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,7 +617,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,12 +644,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -669,6 +663,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,7 +747,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -781,26 +787,26 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -812,12 +818,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,10 +844,10 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -866,6 +866,33 @@
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -875,49 +902,34 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -926,7 +938,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{32ADA8AA-F280-4250-ABBF-7E6B9CB799DC}"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -966,27 +978,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1426,7 +1417,7 @@
       <c r="B12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="34">
         <v>7.8</v>
       </c>
       <c r="D12" s="1"/>
@@ -1435,7 +1426,7 @@
       <c r="B13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="34">
         <v>0.89</v>
       </c>
       <c r="D13" s="1"/>
@@ -1444,14 +1435,14 @@
       <c r="B14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="35">
         <v>1000000</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
-      <c r="C15" s="35"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="1"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.45">
@@ -1627,391 +1618,391 @@
       <c r="AX2" s="2"/>
     </row>
     <row r="3" spans="2:50" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="60" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="61" t="s">
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="51" t="s">
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="52" t="s">
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="64" t="s">
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="AE3" s="64" t="s">
+      <c r="AE3" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="AF3" s="64" t="s">
+      <c r="AF3" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="AG3" s="64" t="s">
+      <c r="AG3" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="AH3" s="53" t="s">
+      <c r="AH3" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="64" t="s">
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59"/>
+      <c r="AN3" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="AO3" s="64" t="s">
+      <c r="AO3" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="AP3" s="64" t="s">
+      <c r="AP3" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="AQ3" s="64" t="s">
+      <c r="AQ3" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="AR3" s="48" t="s">
+      <c r="AR3" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="AS3" s="49"/>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="49"/>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="50"/>
+      <c r="AS3" s="64"/>
+      <c r="AT3" s="64"/>
+      <c r="AU3" s="64"/>
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="64"/>
+      <c r="AX3" s="65"/>
     </row>
     <row r="4" spans="2:50" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J4" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="L4" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="N4" s="40" t="s">
+      <c r="N4" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="O4" s="40" t="s">
+      <c r="O4" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="P4" s="40" t="s">
+      <c r="P4" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="Q4" s="40" t="s">
+      <c r="Q4" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="R4" s="40" t="s">
+      <c r="R4" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="24" t="s">
+      <c r="S4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="24" t="s">
+      <c r="T4" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="U4" s="24" t="s">
+      <c r="U4" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="V4" s="24" t="s">
+      <c r="V4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="W4" s="24" t="s">
+      <c r="W4" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="X4" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="Y4" s="21" t="s">
+      <c r="Y4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="Z4" s="21" t="s">
+      <c r="Z4" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="AA4" s="21" t="s">
+      <c r="AA4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="AB4" s="19" t="s">
+      <c r="AB4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="AC4" s="19" t="s">
+      <c r="AC4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="AD4" s="24" t="s">
+      <c r="AD4" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="AE4" s="24" t="s">
+      <c r="AE4" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="AF4" s="24" t="s">
+      <c r="AF4" s="60" t="s">
         <v>91</v>
       </c>
-      <c r="AG4" s="24" t="s">
+      <c r="AG4" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="AH4" s="17" t="s">
+      <c r="AH4" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="AI4" s="17" t="s">
+      <c r="AI4" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="AJ4" s="17" t="s">
+      <c r="AJ4" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="AK4" s="17" t="s">
+      <c r="AK4" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="AL4" s="17" t="s">
+      <c r="AL4" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="AM4" s="17" t="s">
+      <c r="AM4" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="AN4" s="24" t="s">
+      <c r="AN4" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="AO4" s="24" t="s">
+      <c r="AO4" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="AP4" s="24" t="s">
+      <c r="AP4" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="AQ4" s="24" t="s">
+      <c r="AQ4" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="AR4" s="17" t="s">
+      <c r="AR4" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AS4" s="17" t="s">
+      <c r="AS4" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="AT4" s="17" t="s">
+      <c r="AT4" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="AU4" s="17" t="s">
+      <c r="AU4" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="AV4" s="17" t="s">
+      <c r="AV4" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="AW4" s="17" t="s">
+      <c r="AW4" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="AX4" s="17" t="s">
+      <c r="AX4" s="66" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="M5" s="41" t="s">
+      <c r="M5" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="O5" s="41" t="s">
+      <c r="O5" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="P5" s="41" t="s">
+      <c r="P5" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="Q5" s="41" t="s">
+      <c r="Q5" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="R5" s="41" t="s">
+      <c r="R5" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="U5" s="25" t="s">
+      <c r="U5" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="25" t="s">
+      <c r="W5" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="X5" s="25" t="s">
+      <c r="X5" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="Y5" s="22" t="s">
+      <c r="Y5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Z5" s="23" t="s">
+      <c r="Z5" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AA5" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="AB5" s="20" t="s">
+      <c r="AB5" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="AC5" s="20" t="s">
+      <c r="AC5" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="AD5" s="65" t="s">
+      <c r="AD5" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="AE5" s="65" t="s">
+      <c r="AE5" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="AF5" s="65" t="s">
+      <c r="AF5" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="AG5" s="65" t="s">
+      <c r="AG5" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="AH5" s="18" t="s">
+      <c r="AH5" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="AI5" s="18" t="s">
+      <c r="AI5" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="AJ5" s="18" t="s">
+      <c r="AJ5" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="18" t="s">
+      <c r="AK5" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="AL5" s="18" t="s">
+      <c r="AL5" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="AM5" s="18" t="s">
+      <c r="AM5" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="AN5" s="65" t="s">
+      <c r="AN5" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="AO5" s="65" t="s">
+      <c r="AO5" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="AP5" s="65" t="s">
+      <c r="AP5" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AQ5" s="65" t="s">
+      <c r="AQ5" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AR5" s="18" t="s">
+      <c r="AR5" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="AS5" s="18" t="s">
+      <c r="AS5" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="AT5" s="18" t="s">
+      <c r="AT5" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="AU5" s="18" t="s">
+      <c r="AU5" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="AV5" s="18" t="s">
+      <c r="AV5" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="AW5" s="18" t="s">
+      <c r="AW5" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="AX5" s="18" t="s">
+      <c r="AX5" s="67" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="42" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -2023,45 +2014,45 @@
       <c r="F6" s="8">
         <v>45838</v>
       </c>
-      <c r="G6" s="46">
+      <c r="G6" s="44">
         <v>0</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="31">
         <v>356406257089</v>
       </c>
-      <c r="I6" s="33">
+      <c r="I6" s="31">
         <v>52317931</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="31">
         <f>4114692-23118-19420-59031</f>
         <v>4013123</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="36">
         <f>36904556/48179055</f>
         <v>0.76598754375734435</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="41">
         <f>637405+109397</f>
         <v>746802</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="41">
         <f>28762+40930</f>
         <v>69692</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="31">
         <v>-400918</v>
       </c>
-      <c r="O6" s="39">
+      <c r="O6" s="37">
         <v>0.25</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="31">
         <v>366946</v>
       </c>
-      <c r="Q6" s="42">
+      <c r="Q6" s="40">
         <f>(L6+M6/2+N6)*(1-O6)</f>
         <v>285547.5</v>
       </c>
-      <c r="R6" s="34">
+      <c r="R6" s="32">
         <f>0.1646+0.1434</f>
         <v>0.308</v>
       </c>
@@ -2069,31 +2060,31 @@
         <f>637405/27613781</f>
         <v>2.3082858519085089E-2</v>
       </c>
-      <c r="T6" s="30">
+      <c r="T6" s="28">
         <f t="shared" ref="T6:T11" si="0">-N6/L6</f>
         <v>0.53684644658155711</v>
       </c>
-      <c r="U6" s="30">
+      <c r="U6" s="28">
         <f t="shared" ref="U6:U12" si="1">Q6/J6</f>
         <v>7.115343835710991E-2</v>
       </c>
-      <c r="V6" s="31">
+      <c r="V6" s="29">
         <f t="shared" ref="V6:V12" si="2">L6/I6</f>
         <v>1.4274303010950491E-2</v>
       </c>
-      <c r="W6" s="32">
+      <c r="W6" s="30">
         <f t="shared" ref="W6:W12" si="3">I6/J6</f>
         <v>13.036712555284252</v>
       </c>
-      <c r="X6" s="30">
+      <c r="X6" s="28">
         <f t="shared" ref="X6:X11" si="4">Q6/L6</f>
         <v>0.38236038468027672</v>
       </c>
-      <c r="Y6" s="32">
+      <c r="Y6" s="30">
         <f t="shared" ref="Y6:Y12" si="5">J6/(H6/1000000)*$AL6</f>
         <v>11.259967860210329</v>
       </c>
-      <c r="Z6" s="32">
+      <c r="Z6" s="30">
         <f t="shared" ref="Z6:Z12" si="6">Q6/(H6/1000000)*$AL6</f>
         <v>0.8011854290445144</v>
       </c>
@@ -2125,11 +2116,11 @@
         <f t="shared" ref="AG6:AG12" si="13">PV(Base_Cost_of_Equity,Holding_Period,-R6,-AC6)</f>
         <v>8.5862102417703685</v>
       </c>
-      <c r="AH6" s="45" t="s">
+      <c r="AH6" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AI6" s="47">
-        <v>7.18</v>
+      <c r="AI6" s="45">
+        <v>7.11</v>
       </c>
       <c r="AJ6" s="11" t="s">
         <v>3</v>
@@ -2144,7 +2135,7 @@
       </c>
       <c r="AM6" s="5">
         <f t="shared" ref="AM6:AM12" si="15">R6/AI6</f>
-        <v>4.2896935933147633E-2</v>
+        <v>4.3319268635724328E-2</v>
       </c>
       <c r="AN6" s="7">
         <f t="shared" ref="AN6:AQ12" si="16">IF($AR6="","na",AD6/$AW6)</f>
@@ -2162,18 +2153,18 @@
         <f t="shared" si="16"/>
         <v>9.6474272379442336</v>
       </c>
-      <c r="AR6" s="45" t="s">
+      <c r="AR6" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="AS6" s="47">
-        <v>6.5</v>
+      <c r="AS6" s="45">
+        <v>6.55</v>
       </c>
       <c r="AT6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU6" s="30">
+      <c r="AU6" s="28">
         <f>IF($AR6="","na",AS6/(AI6/AW6)-1)</f>
-        <v>-0.19428969359331472</v>
+        <v>-0.18009845288326309</v>
       </c>
       <c r="AV6" s="7" t="str">
         <f>IF($AR6="","na",AT6&amp;D6)</f>
@@ -2185,14 +2176,14 @@
       </c>
       <c r="AX6" s="5">
         <f>IF($AR6="","na",(R6/AW6)/AS6)</f>
-        <v>5.3241140881590314E-2</v>
+        <v>5.2834719958830087E-2</v>
       </c>
     </row>
     <row r="7" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="42" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -2204,45 +2195,45 @@
       <c r="F7" s="8">
         <v>45838</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="44">
         <v>0</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="31">
         <v>261600381459</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="31">
         <v>44432848</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="31">
         <f>3563298-4942-2461</f>
         <v>3555895</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="36">
         <f>30469491/40847989</f>
         <v>0.74592389358506728</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="41">
         <f>589882+104928</f>
         <v>694810</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="41">
         <f>21210+21417</f>
         <v>42627</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="31">
         <v>-365879</v>
       </c>
-      <c r="O7" s="39">
+      <c r="O7" s="37">
         <v>0.25</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="31">
         <v>335577</v>
       </c>
-      <c r="Q7" s="42">
+      <c r="Q7" s="40">
         <f t="shared" ref="Q7:Q12" si="17">(L7+M7/2+N7)*(1-O7)</f>
         <v>262683.375</v>
       </c>
-      <c r="R7" s="34">
+      <c r="R7" s="32">
         <f>0.206+0.197</f>
         <v>0.40300000000000002</v>
       </c>
@@ -2250,31 +2241,31 @@
         <f>589882/25040400</f>
         <v>2.3557211546141436E-2</v>
       </c>
-      <c r="T7" s="30">
+      <c r="T7" s="28">
         <f t="shared" si="0"/>
         <v>0.52658856378002616</v>
       </c>
-      <c r="U7" s="30">
+      <c r="U7" s="28">
         <f t="shared" si="1"/>
         <v>7.3872646689511365E-2</v>
       </c>
-      <c r="V7" s="31">
+      <c r="V7" s="29">
         <f t="shared" si="2"/>
         <v>1.5637305085642945E-2</v>
       </c>
-      <c r="W7" s="32">
+      <c r="W7" s="30">
         <f t="shared" si="3"/>
         <v>12.495545565884257</v>
       </c>
-      <c r="X7" s="30">
+      <c r="X7" s="28">
         <f t="shared" si="4"/>
         <v>0.37806504655949108</v>
       </c>
-      <c r="Y7" s="32">
+      <c r="Y7" s="30">
         <f t="shared" si="5"/>
         <v>13.592850974329741</v>
       </c>
-      <c r="Z7" s="32">
+      <c r="Z7" s="30">
         <f t="shared" si="6"/>
         <v>1.0041398775298411</v>
       </c>
@@ -2306,11 +2297,11 @@
         <f t="shared" si="13"/>
         <v>10.945962753461778</v>
       </c>
-      <c r="AH7" s="45" t="s">
+      <c r="AH7" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="AI7" s="47">
-        <v>8.81</v>
+      <c r="AI7" s="45">
+        <v>8.6999999999999993</v>
       </c>
       <c r="AJ7" s="11" t="s">
         <v>3</v>
@@ -2325,7 +2316,7 @@
       </c>
       <c r="AM7" s="5">
         <f t="shared" si="15"/>
-        <v>4.5743473325766178E-2</v>
+        <v>4.6321839080459774E-2</v>
       </c>
       <c r="AN7" s="7">
         <f t="shared" si="16"/>
@@ -2343,18 +2334,18 @@
         <f t="shared" si="16"/>
         <v>12.298834554451435</v>
       </c>
-      <c r="AR7" s="45" t="s">
+      <c r="AR7" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="AS7" s="47">
-        <v>8.08</v>
+      <c r="AS7" s="45">
+        <v>8.17</v>
       </c>
       <c r="AT7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU7" s="30">
+      <c r="AU7" s="28">
         <f t="shared" ref="AU7:AU12" si="18">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
-        <v>-0.18374574347332584</v>
+        <v>-0.16421839080459755</v>
       </c>
       <c r="AV7" s="7" t="str">
         <f t="shared" ref="AV7:AV12" si="19">IF($AR7="","na",AT7&amp;D7)</f>
@@ -2366,14 +2357,14 @@
       </c>
       <c r="AX7" s="5">
         <f>IF($AR7="","na",(R7/AW7)/AS7)</f>
-        <v>5.6040716431193682E-2</v>
+        <v>5.5423376837704402E-2</v>
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="42" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -2385,45 +2376,45 @@
       <c r="F8" s="8">
         <v>45838</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="44">
         <v>0</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="31">
         <v>349983033873</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="31">
         <v>46855878</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="31">
         <f>3143100-28563-1381-300488</f>
         <v>2812668</v>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="36">
         <f>31900486/43706637</f>
         <v>0.72987738681427261</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="41">
         <f>580692+75567</f>
         <v>656259</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="41">
         <f>7943+31139</f>
         <v>39082</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="31">
         <v>-390774</v>
       </c>
-      <c r="O8" s="39">
+      <c r="O8" s="37">
         <v>0.25</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="31">
         <v>282083</v>
       </c>
-      <c r="Q8" s="42">
+      <c r="Q8" s="40">
         <f t="shared" si="17"/>
         <v>213769.5</v>
       </c>
-      <c r="R8" s="34">
+      <c r="R8" s="32">
         <f>0.1255+0.1164</f>
         <v>0.2419</v>
       </c>
@@ -2431,31 +2422,31 @@
         <f>580692/23977013</f>
         <v>2.4218696465652331E-2</v>
       </c>
-      <c r="T8" s="30">
+      <c r="T8" s="28">
         <f t="shared" si="0"/>
         <v>0.59545697659003538</v>
       </c>
-      <c r="U8" s="30">
+      <c r="U8" s="28">
         <f t="shared" si="1"/>
         <v>7.6002393457030831E-2</v>
       </c>
-      <c r="V8" s="31">
+      <c r="V8" s="29">
         <f t="shared" si="2"/>
         <v>1.400590551307138E-2</v>
       </c>
-      <c r="W8" s="32">
+      <c r="W8" s="30">
         <f t="shared" si="3"/>
         <v>16.658872643340771</v>
       </c>
-      <c r="X8" s="30">
+      <c r="X8" s="28">
         <f t="shared" si="4"/>
         <v>0.32573953271497991</v>
       </c>
-      <c r="Y8" s="32">
+      <c r="Y8" s="30">
         <f t="shared" si="5"/>
         <v>8.0365838562924345</v>
       </c>
-      <c r="Z8" s="32">
+      <c r="Z8" s="30">
         <f t="shared" si="6"/>
         <v>0.61079960829635971</v>
       </c>
@@ -2487,11 +2478,11 @@
         <f t="shared" si="13"/>
         <v>6.712372290957056</v>
       </c>
-      <c r="AH8" s="45" t="s">
+      <c r="AH8" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AI8" s="47">
-        <v>6.61</v>
+      <c r="AI8" s="45">
+        <v>6.51</v>
       </c>
       <c r="AJ8" s="11" t="s">
         <v>3</v>
@@ -2506,7 +2497,7 @@
       </c>
       <c r="AM8" s="5">
         <f t="shared" si="15"/>
-        <v>3.6596066565809382E-2</v>
+        <v>3.7158218125960062E-2</v>
       </c>
       <c r="AN8" s="7">
         <f t="shared" si="16"/>
@@ -2524,18 +2515,18 @@
         <f t="shared" si="16"/>
         <v>7.5419913381539958</v>
       </c>
-      <c r="AR8" s="45" t="s">
+      <c r="AR8" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="AS8" s="47">
-        <v>5.54</v>
+      <c r="AS8" s="45">
+        <v>5.51</v>
       </c>
       <c r="AT8" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU8" s="30">
+      <c r="AU8" s="28">
         <f t="shared" si="18"/>
-        <v>-0.25406959152798791</v>
+        <v>-0.24671274961597545</v>
       </c>
       <c r="AV8" s="7" t="str">
         <f t="shared" si="19"/>
@@ -2547,14 +2538,14 @@
       </c>
       <c r="AX8" s="5">
         <f>IF($AR8="","na",(R8/AW8)/AS8)</f>
-        <v>4.9060966211008805E-2</v>
+        <v>4.9328085809253859E-2</v>
       </c>
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="42" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -2566,45 +2557,45 @@
       <c r="F9" s="8">
         <v>45838</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="44">
         <v>0</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="31">
         <v>322212411814</v>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="31">
         <v>36790613</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="31">
         <f>2987590-29158-2795-395040</f>
         <v>2560597</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="36">
         <f>25638312/33664948</f>
         <v>0.76157289772139258</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="41">
         <f>448934+76590</f>
         <v>525524</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="41">
         <f>52049+41453</f>
         <v>93502</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="31">
         <v>-337627</v>
       </c>
-      <c r="O9" s="39">
+      <c r="O9" s="37">
         <v>0.25</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="31">
         <v>252719</v>
       </c>
-      <c r="Q9" s="42">
+      <c r="Q9" s="40">
         <f t="shared" si="17"/>
         <v>175986</v>
       </c>
-      <c r="R9" s="34">
+      <c r="R9" s="32">
         <f>0.1216+0.1208</f>
         <v>0.2424</v>
       </c>
@@ -2612,31 +2603,31 @@
         <f>448934/21055282</f>
         <v>2.1321680707007393E-2</v>
       </c>
-      <c r="T9" s="30">
+      <c r="T9" s="28">
         <f t="shared" si="0"/>
         <v>0.64245781353468157</v>
       </c>
-      <c r="U9" s="30">
+      <c r="U9" s="28">
         <f t="shared" si="1"/>
         <v>6.8728503548195985E-2</v>
       </c>
-      <c r="V9" s="31">
+      <c r="V9" s="29">
         <f t="shared" si="2"/>
         <v>1.4284187110445809E-2</v>
       </c>
-      <c r="W9" s="32">
+      <c r="W9" s="30">
         <f t="shared" si="3"/>
         <v>14.367982544695632</v>
       </c>
-      <c r="X9" s="30">
+      <c r="X9" s="28">
         <f t="shared" si="4"/>
         <v>0.33487718924349791</v>
       </c>
-      <c r="Y9" s="32">
+      <c r="Y9" s="30">
         <f t="shared" si="5"/>
         <v>7.9469222975747051</v>
       </c>
-      <c r="Z9" s="32">
+      <c r="Z9" s="30">
         <f t="shared" si="6"/>
         <v>0.54618007732610097</v>
       </c>
@@ -2668,11 +2659,11 @@
         <f t="shared" si="13"/>
         <v>5.864892240591038</v>
       </c>
-      <c r="AH9" s="45" t="s">
+      <c r="AH9" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="AI9" s="47">
-        <v>5.34</v>
+      <c r="AI9" s="45">
+        <v>5.31</v>
       </c>
       <c r="AJ9" s="11" t="s">
         <v>3</v>
@@ -2687,7 +2678,7 @@
       </c>
       <c r="AM9" s="5">
         <f t="shared" si="15"/>
-        <v>4.5393258426966294E-2</v>
+        <v>4.5649717514124298E-2</v>
       </c>
       <c r="AN9" s="7">
         <f t="shared" si="16"/>
@@ -2705,18 +2696,18 @@
         <f t="shared" si="16"/>
         <v>6.5897665624618407</v>
       </c>
-      <c r="AR9" s="45" t="s">
+      <c r="AR9" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="AS9" s="47">
-        <v>4.72</v>
+      <c r="AS9" s="45">
+        <v>4.74</v>
       </c>
       <c r="AT9" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU9" s="30">
+      <c r="AU9" s="28">
         <f t="shared" si="18"/>
-        <v>-0.21333333333333337</v>
+        <v>-0.20553672316384164</v>
       </c>
       <c r="AV9" s="7" t="str">
         <f t="shared" si="19"/>
@@ -2728,14 +2719,14 @@
       </c>
       <c r="AX9" s="5">
         <f>IF($AR9="","na",(R9/AW9)/AS9)</f>
-        <v>5.7703294610550383E-2</v>
+        <v>5.745982079362822E-2</v>
       </c>
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="42" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -2747,76 +2738,76 @@
       <c r="F10" s="8">
         <v>45838</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="44">
         <v>0</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="31">
         <v>21162855196</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="31">
         <v>10614376</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="31">
         <f>881747-1054-532-78891</f>
         <v>801270</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="36">
         <f>5964497/9720864</f>
         <v>0.6135768384374064</v>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="41">
         <f>148107+24096+661</f>
         <v>172864</v>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="41">
         <f>503+36202</f>
         <v>36705</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="31">
         <v>-125029</v>
       </c>
-      <c r="O10" s="39">
+      <c r="O10" s="37">
         <v>0.25</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="31">
         <v>77205</v>
       </c>
-      <c r="Q10" s="42">
+      <c r="Q10" s="40">
         <f t="shared" si="17"/>
         <v>49640.625</v>
       </c>
-      <c r="R10" s="34">
+      <c r="R10" s="32">
         <v>1.06</v>
       </c>
       <c r="S10" s="10">
         <f>148107/5608859</f>
         <v>2.6405905372197804E-2</v>
       </c>
-      <c r="T10" s="30">
+      <c r="T10" s="28">
         <f t="shared" si="0"/>
         <v>0.72327957238059981</v>
       </c>
-      <c r="U10" s="30">
+      <c r="U10" s="28">
         <f t="shared" si="1"/>
         <v>6.195243176457374E-2</v>
       </c>
-      <c r="V10" s="31">
+      <c r="V10" s="29">
         <f t="shared" si="2"/>
         <v>1.6285837245637425E-2</v>
       </c>
-      <c r="W10" s="32">
+      <c r="W10" s="30">
         <f t="shared" si="3"/>
         <v>13.246940481984849</v>
       </c>
-      <c r="X10" s="30">
+      <c r="X10" s="28">
         <f t="shared" si="4"/>
         <v>0.28716577772121438</v>
       </c>
-      <c r="Y10" s="32">
+      <c r="Y10" s="30">
         <f t="shared" si="5"/>
         <v>37.862093398033004</v>
       </c>
-      <c r="Z10" s="32">
+      <c r="Z10" s="30">
         <f t="shared" si="6"/>
         <v>2.3456487577055571</v>
       </c>
@@ -2848,11 +2839,11 @@
         <f t="shared" si="13"/>
         <v>24.228568841811072</v>
       </c>
-      <c r="AH10" s="45" t="s">
+      <c r="AH10" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="AI10" s="47">
-        <v>18.59</v>
+      <c r="AI10" s="45">
+        <v>18.489999999999998</v>
       </c>
       <c r="AJ10" s="11" t="s">
         <v>3</v>
@@ -2867,7 +2858,7 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="15"/>
-        <v>5.7019903173749331E-2</v>
+        <v>5.7328285559762042E-2</v>
       </c>
       <c r="AN10" s="7" t="str">
         <f t="shared" si="16"/>
@@ -2885,19 +2876,19 @@
         <f t="shared" si="16"/>
         <v>na</v>
       </c>
-      <c r="AR10" s="45"/>
-      <c r="AS10" s="47"/>
+      <c r="AR10" s="43"/>
+      <c r="AS10" s="45"/>
       <c r="AT10" s="11"/>
-      <c r="AU10" s="30"/>
+      <c r="AU10" s="28"/>
       <c r="AV10" s="7"/>
       <c r="AW10" s="7"/>
       <c r="AX10" s="5"/>
     </row>
     <row r="11" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="42" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -2909,45 +2900,45 @@
       <c r="F11" s="8">
         <v>45838</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="44">
         <v>0</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="31">
         <v>120095053492</v>
       </c>
-      <c r="I11" s="33">
+      <c r="I11" s="31">
         <v>18190521</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="31">
         <f>1138639-7832</f>
         <v>1130807</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="36">
         <f>16108809/17049715</f>
         <v>0.94481397489635455</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="41">
         <f>286123+25282</f>
         <v>311405</v>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="41">
         <f>917+31715</f>
         <v>32632</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="31">
         <v>-255176</v>
       </c>
-      <c r="O11" s="39">
+      <c r="O11" s="37">
         <v>0.25</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="31">
         <v>86479</v>
       </c>
-      <c r="Q11" s="42">
+      <c r="Q11" s="40">
         <f t="shared" si="17"/>
         <v>54408.75</v>
       </c>
-      <c r="R11" s="34">
+      <c r="R11" s="32">
         <f>0.1139 +0.1477</f>
         <v>0.2616</v>
       </c>
@@ -2955,31 +2946,31 @@
         <f>286123/8684144</f>
         <v>3.2947749369425475E-2</v>
       </c>
-      <c r="T11" s="30">
+      <c r="T11" s="28">
         <f t="shared" si="0"/>
         <v>0.81943449848268335</v>
       </c>
-      <c r="U11" s="30">
+      <c r="U11" s="28">
         <f t="shared" si="1"/>
         <v>4.8114974527041304E-2</v>
       </c>
-      <c r="V11" s="31">
+      <c r="V11" s="29">
         <f t="shared" si="2"/>
         <v>1.7119080866347919E-2</v>
       </c>
-      <c r="W11" s="32">
+      <c r="W11" s="30">
         <f t="shared" si="3"/>
         <v>16.086318001215062</v>
       </c>
-      <c r="X11" s="30">
+      <c r="X11" s="28">
         <f t="shared" si="4"/>
         <v>0.17472021964965237</v>
       </c>
-      <c r="Y11" s="32">
+      <c r="Y11" s="30">
         <f t="shared" si="5"/>
         <v>9.4159331889162896</v>
       </c>
-      <c r="Z11" s="32">
+      <c r="Z11" s="30">
         <f t="shared" si="6"/>
         <v>0.45304738553303009</v>
       </c>
@@ -3011,11 +3002,11 @@
         <f t="shared" si="13"/>
         <v>4.259894726825121</v>
       </c>
-      <c r="AH11" s="45" t="s">
+      <c r="AH11" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="AI11" s="47">
-        <v>5.1100000000000003</v>
+      <c r="AI11" s="45">
+        <v>5.07</v>
       </c>
       <c r="AJ11" s="11" t="s">
         <v>3</v>
@@ -3030,7 +3021,7 @@
       </c>
       <c r="AM11" s="5">
         <f t="shared" si="15"/>
-        <v>5.1193737769080233E-2</v>
+        <v>5.1597633136094674E-2</v>
       </c>
       <c r="AN11" s="7">
         <f t="shared" si="16"/>
@@ -3048,18 +3039,18 @@
         <f t="shared" si="16"/>
         <v>4.7863985694664279</v>
       </c>
-      <c r="AR11" s="45" t="s">
+      <c r="AR11" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="AS11" s="47">
-        <v>5.09</v>
+      <c r="AS11" s="45">
+        <v>5.15</v>
       </c>
       <c r="AT11" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU11" s="30">
+      <c r="AU11" s="28">
         <f t="shared" si="18"/>
-        <v>-0.11348336594911945</v>
+        <v>-9.5956607495069068E-2</v>
       </c>
       <c r="AV11" s="7" t="str">
         <f t="shared" si="19"/>
@@ -3071,14 +3062,14 @@
       </c>
       <c r="AX11" s="5">
         <f>IF($AR11="","na",(R11/AW11)/AS11)</f>
-        <v>5.7747069601112554E-2</v>
+        <v>5.707428820770153E-2</v>
       </c>
     </row>
     <row r="12" spans="2:50" x14ac:dyDescent="0.45">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="42" t="s">
         <v>115</v>
       </c>
       <c r="D12" s="9" t="s">
@@ -3090,76 +3081,76 @@
       <c r="F12" s="8">
         <v>45838</v>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="44">
         <v>0</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="31">
         <v>25219845601</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="31">
         <v>12657151</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="31">
         <f>1289233-6153-9954-47907</f>
         <v>1225219</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="36">
         <f>9509526/11360291</f>
         <v>0.83708471904460902</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="41">
         <f>211277+72094</f>
         <v>283371</v>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="41">
         <f>14126+29880</f>
         <v>44006</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="31">
         <v>-158469</v>
       </c>
-      <c r="O12" s="39">
+      <c r="O12" s="37">
         <v>0.25</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="31">
         <v>149559</v>
       </c>
-      <c r="Q12" s="42">
+      <c r="Q12" s="40">
         <f t="shared" si="17"/>
         <v>110178.75</v>
       </c>
-      <c r="R12" s="34">
+      <c r="R12" s="32">
         <v>2</v>
       </c>
       <c r="S12" s="10">
         <f>211277/6300684</f>
         <v>3.3532391086428075E-2</v>
       </c>
-      <c r="T12" s="30">
+      <c r="T12" s="28">
         <f>-N12/L12</f>
         <v>0.55922800851180965</v>
       </c>
-      <c r="U12" s="30">
+      <c r="U12" s="28">
         <f t="shared" si="1"/>
         <v>8.9925760211031658E-2</v>
       </c>
-      <c r="V12" s="31">
+      <c r="V12" s="29">
         <f t="shared" si="2"/>
         <v>2.2388213587718121E-2</v>
       </c>
-      <c r="W12" s="32">
+      <c r="W12" s="30">
         <f t="shared" si="3"/>
         <v>10.33052131904582</v>
       </c>
-      <c r="X12" s="30">
+      <c r="X12" s="28">
         <f t="shared" ref="X12" si="20">Q12/L12</f>
         <v>0.38881448701525562</v>
       </c>
-      <c r="Y12" s="32">
+      <c r="Y12" s="30">
         <f t="shared" si="5"/>
         <v>48.581542463979972</v>
       </c>
-      <c r="Z12" s="32">
+      <c r="Z12" s="30">
         <f t="shared" si="6"/>
         <v>4.368732138297915</v>
       </c>
@@ -3191,11 +3182,11 @@
         <f t="shared" si="13"/>
         <v>51.11974717559962</v>
       </c>
-      <c r="AH12" s="45" t="s">
+      <c r="AH12" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="AI12" s="47">
-        <v>38.99</v>
+      <c r="AI12" s="45">
+        <v>38.71</v>
       </c>
       <c r="AJ12" s="11" t="s">
         <v>3</v>
@@ -3210,7 +3201,7 @@
       </c>
       <c r="AM12" s="5">
         <f t="shared" si="15"/>
-        <v>5.129520389843549E-2</v>
+        <v>5.1666236114699046E-2</v>
       </c>
       <c r="AN12" s="7">
         <f t="shared" si="16"/>
@@ -3228,18 +3219,18 @@
         <f t="shared" si="16"/>
         <v>57.437918174831033</v>
       </c>
-      <c r="AR12" s="45" t="s">
+      <c r="AR12" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AS12" s="47">
-        <v>49.62</v>
+      <c r="AS12" s="45">
+        <v>49.84</v>
       </c>
       <c r="AT12" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AU12" s="30">
+      <c r="AU12" s="28">
         <f t="shared" si="18"/>
-        <v>0.13264426776096427</v>
+        <v>0.14589511754068729</v>
       </c>
       <c r="AV12" s="7" t="str">
         <f t="shared" si="19"/>
@@ -3251,7 +3242,7 @@
       </c>
       <c r="AX12" s="5">
         <f>IF($AR12="","na",(R12/AW12)/AS12)</f>
-        <v>4.5288009093832231E-2</v>
+        <v>4.5088102151604234E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3267,7 +3258,7 @@
     <mergeCell ref="S3:X3"/>
   </mergeCells>
   <conditionalFormatting sqref="AD6:AD1048576">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>AI6&lt;AD6</formula>
     </cfRule>
   </conditionalFormatting>

--- a/financial_models/Bank_Monitor.xlsx
+++ b/financial_models/Bank_Monitor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F56FD31-B9C9-402D-860C-D0BBF480498F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31514EEE-A438-419A-B136-D9BF20C404D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -866,12 +866,42 @@
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -901,36 +931,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1511,10 +1511,11 @@
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="10" width="18.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="18.6640625" customWidth="1"/>
-    <col min="12" max="18" width="18.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="24" width="18.6640625" customWidth="1"/>
+    <col min="4" max="10" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="18.6640625" customWidth="1" collapsed="1"/>
+    <col min="12" max="18" width="18.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="18.6640625" customWidth="1" collapsed="1"/>
+    <col min="20" max="24" width="18.6640625" customWidth="1"/>
     <col min="25" max="27" width="18.6640625" customWidth="1" outlineLevel="1"/>
     <col min="28" max="33" width="18.796875" customWidth="1"/>
     <col min="34" max="50" width="16.59765625" customWidth="1"/>
@@ -1618,87 +1619,87 @@
       <c r="AX2" s="2"/>
     </row>
     <row r="3" spans="2:50" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="54" t="s">
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="55" t="s">
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="46" t="s">
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="47" t="s">
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="58" t="s">
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="AE3" s="58" t="s">
+      <c r="AE3" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="AF3" s="58" t="s">
+      <c r="AF3" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="AG3" s="58" t="s">
+      <c r="AG3" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="AH3" s="59" t="s">
+      <c r="AH3" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59"/>
-      <c r="AN3" s="62" t="s">
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="AO3" s="62" t="s">
+      <c r="AO3" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="AP3" s="62" t="s">
+      <c r="AP3" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AQ3" s="62" t="s">
+      <c r="AQ3" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="AR3" s="63" t="s">
+      <c r="AR3" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="AS3" s="64"/>
-      <c r="AT3" s="64"/>
-      <c r="AU3" s="64"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="64"/>
-      <c r="AX3" s="65"/>
+      <c r="AS3" s="53"/>
+      <c r="AT3" s="53"/>
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="53"/>
+      <c r="AX3" s="54"/>
     </row>
     <row r="4" spans="2:50" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="26" t="s">
@@ -1785,67 +1786,67 @@
       <c r="AC4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="AD4" s="60" t="s">
+      <c r="AD4" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="AE4" s="60" t="s">
+      <c r="AE4" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="AF4" s="60" t="s">
+      <c r="AF4" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="AG4" s="60" t="s">
+      <c r="AG4" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="AH4" s="60" t="s">
+      <c r="AH4" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="AI4" s="60" t="s">
+      <c r="AI4" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="AJ4" s="60" t="s">
+      <c r="AJ4" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="AK4" s="60" t="s">
+      <c r="AK4" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="AL4" s="60" t="s">
+      <c r="AL4" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="AM4" s="60" t="s">
+      <c r="AM4" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="AN4" s="66" t="s">
+      <c r="AN4" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="AO4" s="66" t="s">
+      <c r="AO4" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="AP4" s="66" t="s">
+      <c r="AP4" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="AQ4" s="66" t="s">
+      <c r="AQ4" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="AR4" s="66" t="s">
+      <c r="AR4" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="AS4" s="66" t="s">
+      <c r="AS4" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="AT4" s="66" t="s">
+      <c r="AT4" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="AU4" s="66" t="s">
+      <c r="AU4" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="AV4" s="66" t="s">
+      <c r="AV4" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="AW4" s="66" t="s">
+      <c r="AW4" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="AX4" s="66" t="s">
+      <c r="AX4" s="50" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1934,67 +1935,67 @@
       <c r="AC5" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="AD5" s="61" t="s">
+      <c r="AD5" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="AE5" s="61" t="s">
+      <c r="AE5" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="AF5" s="61" t="s">
+      <c r="AF5" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="AG5" s="61" t="s">
+      <c r="AG5" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="AH5" s="61" t="s">
+      <c r="AH5" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="AI5" s="61" t="s">
+      <c r="AI5" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="AJ5" s="61" t="s">
+      <c r="AJ5" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="61" t="s">
+      <c r="AK5" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="AL5" s="61" t="s">
+      <c r="AL5" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="AM5" s="61" t="s">
+      <c r="AM5" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="AN5" s="67" t="s">
+      <c r="AN5" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="AO5" s="67" t="s">
+      <c r="AO5" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="AP5" s="67" t="s">
+      <c r="AP5" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="AQ5" s="67" t="s">
+      <c r="AQ5" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="AR5" s="67" t="s">
+      <c r="AR5" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="AS5" s="67" t="s">
+      <c r="AS5" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="AT5" s="67" t="s">
+      <c r="AT5" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="AU5" s="67" t="s">
+      <c r="AU5" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="AV5" s="67" t="s">
+      <c r="AV5" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="AW5" s="67" t="s">
+      <c r="AW5" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="AX5" s="67" t="s">
+      <c r="AX5" s="51" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2120,7 +2121,7 @@
         <v>156</v>
       </c>
       <c r="AI6" s="45">
-        <v>7.11</v>
+        <v>7.35</v>
       </c>
       <c r="AJ6" s="11" t="s">
         <v>3</v>
@@ -2135,7 +2136,7 @@
       </c>
       <c r="AM6" s="5">
         <f t="shared" ref="AM6:AM12" si="15">R6/AI6</f>
-        <v>4.3319268635724328E-2</v>
+        <v>4.1904761904761903E-2</v>
       </c>
       <c r="AN6" s="7">
         <f t="shared" ref="AN6:AQ12" si="16">IF($AR6="","na",AD6/$AW6)</f>
@@ -2157,14 +2158,14 @@
         <v>147</v>
       </c>
       <c r="AS6" s="45">
-        <v>6.55</v>
+        <v>6.48</v>
       </c>
       <c r="AT6" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU6" s="28">
         <f>IF($AR6="","na",AS6/(AI6/AW6)-1)</f>
-        <v>-0.18009845288326309</v>
+        <v>-0.21534693877551014</v>
       </c>
       <c r="AV6" s="7" t="str">
         <f>IF($AR6="","na",AT6&amp;D6)</f>
@@ -2176,7 +2177,7 @@
       </c>
       <c r="AX6" s="5">
         <f>IF($AR6="","na",(R6/AW6)/AS6)</f>
-        <v>5.2834719958830087E-2</v>
+        <v>5.340546539048411E-2</v>
       </c>
     </row>
     <row r="7" spans="2:50" x14ac:dyDescent="0.45">
@@ -2301,7 +2302,7 @@
         <v>157</v>
       </c>
       <c r="AI7" s="45">
-        <v>8.6999999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AJ7" s="11" t="s">
         <v>3</v>
@@ -2316,7 +2317,7 @@
       </c>
       <c r="AM7" s="5">
         <f t="shared" si="15"/>
-        <v>4.6321839080459774E-2</v>
+        <v>4.3333333333333335E-2</v>
       </c>
       <c r="AN7" s="7">
         <f t="shared" si="16"/>
@@ -2338,14 +2339,14 @@
         <v>146</v>
       </c>
       <c r="AS7" s="45">
-        <v>8.17</v>
+        <v>8.09</v>
       </c>
       <c r="AT7" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU7" s="28">
         <f t="shared" ref="AU7:AU12" si="18">IF($AR7="","na",AS7/(AI7/AW7)-1)</f>
-        <v>-0.16421839080459755</v>
+        <v>-0.22579569892473128</v>
       </c>
       <c r="AV7" s="7" t="str">
         <f t="shared" ref="AV7:AV12" si="19">IF($AR7="","na",AT7&amp;D7)</f>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="AX7" s="5">
         <f>IF($AR7="","na",(R7/AW7)/AS7)</f>
-        <v>5.5423376837704402E-2</v>
+        <v>5.5971444841043876E-2</v>
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.45">
@@ -2482,7 +2483,7 @@
         <v>158</v>
       </c>
       <c r="AI8" s="45">
-        <v>6.51</v>
+        <v>6.73</v>
       </c>
       <c r="AJ8" s="11" t="s">
         <v>3</v>
@@ -2497,7 +2498,7 @@
       </c>
       <c r="AM8" s="5">
         <f t="shared" si="15"/>
-        <v>3.7158218125960062E-2</v>
+        <v>3.5943536404160474E-2</v>
       </c>
       <c r="AN8" s="7">
         <f t="shared" si="16"/>
@@ -2519,14 +2520,14 @@
         <v>148</v>
       </c>
       <c r="AS8" s="45">
-        <v>5.51</v>
+        <v>5.33</v>
       </c>
       <c r="AT8" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU8" s="28">
         <f t="shared" si="18"/>
-        <v>-0.24671274961597545</v>
+        <v>-0.29514115898959881</v>
       </c>
       <c r="AV8" s="7" t="str">
         <f t="shared" si="19"/>
@@ -2538,7 +2539,7 @@
       </c>
       <c r="AX8" s="5">
         <f>IF($AR8="","na",(R8/AW8)/AS8)</f>
-        <v>4.9328085809253859E-2</v>
+        <v>5.0993949870354362E-2</v>
       </c>
     </row>
     <row r="9" spans="2:50" x14ac:dyDescent="0.45">
@@ -2663,7 +2664,7 @@
         <v>159</v>
       </c>
       <c r="AI9" s="45">
-        <v>5.31</v>
+        <v>5.46</v>
       </c>
       <c r="AJ9" s="11" t="s">
         <v>3</v>
@@ -2678,7 +2679,7 @@
       </c>
       <c r="AM9" s="5">
         <f t="shared" si="15"/>
-        <v>4.5649717514124298E-2</v>
+        <v>4.4395604395604395E-2</v>
       </c>
       <c r="AN9" s="7">
         <f t="shared" si="16"/>
@@ -2700,14 +2701,14 @@
         <v>149</v>
       </c>
       <c r="AS9" s="45">
-        <v>4.74</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="AT9" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU9" s="28">
         <f t="shared" si="18"/>
-        <v>-0.20553672316384164</v>
+        <v>-0.24855311355311338</v>
       </c>
       <c r="AV9" s="7" t="str">
         <f t="shared" si="19"/>
@@ -2719,7 +2720,7 @@
       </c>
       <c r="AX9" s="5">
         <f>IF($AR9="","na",(R9/AW9)/AS9)</f>
-        <v>5.745982079362822E-2</v>
+        <v>5.9080162811669799E-2</v>
       </c>
     </row>
     <row r="10" spans="2:50" x14ac:dyDescent="0.45">
@@ -2843,7 +2844,7 @@
         <v>143</v>
       </c>
       <c r="AI10" s="45">
-        <v>18.489999999999998</v>
+        <v>18.98</v>
       </c>
       <c r="AJ10" s="11" t="s">
         <v>3</v>
@@ -2858,7 +2859,7 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="15"/>
-        <v>5.7328285559762042E-2</v>
+        <v>5.5848261327713387E-2</v>
       </c>
       <c r="AN10" s="7" t="str">
         <f t="shared" si="16"/>
@@ -3006,7 +3007,7 @@
         <v>160</v>
       </c>
       <c r="AI11" s="45">
-        <v>5.07</v>
+        <v>5.17</v>
       </c>
       <c r="AJ11" s="11" t="s">
         <v>3</v>
@@ -3021,7 +3022,7 @@
       </c>
       <c r="AM11" s="5">
         <f t="shared" si="15"/>
-        <v>5.1597633136094674E-2</v>
+        <v>5.0599613152804646E-2</v>
       </c>
       <c r="AN11" s="7">
         <f t="shared" si="16"/>
@@ -3043,14 +3044,14 @@
         <v>150</v>
       </c>
       <c r="AS11" s="45">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AT11" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU11" s="28">
         <f t="shared" si="18"/>
-        <v>-9.5956607495069068E-2</v>
+        <v>-0.13926499032882012</v>
       </c>
       <c r="AV11" s="7" t="str">
         <f t="shared" si="19"/>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="AX11" s="5">
         <f>IF($AR11="","na",(R11/AW11)/AS11)</f>
-        <v>5.707428820770153E-2</v>
+        <v>5.8786516853932581E-2</v>
       </c>
     </row>
     <row r="12" spans="2:50" x14ac:dyDescent="0.45">
@@ -3186,7 +3187,7 @@
         <v>161</v>
       </c>
       <c r="AI12" s="45">
-        <v>38.71</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="AJ12" s="11" t="s">
         <v>3</v>
@@ -3201,7 +3202,7 @@
       </c>
       <c r="AM12" s="5">
         <f t="shared" si="15"/>
-        <v>5.1666236114699046E-2</v>
+        <v>4.9751243781094523E-2</v>
       </c>
       <c r="AN12" s="7">
         <f t="shared" si="16"/>
@@ -3223,14 +3224,14 @@
         <v>151</v>
       </c>
       <c r="AS12" s="45">
-        <v>49.84</v>
+        <v>50.25</v>
       </c>
       <c r="AT12" s="11" t="s">
         <v>106</v>
       </c>
       <c r="AU12" s="28">
         <f t="shared" si="18"/>
-        <v>0.14589511754068729</v>
+        <v>0.11249999999999982</v>
       </c>
       <c r="AV12" s="7" t="str">
         <f t="shared" si="19"/>
@@ -3242,7 +3243,7 @@
       </c>
       <c r="AX12" s="5">
         <f>IF($AR12="","na",(R12/AW12)/AS12)</f>
-        <v>4.5088102151604234E-2</v>
+        <v>4.4720219129073736E-2</v>
       </c>
     </row>
   </sheetData>
